--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F323A3D-E1A6-4EAE-9D95-272FDED97AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BBD3F6-C799-4087-931E-AFA4754E2086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="99">
   <si>
     <t>Protocolo</t>
   </si>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t>Caco</t>
+  </si>
+  <si>
+    <t>Atividades esportivas e recreativas</t>
   </si>
 </sst>
 </file>
@@ -436,7 +439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -511,6 +514,10 @@
     <xf numFmtId="22" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -825,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J163"/>
+  <dimension ref="A1:J164"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -6052,6 +6059,32 @@
         <v>20</v>
       </c>
     </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" s="19">
+        <v>202603001000175</v>
+      </c>
+      <c r="B164" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C164" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D164" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E164" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F164" s="14">
+        <v>46108.686805555553</v>
+      </c>
+      <c r="G164" s="28">
+        <v>46138</v>
+      </c>
+      <c r="H164" s="29"/>
+      <c r="I164" s="29"/>
+      <c r="J164" s="29"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J160" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J159">

--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BBD3F6-C799-4087-931E-AFA4754E2086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B922D5-4CFA-454E-9868-EFEC952EFC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Dash" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$168</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="101">
   <si>
     <t>Protocolo</t>
   </si>
@@ -66,9 +66,6 @@
     <t>Administra</t>
   </si>
   <si>
-    <t>Em Andamento</t>
-  </si>
-  <si>
     <t>Segurança Pública e Trânsito</t>
   </si>
   <si>
@@ -325,13 +322,22 @@
   </si>
   <si>
     <t>Atividades esportivas e recreativas</t>
+  </si>
+  <si>
+    <t>Taxas</t>
+  </si>
+  <si>
+    <t>Projetos</t>
+  </si>
+  <si>
+    <t>Vigilância sanitária</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -372,6 +378,13 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF747474"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -439,7 +452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -518,6 +531,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -832,7 +848,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J164"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:J168"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -869,27 +886,27 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>202509001000009</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>11</v>
@@ -908,24 +925,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19">
         <v>202509002000010</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="E3" s="11" t="s">
         <v>93</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>94</v>
       </c>
       <c r="F3" s="14">
         <v>45915.672222222223</v>
@@ -941,21 +958,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>202509001000011</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>11</v>
@@ -974,21 +991,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19">
         <v>202509001000012</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>11</v>
@@ -1007,24 +1024,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20">
         <v>202509011000013</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F6" s="16">
         <v>45917.379166666666</v>
@@ -1040,24 +1057,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19">
         <v>202509011000014</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>54</v>
-      </c>
       <c r="E7" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F7" s="14">
         <v>45917.64166666667</v>
@@ -1073,21 +1090,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>202509001000015</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>11</v>
@@ -1106,24 +1123,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>202509009000016</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>41</v>
       </c>
       <c r="F9" s="14">
         <v>45919.35833333333</v>
@@ -1139,21 +1156,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>202509001000017</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>11</v>
@@ -1172,24 +1189,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19">
         <v>202509003000018</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F11" s="14">
         <v>45919.522222222222</v>
@@ -1205,24 +1222,24 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>202509011000019</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F12" s="16">
         <v>45922.386805555558</v>
@@ -1238,24 +1255,24 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19">
         <v>202509011000020</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F13" s="14">
         <v>45923.649305555555</v>
@@ -1271,24 +1288,24 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20">
         <v>202509007000021</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F14" s="16">
         <v>45924.336111111108</v>
@@ -1304,24 +1321,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19">
         <v>202509004000022</v>
       </c>
       <c r="B15" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="D15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>19</v>
-      </c>
       <c r="E15" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F15" s="14">
         <v>45924.671527777777</v>
@@ -1337,21 +1354,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20">
         <v>202509001000023</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>11</v>
@@ -1370,24 +1387,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19">
         <v>202509011000024</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>54</v>
-      </c>
       <c r="E17" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F17" s="14">
         <v>45925.611111111109</v>
@@ -1403,24 +1420,24 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20">
         <v>202509011000025</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F18" s="16">
         <v>45930.364583333336</v>
@@ -1436,24 +1453,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19">
         <v>202509015000026</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="E19" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>30</v>
       </c>
       <c r="F19" s="14">
         <v>45930.580555555556</v>
@@ -1469,21 +1486,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="20">
         <v>202509001000027</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>88</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>89</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>11</v>
@@ -1502,24 +1519,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19">
         <v>202510011000028</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F21" s="14">
         <v>45931.661805555559</v>
@@ -1535,24 +1552,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="20">
         <v>202510009000029</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F22" s="16">
         <v>45932.51458333333</v>
@@ -1568,21 +1585,21 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19">
         <v>202510001000030</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>11</v>
@@ -1601,21 +1618,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="20">
         <v>202510001000031</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>11</v>
@@ -1634,21 +1651,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19">
         <v>202510001000032</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>11</v>
@@ -1667,21 +1684,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="20">
         <v>202510001000033</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>11</v>
@@ -1700,24 +1717,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="19">
         <v>202510007000034</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C27" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="E27" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F27" s="14">
         <v>45937.351388888892</v>
@@ -1733,21 +1750,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="20">
         <v>202510001000035</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>11</v>
@@ -1766,24 +1783,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19">
         <v>202510015000036</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="E29" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>30</v>
       </c>
       <c r="F29" s="14">
         <v>45937.414583333331</v>
@@ -1799,7 +1816,7 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -1807,16 +1824,16 @@
         <v>202510011000037</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="E30" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F30" s="16">
         <v>45937.469444444447</v>
@@ -1827,24 +1844,24 @@
       <c r="H30" s="9"/>
       <c r="I30" s="21"/>
       <c r="J30" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19">
         <v>202510003000038</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F31" s="14">
         <v>45937.5</v>
@@ -1860,24 +1877,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20">
         <v>202510011000039</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F32" s="16">
         <v>45937.508333333331</v>
@@ -1893,24 +1910,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19">
         <v>202510004000040</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C33" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="11" t="s">
-        <v>19</v>
-      </c>
       <c r="E33" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F33" s="14">
         <v>45937.513194444444</v>
@@ -1926,24 +1943,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="20">
         <v>202510008000041</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F34" s="16">
         <v>45938.362500000003</v>
@@ -1959,24 +1976,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19">
         <v>202510009000042</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F35" s="14">
         <v>45938.427083333336</v>
@@ -1992,7 +2009,7 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2000,16 +2017,16 @@
         <v>202510011000043</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C36" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D36" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="E36" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F36" s="16">
         <v>45938.615972222222</v>
@@ -2020,24 +2037,24 @@
       <c r="H36" s="9"/>
       <c r="I36" s="15"/>
       <c r="J36" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19">
         <v>202510004000044</v>
       </c>
       <c r="B37" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="D37" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D37" s="11" t="s">
-        <v>19</v>
-      </c>
       <c r="E37" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F37" s="14">
         <v>45939.629861111112</v>
@@ -2053,21 +2070,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="20">
         <v>202510001000045</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>11</v>
@@ -2086,24 +2103,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19">
         <v>202510011000046</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F39" s="14">
         <v>45940.353472222225</v>
@@ -2119,24 +2136,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="20">
         <v>202510004000047</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C40" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D40" s="9" t="s">
-        <v>19</v>
-      </c>
       <c r="E40" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F40" s="16">
         <v>45940.359027777777</v>
@@ -2152,21 +2169,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19">
         <v>202510001000048</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E41" s="11" t="s">
         <v>11</v>
@@ -2185,24 +2202,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="20">
         <v>202510007000049</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F42" s="16">
         <v>45940.499305555553</v>
@@ -2218,21 +2235,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19">
         <v>202510001000050</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E43" s="11" t="s">
         <v>11</v>
@@ -2251,21 +2268,21 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="20">
         <v>202510001000051</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>11</v>
@@ -2284,21 +2301,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="19">
         <v>202510001000052</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C45" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" s="11" t="s">
         <v>79</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>80</v>
       </c>
       <c r="E45" s="11" t="s">
         <v>11</v>
@@ -2317,21 +2334,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="20">
         <v>202510001000053</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>11</v>
@@ -2350,24 +2367,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19">
         <v>202510007000054</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F47" s="14">
         <v>45945.644444444442</v>
@@ -2383,24 +2400,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="20">
         <v>202510015000055</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C48" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D48" s="9" t="s">
+      <c r="E48" s="9" t="s">
         <v>29</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>30</v>
       </c>
       <c r="F48" s="16">
         <v>45945.699305555558</v>
@@ -2416,24 +2433,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19">
         <v>202510011000056</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F49" s="14">
         <v>45946.624305555553</v>
@@ -2449,24 +2466,24 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="20">
         <v>202510009000057</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F50" s="16">
         <v>45947.603472222225</v>
@@ -2482,10 +2499,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="19">
         <v>202510004000058</v>
       </c>
@@ -2493,13 +2510,13 @@
         <v>8</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F51" s="14">
         <v>45947.694444444445</v>
@@ -2515,21 +2532,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="20">
         <v>202510001000059</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>11</v>
@@ -2548,10 +2565,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="19">
         <v>202510001000060</v>
       </c>
@@ -2559,10 +2576,10 @@
         <v>8</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>11</v>
@@ -2581,21 +2598,21 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="20">
         <v>202510001000061</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>11</v>
@@ -2614,10 +2631,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="19">
         <v>202510011000062</v>
       </c>
@@ -2625,13 +2642,13 @@
         <v>8</v>
       </c>
       <c r="C55" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D55" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D55" s="11" t="s">
-        <v>54</v>
-      </c>
       <c r="E55" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F55" s="14">
         <v>45953.380555555559</v>
@@ -2647,10 +2664,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="20">
         <v>202510009000063</v>
       </c>
@@ -2658,13 +2675,13 @@
         <v>8</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D56" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E56" s="9" t="s">
         <v>40</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>41</v>
       </c>
       <c r="F56" s="16">
         <v>45953.43472222222</v>
@@ -2680,24 +2697,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="19">
         <v>202510004000064</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C57" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D57" s="11" t="s">
-        <v>19</v>
-      </c>
       <c r="E57" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F57" s="14">
         <v>45953.693055555559</v>
@@ -2713,10 +2730,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="20">
         <v>202510009000065</v>
       </c>
@@ -2724,13 +2741,13 @@
         <v>8</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D58" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E58" s="9" t="s">
         <v>40</v>
-      </c>
-      <c r="E58" s="9" t="s">
-        <v>41</v>
       </c>
       <c r="F58" s="16">
         <v>45954.374305555553</v>
@@ -2746,10 +2763,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="19">
         <v>202510001000066</v>
       </c>
@@ -2757,10 +2774,10 @@
         <v>8</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E59" s="11" t="s">
         <v>11</v>
@@ -2779,24 +2796,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="20">
         <v>202510008000067</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C60" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D60" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="E60" s="9" t="s">
         <v>65</v>
-      </c>
-      <c r="E60" s="9" t="s">
-        <v>66</v>
       </c>
       <c r="F60" s="16">
         <v>45954.411111111112</v>
@@ -2812,21 +2829,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="19">
         <v>202510001000068</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E61" s="11" t="s">
         <v>11</v>
@@ -2845,21 +2862,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="20">
         <v>202510001000069</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C62" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D62" s="9" t="s">
         <v>31</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>32</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>11</v>
@@ -2878,24 +2895,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="19">
         <v>202510007000070</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C63" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D63" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D63" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="E63" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F63" s="14">
         <v>45958.375694444447</v>
@@ -2911,24 +2928,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="20">
         <v>202510004000071</v>
       </c>
       <c r="B64" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C64" s="9" t="s">
+      <c r="D64" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D64" s="9" t="s">
-        <v>19</v>
-      </c>
       <c r="E64" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F64" s="16">
         <v>45958.496527777781</v>
@@ -2944,10 +2961,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="19">
         <v>202510011000072</v>
       </c>
@@ -2955,13 +2972,13 @@
         <v>8</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F65" s="14">
         <v>45959.40347222222</v>
@@ -2977,21 +2994,21 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="20">
         <v>202510001000073</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>11</v>
@@ -3010,24 +3027,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="19">
         <v>202510004000074</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C67" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D67" s="11" t="s">
-        <v>19</v>
-      </c>
       <c r="E67" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F67" s="14">
         <v>45959.695833333331</v>
@@ -3043,24 +3060,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="20">
         <v>202510011000075</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F68" s="16">
         <v>45959.704861111109</v>
@@ -3076,18 +3093,18 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="19">
         <v>202510001000076</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D69" s="11" t="s">
         <v>0</v>
@@ -3109,18 +3126,18 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="20">
         <v>202510001000077</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D70" s="9" t="s">
         <v>0</v>
@@ -3142,24 +3159,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="19">
         <v>202510004000078</v>
       </c>
       <c r="B71" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="D71" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D71" s="11" t="s">
-        <v>19</v>
-      </c>
       <c r="E71" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F71" s="14">
         <v>45960.4375</v>
@@ -3175,21 +3192,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="20">
         <v>202510001000079</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E72" s="9" t="s">
         <v>11</v>
@@ -3208,10 +3225,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="19">
         <v>202510016000080</v>
       </c>
@@ -3219,13 +3236,13 @@
         <v>8</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D73" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E73" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="E73" s="11" t="s">
-        <v>74</v>
       </c>
       <c r="F73" s="14">
         <v>45961.374305555553</v>
@@ -3241,24 +3258,24 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="20">
         <v>202510007000081</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F74" s="16">
         <v>45961.45</v>
@@ -3274,24 +3291,24 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="19">
         <v>202511011000082</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F75" s="14">
         <v>45964.479861111111</v>
@@ -3307,24 +3324,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="20">
         <v>202511007000083</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F76" s="16">
         <v>45965.35833333333</v>
@@ -3340,24 +3357,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="19">
         <v>202511015000084</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C77" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D77" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D77" s="11" t="s">
+      <c r="E77" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="E77" s="11" t="s">
-        <v>30</v>
       </c>
       <c r="F77" s="14">
         <v>45966.474305555559</v>
@@ -3373,21 +3390,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="20">
         <v>202511001000085</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E78" s="9" t="s">
         <v>11</v>
@@ -3406,24 +3423,24 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="19">
         <v>202511006000086</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D79" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E79" s="11" t="s">
         <v>47</v>
-      </c>
-      <c r="E79" s="11" t="s">
-        <v>48</v>
       </c>
       <c r="F79" s="14">
         <v>45967.488888888889</v>
@@ -3439,24 +3456,24 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="20">
         <v>202511004000087</v>
       </c>
       <c r="B80" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C80" s="9" t="s">
+      <c r="D80" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D80" s="9" t="s">
-        <v>19</v>
-      </c>
       <c r="E80" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F80" s="16">
         <v>45968.387499999997</v>
@@ -3472,24 +3489,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="19">
         <v>202511007000088</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F81" s="14">
         <v>45968.465277777781</v>
@@ -3505,24 +3522,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="20">
         <v>202511008000089</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C82" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D82" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D82" s="9" t="s">
+      <c r="E82" s="9" t="s">
         <v>65</v>
-      </c>
-      <c r="E82" s="9" t="s">
-        <v>66</v>
       </c>
       <c r="F82" s="16">
         <v>45968.493055555555</v>
@@ -3538,24 +3555,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="19">
         <v>202511009000090</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F83" s="14">
         <v>45971.415277777778</v>
@@ -3571,24 +3588,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="20">
         <v>202511009000091</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F84" s="16">
         <v>45971.454861111109</v>
@@ -3604,24 +3621,24 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="19">
         <v>202511011000092</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F85" s="14">
         <v>45972.674305555556</v>
@@ -3637,24 +3654,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="20">
         <v>202511011000093</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F86" s="16">
         <v>45974.462500000001</v>
@@ -3670,24 +3687,24 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="19">
         <v>202511004000094</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C87" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D87" s="11" t="s">
-        <v>19</v>
-      </c>
       <c r="E87" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F87" s="14">
         <v>45974.622916666667</v>
@@ -3703,7 +3720,7 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -3711,16 +3728,16 @@
         <v>202511011000095</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F88" s="16">
         <v>45979.40902777778</v>
@@ -3731,7 +3748,7 @@
       <c r="H88" s="10"/>
       <c r="I88" s="15"/>
       <c r="J88" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -3742,13 +3759,13 @@
         <v>8</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F89" s="14">
         <v>45979.479861111111</v>
@@ -3759,10 +3776,10 @@
       <c r="H89" s="11"/>
       <c r="I89" s="15"/>
       <c r="J89" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="20">
         <v>202511001000097</v>
       </c>
@@ -3770,10 +3787,10 @@
         <v>8</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E90" s="9" t="s">
         <v>11</v>
@@ -3792,24 +3809,24 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="19">
         <v>202511007000098</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F91" s="14">
         <v>45980.656944444447</v>
@@ -3825,24 +3842,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="20">
         <v>202511007000099</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C92" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D92" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D92" s="9" t="s">
-        <v>27</v>
-      </c>
       <c r="E92" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F92" s="16">
         <v>45982.683333333334</v>
@@ -3858,24 +3875,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="19">
         <v>202511007000100</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F93" s="14">
         <v>45982.686805555553</v>
@@ -3891,10 +3908,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="20">
         <v>202511011000101</v>
       </c>
@@ -3902,13 +3919,13 @@
         <v>8</v>
       </c>
       <c r="C94" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D94" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D94" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="E94" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F94" s="16">
         <v>45985.623611111114</v>
@@ -3924,10 +3941,10 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="19">
         <v>202511009000102</v>
       </c>
@@ -3935,13 +3952,13 @@
         <v>8</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F95" s="14">
         <v>45986.402777777781</v>
@@ -3957,10 +3974,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="20">
         <v>202511001000103</v>
       </c>
@@ -3968,10 +3985,10 @@
         <v>8</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E96" s="9" t="s">
         <v>11</v>
@@ -3990,7 +4007,7 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -3998,16 +4015,16 @@
         <v>202511007000104</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F97" s="14">
         <v>45987.506944444445</v>
@@ -4018,10 +4035,10 @@
       <c r="H97" s="10"/>
       <c r="I97" s="15"/>
       <c r="J97" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="20">
         <v>202511007000105</v>
       </c>
@@ -4029,13 +4046,13 @@
         <v>8</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F98" s="16">
         <v>45988.619444444441</v>
@@ -4051,10 +4068,10 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="19">
         <v>202511009000106</v>
       </c>
@@ -4062,13 +4079,13 @@
         <v>8</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F99" s="14">
         <v>45988.675000000003</v>
@@ -4084,10 +4101,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="20">
         <v>202511001000107</v>
       </c>
@@ -4095,10 +4112,10 @@
         <v>8</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>11</v>
@@ -4117,10 +4134,10 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="19">
         <v>202511009000108</v>
       </c>
@@ -4128,13 +4145,13 @@
         <v>8</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F101" s="14">
         <v>45989.461111111108</v>
@@ -4150,7 +4167,7 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -4161,13 +4178,13 @@
         <v>8</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F102" s="16">
         <v>45989.697916666664</v>
@@ -4178,10 +4195,10 @@
       <c r="H102" s="9"/>
       <c r="I102" s="15"/>
       <c r="J102" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="19">
         <v>202511001000110</v>
       </c>
@@ -4189,10 +4206,10 @@
         <v>8</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E103" s="11" t="s">
         <v>11</v>
@@ -4211,10 +4228,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="20">
         <v>202512011000111</v>
       </c>
@@ -4222,13 +4239,13 @@
         <v>8</v>
       </c>
       <c r="C104" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D104" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D104" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="E104" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F104" s="16">
         <v>45992.445138888892</v>
@@ -4244,10 +4261,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="19">
         <v>202512015000112</v>
       </c>
@@ -4255,13 +4272,13 @@
         <v>8</v>
       </c>
       <c r="C105" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D105" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D105" s="11" t="s">
+      <c r="E105" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="E105" s="11" t="s">
-        <v>30</v>
       </c>
       <c r="F105" s="14">
         <v>45992.684027777781</v>
@@ -4277,7 +4294,7 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -4288,13 +4305,13 @@
         <v>8</v>
       </c>
       <c r="C106" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D106" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D106" s="9" t="s">
+      <c r="E106" s="9" t="s">
         <v>29</v>
-      </c>
-      <c r="E106" s="9" t="s">
-        <v>30</v>
       </c>
       <c r="F106" s="16">
         <v>45993.400694444441</v>
@@ -4305,10 +4322,10 @@
       <c r="H106" s="9"/>
       <c r="I106" s="15"/>
       <c r="J106" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="19">
         <v>202512008000114</v>
       </c>
@@ -4316,13 +4333,13 @@
         <v>8</v>
       </c>
       <c r="C107" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D107" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D107" s="11" t="s">
+      <c r="E107" s="11" t="s">
         <v>65</v>
-      </c>
-      <c r="E107" s="11" t="s">
-        <v>66</v>
       </c>
       <c r="F107" s="14">
         <v>45993.460416666669</v>
@@ -4338,7 +4355,7 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -4349,13 +4366,13 @@
         <v>8</v>
       </c>
       <c r="C108" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D108" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D108" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="E108" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F108" s="16">
         <v>45993.638888888891</v>
@@ -4366,10 +4383,10 @@
       <c r="H108" s="9"/>
       <c r="I108" s="15"/>
       <c r="J108" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="19">
         <v>202512015000116</v>
       </c>
@@ -4377,13 +4394,13 @@
         <v>8</v>
       </c>
       <c r="C109" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D109" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D109" s="11" t="s">
+      <c r="E109" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="E109" s="11" t="s">
-        <v>30</v>
       </c>
       <c r="F109" s="14">
         <v>45993.895833333336</v>
@@ -4399,10 +4416,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="20">
         <v>202512007000117</v>
       </c>
@@ -4410,13 +4427,13 @@
         <v>8</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E110" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F110" s="16">
         <v>45994.686805555553</v>
@@ -4432,10 +4449,10 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="19">
         <v>202512001000118</v>
       </c>
@@ -4443,10 +4460,10 @@
         <v>8</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E111" s="11" t="s">
         <v>11</v>
@@ -4465,24 +4482,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="20">
         <v>202512009000119</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F112" s="16">
         <v>45995.634027777778</v>
@@ -4498,24 +4515,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="19">
         <v>202512011000120</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C113" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D113" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D113" s="11" t="s">
-        <v>54</v>
-      </c>
       <c r="E113" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F113" s="14">
         <v>45999.407638888886</v>
@@ -4531,7 +4548,7 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -4542,13 +4559,13 @@
         <v>8</v>
       </c>
       <c r="C114" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D114" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D114" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="E114" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F114" s="16">
         <v>46001.634722222225</v>
@@ -4559,10 +4576,10 @@
       <c r="H114" s="9"/>
       <c r="I114" s="15"/>
       <c r="J114" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="19">
         <v>202512011000122</v>
       </c>
@@ -4570,13 +4587,13 @@
         <v>8</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F115" s="14">
         <v>46003.506944444445</v>
@@ -4592,7 +4609,7 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -4600,16 +4617,16 @@
         <v>202512007000123</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F116" s="16">
         <v>46008.395138888889</v>
@@ -4620,7 +4637,7 @@
       <c r="H116" s="9"/>
       <c r="I116" s="15"/>
       <c r="J116" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -4631,13 +4648,13 @@
         <v>8</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F117" s="14">
         <v>46010.370138888888</v>
@@ -4648,10 +4665,10 @@
       <c r="H117" s="11"/>
       <c r="I117" s="15"/>
       <c r="J117" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="20">
         <v>202512015000125</v>
       </c>
@@ -4659,13 +4676,13 @@
         <v>8</v>
       </c>
       <c r="C118" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D118" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D118" s="9" t="s">
+      <c r="E118" s="9" t="s">
         <v>29</v>
-      </c>
-      <c r="E118" s="9" t="s">
-        <v>30</v>
       </c>
       <c r="F118" s="16">
         <v>46014.677777777775</v>
@@ -4681,10 +4698,10 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="19">
         <v>202512001000126</v>
       </c>
@@ -4692,10 +4709,10 @@
         <v>8</v>
       </c>
       <c r="C119" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D119" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="D119" s="11" t="s">
-        <v>24</v>
       </c>
       <c r="E119" s="11" t="s">
         <v>11</v>
@@ -4714,10 +4731,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="20">
         <v>202512011000127</v>
       </c>
@@ -4725,13 +4742,13 @@
         <v>8</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E120" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F120" s="16">
         <v>46019.70416666667</v>
@@ -4747,24 +4764,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="19">
         <v>202601011000128</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F121" s="14">
         <v>46024.73333333333</v>
@@ -4780,7 +4797,7 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -4788,16 +4805,16 @@
         <v>202601003000129</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F122" s="16">
         <v>46027.561805555553</v>
@@ -4808,10 +4825,10 @@
       <c r="H122" s="10"/>
       <c r="I122" s="15"/>
       <c r="J122" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="19">
         <v>202601011000130</v>
       </c>
@@ -4819,13 +4836,13 @@
         <v>8</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E123" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F123" s="14">
         <v>46030.428472222222</v>
@@ -4841,7 +4858,7 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -4852,13 +4869,13 @@
         <v>8</v>
       </c>
       <c r="C124" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D124" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D124" s="9" t="s">
+      <c r="E124" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="E124" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="F124" s="16">
         <v>46030.569444444445</v>
@@ -4869,10 +4886,10 @@
       <c r="H124" s="10"/>
       <c r="I124" s="15"/>
       <c r="J124" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="19">
         <v>202601007000132</v>
       </c>
@@ -4880,13 +4897,13 @@
         <v>8</v>
       </c>
       <c r="C125" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D125" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D125" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="E125" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F125" s="14">
         <v>46031.270833333336</v>
@@ -4902,7 +4919,7 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
@@ -4910,16 +4927,16 @@
         <v>202601007000133</v>
       </c>
       <c r="B126" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C126" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D126" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C126" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D126" s="9" t="s">
-        <v>38</v>
-      </c>
       <c r="E126" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F126" s="16">
         <v>46032.509722222225</v>
@@ -4930,10 +4947,10 @@
       <c r="H126" s="10"/>
       <c r="I126" s="15"/>
       <c r="J126" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="19">
         <v>202601009000134</v>
       </c>
@@ -4941,13 +4958,13 @@
         <v>8</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E127" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F127" s="14">
         <v>46034.411805555559</v>
@@ -4963,7 +4980,7 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
@@ -4971,16 +4988,16 @@
         <v>202601011000135</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C128" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D128" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D128" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="E128" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F128" s="16">
         <v>46034.448611111111</v>
@@ -4991,24 +5008,24 @@
       <c r="H128" s="10"/>
       <c r="I128" s="15"/>
       <c r="J128" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="19">
         <v>202601001000136</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E129" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F129" s="14">
         <v>46035.555555555555</v>
@@ -5024,24 +5041,24 @@
         <v>Fora do Prazo</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="20">
         <v>202601001000137</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E130" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F130" s="16">
         <v>46036.696527777778</v>
@@ -5057,24 +5074,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="19">
         <v>202601007000138</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C131" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D131" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D131" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="E131" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F131" s="14">
         <v>46037.330555555556</v>
@@ -5090,10 +5107,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="20">
         <v>202601007000141</v>
       </c>
@@ -5101,13 +5118,13 @@
         <v>8</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E132" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F132" s="16">
         <v>46048.584722222222</v>
@@ -5123,7 +5140,7 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -5131,13 +5148,13 @@
         <v>202601013000142</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D133" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E133" s="11" t="s">
         <v>3</v>
@@ -5151,7 +5168,7 @@
       <c r="H133" s="10"/>
       <c r="I133" s="15"/>
       <c r="J133" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -5159,16 +5176,16 @@
         <v>202601007000143</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E134" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F134" s="16">
         <v>46051.736111111109</v>
@@ -5179,7 +5196,7 @@
       <c r="H134" s="10"/>
       <c r="I134" s="15"/>
       <c r="J134" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -5190,13 +5207,13 @@
         <v>8</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E135" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F135" s="14">
         <v>46058.554861111108</v>
@@ -5207,24 +5224,24 @@
       <c r="H135" s="11"/>
       <c r="I135" s="15"/>
       <c r="J135" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="20">
         <v>202602007000145</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E136" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F136" s="16">
         <v>46062.308333333334</v>
@@ -5240,24 +5257,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="19">
         <v>202602007000146</v>
       </c>
       <c r="B137" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E137" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F137" s="14">
         <v>46062.349305555559</v>
@@ -5273,7 +5290,7 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -5281,7 +5298,7 @@
         <v>202602001000147</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C138" s="9" t="s">
         <v>9</v>
@@ -5301,7 +5318,7 @@
       <c r="H138" s="21"/>
       <c r="I138" s="15"/>
       <c r="J138" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -5309,16 +5326,16 @@
         <v>202602006000148</v>
       </c>
       <c r="B139" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C139" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E139" s="11" t="s">
         <v>47</v>
-      </c>
-      <c r="D139" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E139" s="11" t="s">
-        <v>48</v>
       </c>
       <c r="F139" s="14">
         <v>46066.445833333331</v>
@@ -5329,7 +5346,7 @@
       <c r="H139" s="21"/>
       <c r="I139" s="15"/>
       <c r="J139" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -5337,16 +5354,16 @@
         <v>202602007000149</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E140" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F140" s="16">
         <v>46066.645833333336</v>
@@ -5357,7 +5374,7 @@
       <c r="H140" s="9"/>
       <c r="I140" s="15"/>
       <c r="J140" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -5365,16 +5382,16 @@
         <v>202602007000150</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E141" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F141" s="14">
         <v>46068.59375</v>
@@ -5385,21 +5402,21 @@
       <c r="H141" s="21"/>
       <c r="I141" s="15"/>
       <c r="J141" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="20">
         <v>202602001000151</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C142" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D142" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="D142" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="E142" s="9" t="s">
         <v>11</v>
@@ -5418,7 +5435,7 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -5426,16 +5443,16 @@
         <v>202602012000152</v>
       </c>
       <c r="B143" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E143" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F143" s="14">
         <v>46071.645833333336</v>
@@ -5446,21 +5463,21 @@
       <c r="H143" s="10"/>
       <c r="I143" s="15"/>
       <c r="J143" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="20">
         <v>202602001000153</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E144" s="9" t="s">
         <v>11</v>
@@ -5479,7 +5496,7 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -5490,13 +5507,13 @@
         <v>8</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D145" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E145" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="E145" s="11" t="s">
-        <v>41</v>
       </c>
       <c r="F145" s="14">
         <v>46072.405555555553</v>
@@ -5507,7 +5524,7 @@
       <c r="H145" s="11"/>
       <c r="I145" s="15"/>
       <c r="J145" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -5515,16 +5532,16 @@
         <v>202602007000155</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C146" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D146" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D146" s="9" t="s">
-        <v>27</v>
-      </c>
       <c r="E146" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F146" s="16">
         <v>46073.628472222219</v>
@@ -5535,24 +5552,24 @@
       <c r="H146" s="10"/>
       <c r="I146" s="15"/>
       <c r="J146" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="19">
         <v>202602007000156</v>
       </c>
       <c r="B147" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E147" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F147" s="14">
         <v>46073.695138888892</v>
@@ -5568,7 +5585,7 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J147" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -5576,16 +5593,16 @@
         <v>202602007000157</v>
       </c>
       <c r="B148" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C148" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D148" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C148" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D148" s="9" t="s">
-        <v>38</v>
-      </c>
       <c r="E148" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F148" s="16">
         <v>46075.175694444442</v>
@@ -5596,7 +5613,7 @@
       <c r="H148" s="9"/>
       <c r="I148" s="15"/>
       <c r="J148" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -5604,13 +5621,13 @@
         <v>202602013000158</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C149" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D149" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="D149" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="E149" s="4" t="s">
         <v>3</v>
@@ -5624,21 +5641,21 @@
       <c r="H149" s="12"/>
       <c r="I149" s="13"/>
       <c r="J149" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="25">
         <v>202602001000159</v>
       </c>
       <c r="B150" s="26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C150" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D150" s="26" t="s">
         <v>31</v>
-      </c>
-      <c r="D150" s="26" t="s">
-        <v>32</v>
       </c>
       <c r="E150" s="26" t="s">
         <v>11</v>
@@ -5657,7 +5674,7 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -5668,13 +5685,13 @@
         <v>8</v>
       </c>
       <c r="C151" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D151" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D151" s="4" t="s">
+      <c r="E151" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="E151" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="F151" s="24">
         <v>46077.585416666669</v>
@@ -5685,7 +5702,7 @@
       <c r="H151" s="12"/>
       <c r="I151" s="13"/>
       <c r="J151" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -5696,13 +5713,13 @@
         <v>8</v>
       </c>
       <c r="C152" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D152" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="D152" s="26" t="s">
-        <v>27</v>
-      </c>
       <c r="E152" s="26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F152" s="27">
         <v>46079.628472222219</v>
@@ -5712,11 +5729,11 @@
       </c>
       <c r="H152" s="13"/>
       <c r="I152" s="13"/>
-      <c r="J152" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J152" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="23">
         <v>202603012000162</v>
       </c>
@@ -5724,13 +5741,13 @@
         <v>8</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F153" s="24">
         <v>46084.686805555553</v>
@@ -5746,10 +5763,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J153" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="25">
         <v>202603012000163</v>
       </c>
@@ -5757,13 +5774,13 @@
         <v>8</v>
       </c>
       <c r="C154" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D154" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="D154" s="26" t="s">
-        <v>24</v>
-      </c>
       <c r="E154" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F154" s="27">
         <v>46087.588194444441</v>
@@ -5779,21 +5796,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J154" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="23">
         <v>202603001000165</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E155" s="4" t="s">
         <v>11</v>
@@ -5812,24 +5829,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="25">
         <v>202603004000166</v>
       </c>
       <c r="B156" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C156" s="26" t="s">
+      <c r="D156" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D156" s="26" t="s">
-        <v>19</v>
-      </c>
       <c r="E156" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F156" s="27">
         <v>46093.43472222222</v>
@@ -5845,10 +5862,10 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="23">
         <v>202603007000167</v>
       </c>
@@ -5856,13 +5873,13 @@
         <v>8</v>
       </c>
       <c r="C157" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D157" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D157" s="4" t="s">
+      <c r="E157" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="E157" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="F157" s="24">
         <v>46093.443055555559</v>
@@ -5870,13 +5887,18 @@
       <c r="G157" s="12">
         <v>46123</v>
       </c>
-      <c r="H157" s="12"/>
-      <c r="I157" s="12"/>
-      <c r="J157" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H157" s="13">
+        <v>46118</v>
+      </c>
+      <c r="I157" s="13" t="str">
+        <f>IF(H157&lt;=G157,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J157" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="25">
         <v>202603001000168</v>
       </c>
@@ -5898,13 +5920,18 @@
       <c r="G158" s="13">
         <v>46124</v>
       </c>
-      <c r="H158" s="13"/>
-      <c r="I158" s="13"/>
+      <c r="H158" s="13">
+        <v>46113</v>
+      </c>
+      <c r="I158" s="13" t="str">
+        <f>IF(H158&lt;=G158,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J158" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="23">
         <v>202603001000170</v>
       </c>
@@ -5934,15 +5961,15 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" s="5" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="20">
         <v>202603001000171</v>
       </c>
       <c r="B160" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C160" s="9" t="s">
         <v>9</v>
@@ -5967,24 +5994,24 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="19">
         <v>202603007000172</v>
       </c>
       <c r="B161" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E161" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F161" s="14">
         <v>46102.166666666664</v>
@@ -5995,10 +6022,10 @@
       <c r="H161" s="15"/>
       <c r="I161" s="15"/>
       <c r="J161" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="20">
         <v>202603012000173</v>
       </c>
@@ -6006,13 +6033,13 @@
         <v>8</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D162" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E162" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F162" s="16">
         <v>46104.602777777778</v>
@@ -6023,21 +6050,21 @@
       <c r="H162" s="17"/>
       <c r="I162" s="15"/>
       <c r="J162" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="20">
         <v>202603001000174</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D163" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>11</v>
@@ -6056,21 +6083,21 @@
         <v>Dentro do Prazo</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="19">
         <v>202603001000175</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E164" s="11" t="s">
         <v>11</v>
@@ -6081,15 +6108,146 @@
       <c r="G164" s="28">
         <v>46138</v>
       </c>
-      <c r="H164" s="29"/>
-      <c r="I164" s="29"/>
-      <c r="J164" s="29"/>
+      <c r="H164" s="18">
+        <v>46118</v>
+      </c>
+      <c r="I164" s="13" t="str">
+        <f>IF(H164&lt;=G164,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J164" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="20">
+        <v>202603001000179</v>
+      </c>
+      <c r="B165" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D165" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E165" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F165" s="16">
+        <v>46111.413888888892</v>
+      </c>
+      <c r="G165" s="7">
+        <v>46141</v>
+      </c>
+      <c r="H165" s="18">
+        <v>46113</v>
+      </c>
+      <c r="I165" s="13" t="str">
+        <f>IF(H165&lt;=G165,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J165" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="19">
+        <v>202603012000180</v>
+      </c>
+      <c r="B166" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C166" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D166" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E166" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F166" s="14">
+        <v>46111.465277777781</v>
+      </c>
+      <c r="G166" s="6">
+        <v>46141</v>
+      </c>
+      <c r="H166" s="30"/>
+      <c r="I166" s="29"/>
+      <c r="J166" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="20">
+        <v>202603007000181</v>
+      </c>
+      <c r="B167" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C167" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D167" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E167" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F167" s="16">
+        <v>46111.618750000001</v>
+      </c>
+      <c r="G167" s="7">
+        <v>46141</v>
+      </c>
+      <c r="H167" s="29"/>
+      <c r="I167" s="29"/>
+      <c r="J167" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="20">
+        <v>202604012000182</v>
+      </c>
+      <c r="B168" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C168" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D168" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E168" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F168" s="16">
+        <v>46113.658333333333</v>
+      </c>
+      <c r="G168" s="7">
+        <v>46143</v>
+      </c>
+      <c r="H168" s="17"/>
+      <c r="I168" s="15"/>
+      <c r="J168" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J160" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
+  <autoFilter ref="A1:J168" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
+    <filterColumn colId="9">
+      <filters>
+        <filter val="ATRASO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J159">
     <sortCondition ref="F1:F159"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967294" verticalDpi="4294967294" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B922D5-4CFA-454E-9868-EFEC952EFC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A8EE3E-2EC6-4495-BE95-B1F8CEA83F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="102">
   <si>
     <t>Protocolo</t>
   </si>
@@ -331,6 +331,9 @@
   </si>
   <si>
     <t>Vigilância sanitária</t>
+  </si>
+  <si>
+    <t>Roçagem</t>
   </si>
 </sst>
 </file>
@@ -848,8 +851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J169"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -895,7 +897,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>202509001000009</v>
       </c>
@@ -928,7 +930,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="19">
         <v>202509002000010</v>
       </c>
@@ -961,7 +963,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>202509001000011</v>
       </c>
@@ -994,7 +996,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="19">
         <v>202509001000012</v>
       </c>
@@ -1027,7 +1029,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="20">
         <v>202509011000013</v>
       </c>
@@ -1060,7 +1062,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="19">
         <v>202509011000014</v>
       </c>
@@ -1093,7 +1095,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>202509001000015</v>
       </c>
@@ -1126,7 +1128,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>202509009000016</v>
       </c>
@@ -1159,7 +1161,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>202509001000017</v>
       </c>
@@ -1192,7 +1194,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="19">
         <v>202509003000018</v>
       </c>
@@ -1225,7 +1227,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>202509011000019</v>
       </c>
@@ -1258,7 +1260,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="19">
         <v>202509011000020</v>
       </c>
@@ -1291,7 +1293,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="20">
         <v>202509007000021</v>
       </c>
@@ -1324,7 +1326,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="19">
         <v>202509004000022</v>
       </c>
@@ -1357,7 +1359,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="20">
         <v>202509001000023</v>
       </c>
@@ -1390,7 +1392,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="19">
         <v>202509011000024</v>
       </c>
@@ -1423,7 +1425,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="20">
         <v>202509011000025</v>
       </c>
@@ -1456,7 +1458,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="19">
         <v>202509015000026</v>
       </c>
@@ -1489,7 +1491,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="20">
         <v>202509001000027</v>
       </c>
@@ -1522,7 +1524,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="19">
         <v>202510011000028</v>
       </c>
@@ -1555,7 +1557,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="20">
         <v>202510009000029</v>
       </c>
@@ -1588,7 +1590,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="19">
         <v>202510001000030</v>
       </c>
@@ -1621,7 +1623,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="20">
         <v>202510001000031</v>
       </c>
@@ -1654,7 +1656,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="19">
         <v>202510001000032</v>
       </c>
@@ -1687,7 +1689,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="20">
         <v>202510001000033</v>
       </c>
@@ -1720,7 +1722,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="19">
         <v>202510007000034</v>
       </c>
@@ -1753,7 +1755,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="20">
         <v>202510001000035</v>
       </c>
@@ -1786,7 +1788,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="19">
         <v>202510015000036</v>
       </c>
@@ -1847,7 +1849,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="19">
         <v>202510003000038</v>
       </c>
@@ -1880,7 +1882,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="20">
         <v>202510011000039</v>
       </c>
@@ -1913,7 +1915,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="19">
         <v>202510004000040</v>
       </c>
@@ -1946,7 +1948,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="20">
         <v>202510008000041</v>
       </c>
@@ -1979,7 +1981,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="19">
         <v>202510009000042</v>
       </c>
@@ -2040,7 +2042,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="19">
         <v>202510004000044</v>
       </c>
@@ -2073,7 +2075,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="20">
         <v>202510001000045</v>
       </c>
@@ -2106,7 +2108,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="19">
         <v>202510011000046</v>
       </c>
@@ -2139,7 +2141,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="20">
         <v>202510004000047</v>
       </c>
@@ -2172,7 +2174,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="19">
         <v>202510001000048</v>
       </c>
@@ -2205,7 +2207,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="20">
         <v>202510007000049</v>
       </c>
@@ -2238,7 +2240,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="19">
         <v>202510001000050</v>
       </c>
@@ -2271,7 +2273,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="20">
         <v>202510001000051</v>
       </c>
@@ -2304,7 +2306,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="19">
         <v>202510001000052</v>
       </c>
@@ -2337,7 +2339,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="20">
         <v>202510001000053</v>
       </c>
@@ -2370,7 +2372,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="19">
         <v>202510007000054</v>
       </c>
@@ -2403,7 +2405,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="20">
         <v>202510015000055</v>
       </c>
@@ -2436,7 +2438,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="19">
         <v>202510011000056</v>
       </c>
@@ -2469,7 +2471,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="20">
         <v>202510009000057</v>
       </c>
@@ -2502,7 +2504,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="19">
         <v>202510004000058</v>
       </c>
@@ -2535,7 +2537,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="20">
         <v>202510001000059</v>
       </c>
@@ -2568,7 +2570,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="19">
         <v>202510001000060</v>
       </c>
@@ -2601,7 +2603,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="20">
         <v>202510001000061</v>
       </c>
@@ -2634,7 +2636,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="19">
         <v>202510011000062</v>
       </c>
@@ -2667,7 +2669,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="20">
         <v>202510009000063</v>
       </c>
@@ -2700,7 +2702,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="19">
         <v>202510004000064</v>
       </c>
@@ -2733,7 +2735,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="20">
         <v>202510009000065</v>
       </c>
@@ -2766,7 +2768,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="19">
         <v>202510001000066</v>
       </c>
@@ -2799,7 +2801,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="20">
         <v>202510008000067</v>
       </c>
@@ -2832,7 +2834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="19">
         <v>202510001000068</v>
       </c>
@@ -2865,7 +2867,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="20">
         <v>202510001000069</v>
       </c>
@@ -2898,7 +2900,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="19">
         <v>202510007000070</v>
       </c>
@@ -2931,7 +2933,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="20">
         <v>202510004000071</v>
       </c>
@@ -2964,7 +2966,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="19">
         <v>202510011000072</v>
       </c>
@@ -2997,7 +2999,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="20">
         <v>202510001000073</v>
       </c>
@@ -3030,7 +3032,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="19">
         <v>202510004000074</v>
       </c>
@@ -3063,7 +3065,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="20">
         <v>202510011000075</v>
       </c>
@@ -3096,7 +3098,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="19">
         <v>202510001000076</v>
       </c>
@@ -3129,7 +3131,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="20">
         <v>202510001000077</v>
       </c>
@@ -3162,7 +3164,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="19">
         <v>202510004000078</v>
       </c>
@@ -3195,7 +3197,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="20">
         <v>202510001000079</v>
       </c>
@@ -3228,7 +3230,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="19">
         <v>202510016000080</v>
       </c>
@@ -3261,7 +3263,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="20">
         <v>202510007000081</v>
       </c>
@@ -3294,7 +3296,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="19">
         <v>202511011000082</v>
       </c>
@@ -3327,7 +3329,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="20">
         <v>202511007000083</v>
       </c>
@@ -3360,7 +3362,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="19">
         <v>202511015000084</v>
       </c>
@@ -3393,7 +3395,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="20">
         <v>202511001000085</v>
       </c>
@@ -3426,7 +3428,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="19">
         <v>202511006000086</v>
       </c>
@@ -3459,7 +3461,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="20">
         <v>202511004000087</v>
       </c>
@@ -3492,7 +3494,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="19">
         <v>202511007000088</v>
       </c>
@@ -3525,7 +3527,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="20">
         <v>202511008000089</v>
       </c>
@@ -3558,7 +3560,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="19">
         <v>202511009000090</v>
       </c>
@@ -3591,7 +3593,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="20">
         <v>202511009000091</v>
       </c>
@@ -3624,7 +3626,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="19">
         <v>202511011000092</v>
       </c>
@@ -3657,7 +3659,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="20">
         <v>202511011000093</v>
       </c>
@@ -3690,7 +3692,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="19">
         <v>202511004000094</v>
       </c>
@@ -3779,7 +3781,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="20">
         <v>202511001000097</v>
       </c>
@@ -3812,7 +3814,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="19">
         <v>202511007000098</v>
       </c>
@@ -3845,7 +3847,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="20">
         <v>202511007000099</v>
       </c>
@@ -3878,7 +3880,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="19">
         <v>202511007000100</v>
       </c>
@@ -3911,7 +3913,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="20">
         <v>202511011000101</v>
       </c>
@@ -3944,7 +3946,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="19">
         <v>202511009000102</v>
       </c>
@@ -3977,7 +3979,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="20">
         <v>202511001000103</v>
       </c>
@@ -4038,7 +4040,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="20">
         <v>202511007000105</v>
       </c>
@@ -4071,7 +4073,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="19">
         <v>202511009000106</v>
       </c>
@@ -4104,7 +4106,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="20">
         <v>202511001000107</v>
       </c>
@@ -4137,7 +4139,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="19">
         <v>202511009000108</v>
       </c>
@@ -4198,7 +4200,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="19">
         <v>202511001000110</v>
       </c>
@@ -4231,7 +4233,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="20">
         <v>202512011000111</v>
       </c>
@@ -4264,7 +4266,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="19">
         <v>202512015000112</v>
       </c>
@@ -4325,7 +4327,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="19">
         <v>202512008000114</v>
       </c>
@@ -4386,7 +4388,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="19">
         <v>202512015000116</v>
       </c>
@@ -4419,7 +4421,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="20">
         <v>202512007000117</v>
       </c>
@@ -4452,7 +4454,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="19">
         <v>202512001000118</v>
       </c>
@@ -4485,7 +4487,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="20">
         <v>202512009000119</v>
       </c>
@@ -4518,7 +4520,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="19">
         <v>202512011000120</v>
       </c>
@@ -4579,7 +4581,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="19">
         <v>202512011000122</v>
       </c>
@@ -4668,7 +4670,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="20">
         <v>202512015000125</v>
       </c>
@@ -4701,7 +4703,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="19">
         <v>202512001000126</v>
       </c>
@@ -4734,7 +4736,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="20">
         <v>202512011000127</v>
       </c>
@@ -4767,7 +4769,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="19">
         <v>202601011000128</v>
       </c>
@@ -4828,7 +4830,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="19">
         <v>202601011000130</v>
       </c>
@@ -4889,7 +4891,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="19">
         <v>202601007000132</v>
       </c>
@@ -4950,7 +4952,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="19">
         <v>202601009000134</v>
       </c>
@@ -5011,7 +5013,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="19">
         <v>202601001000136</v>
       </c>
@@ -5044,7 +5046,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="20">
         <v>202601001000137</v>
       </c>
@@ -5077,7 +5079,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="19">
         <v>202601007000138</v>
       </c>
@@ -5110,7 +5112,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="20">
         <v>202601007000141</v>
       </c>
@@ -5227,7 +5229,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="20">
         <v>202602007000145</v>
       </c>
@@ -5260,7 +5262,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="19">
         <v>202602007000146</v>
       </c>
@@ -5405,7 +5407,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="20">
         <v>202602001000151</v>
       </c>
@@ -5466,7 +5468,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="20">
         <v>202602001000153</v>
       </c>
@@ -5555,7 +5557,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="19">
         <v>202602007000156</v>
       </c>
@@ -5644,7 +5646,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="25">
         <v>202602001000159</v>
       </c>
@@ -5733,7 +5735,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="23">
         <v>202603012000162</v>
       </c>
@@ -5759,14 +5761,14 @@
         <v>46091</v>
       </c>
       <c r="I153" s="13" t="str">
-        <f>IF(H153&lt;=G153,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I153:I160" si="5">IF(H153&lt;=G153,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J153" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="25">
         <v>202603012000163</v>
       </c>
@@ -5792,14 +5794,14 @@
         <v>46104</v>
       </c>
       <c r="I154" s="13" t="str">
-        <f>IF(H154&lt;=G154,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="5"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J154" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="23">
         <v>202603001000165</v>
       </c>
@@ -5825,14 +5827,14 @@
         <v>46093</v>
       </c>
       <c r="I155" s="13" t="str">
-        <f>IF(H155&lt;=G155,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="5"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J155" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="25">
         <v>202603004000166</v>
       </c>
@@ -5858,14 +5860,14 @@
         <v>46099</v>
       </c>
       <c r="I156" s="13" t="str">
-        <f>IF(H156&lt;=G156,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="5"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="23">
         <v>202603007000167</v>
       </c>
@@ -5891,14 +5893,14 @@
         <v>46118</v>
       </c>
       <c r="I157" s="13" t="str">
-        <f>IF(H157&lt;=G157,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="5"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="25">
         <v>202603001000168</v>
       </c>
@@ -5924,14 +5926,14 @@
         <v>46113</v>
       </c>
       <c r="I158" s="13" t="str">
-        <f>IF(H158&lt;=G158,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="5"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="23">
         <v>202603001000170</v>
       </c>
@@ -5957,14 +5959,14 @@
         <v>46101</v>
       </c>
       <c r="I159" s="13" t="str">
-        <f>IF(H159&lt;=G159,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="5"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="160" spans="1:10" s="5" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:10" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A160" s="20">
         <v>202603001000171</v>
       </c>
@@ -5990,14 +5992,14 @@
         <v>46101</v>
       </c>
       <c r="I160" s="13" t="str">
-        <f>IF(H160&lt;=G160,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="5"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="19">
         <v>202603007000172</v>
       </c>
@@ -6025,7 +6027,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="20">
         <v>202603012000173</v>
       </c>
@@ -6053,7 +6055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="20">
         <v>202603001000174</v>
       </c>
@@ -6086,7 +6088,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="19">
         <v>202603001000175</v>
       </c>
@@ -6119,7 +6121,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="20">
         <v>202603001000179</v>
       </c>
@@ -6152,7 +6154,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="19">
         <v>202603012000180</v>
       </c>
@@ -6180,7 +6182,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="20">
         <v>202603007000181</v>
       </c>
@@ -6208,7 +6210,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="20">
         <v>202604012000182</v>
       </c>
@@ -6236,14 +6238,36 @@
         <v>15</v>
       </c>
     </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A169" s="20">
+        <v>202604013000183</v>
+      </c>
+      <c r="B169" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D169" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E169" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F169" s="16">
+        <v>46119.414583333331</v>
+      </c>
+      <c r="G169" s="7">
+        <v>46149</v>
+      </c>
+      <c r="H169" s="15"/>
+      <c r="I169" s="15"/>
+      <c r="J169" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J168" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-    <filterColumn colId="9">
-      <filters>
-        <filter val="ATRASO"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J168" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J159">
     <sortCondition ref="F1:F159"/>
   </sortState>

--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A8EE3E-2EC6-4495-BE95-B1F8CEA83F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5A0F24-4739-4912-97A5-F4A980007B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Dash" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$169</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="102">
   <si>
     <t>Protocolo</t>
   </si>
@@ -340,7 +340,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -381,13 +381,6 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF747474"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -455,7 +448,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -534,9 +527,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -851,7 +841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J169"/>
+  <dimension ref="A1:J171"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -3807,7 +3797,7 @@
         <v>46020</v>
       </c>
       <c r="I90" s="21" t="str">
-        <f t="shared" ref="I90:I115" si="2">IF(H90&lt;=G90,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I90:I116" si="2">IF(H90&lt;=G90,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Fora do Prazo</v>
       </c>
       <c r="J90" s="2" t="s">
@@ -4575,10 +4565,15 @@
       <c r="G114" s="7">
         <v>46031</v>
       </c>
-      <c r="H114" s="9"/>
-      <c r="I114" s="15"/>
-      <c r="J114" s="22" t="s">
-        <v>94</v>
+      <c r="H114" s="7">
+        <v>46121</v>
+      </c>
+      <c r="I114" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -4636,10 +4631,15 @@
       <c r="G116" s="7">
         <v>46038</v>
       </c>
-      <c r="H116" s="9"/>
-      <c r="I116" s="15"/>
-      <c r="J116" s="22" t="s">
-        <v>94</v>
+      <c r="H116" s="7">
+        <v>46010</v>
+      </c>
+      <c r="I116" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -4696,7 +4696,7 @@
         <v>46062</v>
       </c>
       <c r="I118" s="21" t="str">
-        <f t="shared" ref="I118:I132" si="3">IF(H118&lt;=G118,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I118:I134" si="3">IF(H118&lt;=G118,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Fora do Prazo</v>
       </c>
       <c r="J118" s="2" t="s">
@@ -5007,10 +5007,15 @@
       <c r="G128" s="7">
         <v>46064</v>
       </c>
-      <c r="H128" s="10"/>
-      <c r="I128" s="15"/>
-      <c r="J128" s="22" t="s">
-        <v>94</v>
+      <c r="H128" s="8">
+        <v>46127</v>
+      </c>
+      <c r="I128" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
@@ -5195,10 +5200,15 @@
       <c r="G134" s="7">
         <v>46081</v>
       </c>
-      <c r="H134" s="10"/>
-      <c r="I134" s="15"/>
-      <c r="J134" s="22" t="s">
-        <v>94</v>
+      <c r="H134" s="8">
+        <v>46125</v>
+      </c>
+      <c r="I134" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -5373,10 +5383,15 @@
       <c r="G140" s="7">
         <v>46096</v>
       </c>
-      <c r="H140" s="9"/>
-      <c r="I140" s="15"/>
-      <c r="J140" s="22" t="s">
-        <v>94</v>
+      <c r="H140" s="7">
+        <v>46125</v>
+      </c>
+      <c r="I140" s="21" t="str">
+        <f t="shared" ref="I140" si="5">IF(H140&lt;=G140,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J140" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -5551,10 +5566,15 @@
       <c r="G146" s="7">
         <v>46103</v>
       </c>
-      <c r="H146" s="10"/>
-      <c r="I146" s="15"/>
-      <c r="J146" s="22" t="s">
-        <v>94</v>
+      <c r="H146" s="8">
+        <v>46125</v>
+      </c>
+      <c r="I146" s="13" t="str">
+        <f>IF(H146&lt;=G146,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -5761,7 +5781,7 @@
         <v>46091</v>
       </c>
       <c r="I153" s="13" t="str">
-        <f t="shared" ref="I153:I160" si="5">IF(H153&lt;=G153,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I153:I160" si="6">IF(H153&lt;=G153,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J153" s="4" t="s">
@@ -5794,7 +5814,7 @@
         <v>46104</v>
       </c>
       <c r="I154" s="13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J154" s="4" t="s">
@@ -5827,7 +5847,7 @@
         <v>46093</v>
       </c>
       <c r="I155" s="13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J155" s="3" t="s">
@@ -5860,7 +5880,7 @@
         <v>46099</v>
       </c>
       <c r="I156" s="13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J156" s="2" t="s">
@@ -5893,7 +5913,7 @@
         <v>46118</v>
       </c>
       <c r="I157" s="13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J157" s="2" t="s">
@@ -5926,7 +5946,7 @@
         <v>46113</v>
       </c>
       <c r="I158" s="13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J158" s="2" t="s">
@@ -5959,7 +5979,7 @@
         <v>46101</v>
       </c>
       <c r="I159" s="13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J159" s="2" t="s">
@@ -5992,7 +6012,7 @@
         <v>46101</v>
       </c>
       <c r="I160" s="13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J160" s="2" t="s">
@@ -6176,10 +6196,15 @@
       <c r="G166" s="6">
         <v>46141</v>
       </c>
-      <c r="H166" s="30"/>
-      <c r="I166" s="29"/>
+      <c r="H166" s="18">
+        <v>46119</v>
+      </c>
+      <c r="I166" s="13" t="str">
+        <f>IF(H166&lt;=G166,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J166" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
@@ -6232,10 +6257,15 @@
       <c r="G168" s="7">
         <v>46143</v>
       </c>
-      <c r="H168" s="17"/>
-      <c r="I168" s="15"/>
+      <c r="H168" s="18">
+        <v>46125</v>
+      </c>
+      <c r="I168" s="13" t="str">
+        <f>IF(H168&lt;=G168,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J168" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
@@ -6260,14 +6290,75 @@
       <c r="G169" s="7">
         <v>46149</v>
       </c>
-      <c r="H169" s="15"/>
-      <c r="I169" s="15"/>
+      <c r="H169" s="18">
+        <v>46121</v>
+      </c>
+      <c r="I169" s="13" t="str">
+        <f>IF(H169&lt;=G169,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J169" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A170" s="20">
+        <v>202604004000184</v>
+      </c>
+      <c r="B170" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C170" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D170" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E170" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F170" s="16">
+        <v>46122.668055555558</v>
+      </c>
+      <c r="G170" s="7">
+        <v>46152</v>
+      </c>
+      <c r="H170" s="17"/>
+      <c r="I170" s="15"/>
+      <c r="J170" s="2" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A171" s="20">
+        <v>202604007000185</v>
+      </c>
+      <c r="B171" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D171" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E171" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F171" s="16">
+        <v>46127.354166666664</v>
+      </c>
+      <c r="G171" s="7">
+        <v>46157</v>
+      </c>
+      <c r="H171" s="17"/>
+      <c r="I171" s="15"/>
+      <c r="J171" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J168" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
+  <autoFilter ref="A1:J169" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J159">
     <sortCondition ref="F1:F159"/>
   </sortState>

--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5A0F24-4739-4912-97A5-F4A980007B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BC586F-B907-4BF1-A607-6CC8AFF14FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Dash" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$171</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="105">
   <si>
     <t>Protocolo</t>
   </si>
@@ -334,6 +334,15 @@
   </si>
   <si>
     <t>Roçagem</t>
+  </si>
+  <si>
+    <t>Entulho</t>
+  </si>
+  <si>
+    <t>Habitação</t>
+  </si>
+  <si>
+    <t>Regularização fundiária</t>
   </si>
 </sst>
 </file>
@@ -841,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J171"/>
+  <dimension ref="A1:J177"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -3797,7 +3806,7 @@
         <v>46020</v>
       </c>
       <c r="I90" s="21" t="str">
-        <f t="shared" ref="I90:I116" si="2">IF(H90&lt;=G90,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I90:I117" si="2">IF(H90&lt;=G90,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Fora do Prazo</v>
       </c>
       <c r="J90" s="2" t="s">
@@ -4664,10 +4673,15 @@
       <c r="G117" s="6">
         <v>46040</v>
       </c>
-      <c r="H117" s="11"/>
-      <c r="I117" s="15"/>
-      <c r="J117" s="22" t="s">
-        <v>94</v>
+      <c r="H117" s="6">
+        <v>46135</v>
+      </c>
+      <c r="I117" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J117" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -4696,7 +4710,7 @@
         <v>46062</v>
       </c>
       <c r="I118" s="21" t="str">
-        <f t="shared" ref="I118:I134" si="3">IF(H118&lt;=G118,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I118:I135" si="3">IF(H118&lt;=G118,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Fora do Prazo</v>
       </c>
       <c r="J118" s="2" t="s">
@@ -5233,10 +5247,15 @@
       <c r="G135" s="6">
         <v>46088</v>
       </c>
-      <c r="H135" s="11"/>
-      <c r="I135" s="15"/>
-      <c r="J135" s="22" t="s">
-        <v>94</v>
+      <c r="H135" s="6">
+        <v>46135</v>
+      </c>
+      <c r="I135" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -6043,8 +6062,8 @@
       </c>
       <c r="H161" s="15"/>
       <c r="I161" s="15"/>
-      <c r="J161" s="2" t="s">
-        <v>15</v>
+      <c r="J161" s="22" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
@@ -6071,8 +6090,8 @@
       </c>
       <c r="H162" s="17"/>
       <c r="I162" s="15"/>
-      <c r="J162" s="2" t="s">
-        <v>15</v>
+      <c r="J162" s="22" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
@@ -6323,10 +6342,15 @@
       <c r="G170" s="7">
         <v>46152</v>
       </c>
-      <c r="H170" s="17"/>
-      <c r="I170" s="15"/>
+      <c r="H170" s="18">
+        <v>46127</v>
+      </c>
+      <c r="I170" s="13" t="str">
+        <f>IF(H170&lt;=G170,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J170" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
@@ -6357,8 +6381,186 @@
         <v>15</v>
       </c>
     </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A172" s="19">
+        <v>202604011000186</v>
+      </c>
+      <c r="B172" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C172" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D172" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E172" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F172" s="14">
+        <v>46128.45416666667</v>
+      </c>
+      <c r="G172" s="6">
+        <v>46158</v>
+      </c>
+      <c r="H172" s="15"/>
+      <c r="I172" s="15"/>
+      <c r="J172" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A173" s="20">
+        <v>202604013000187</v>
+      </c>
+      <c r="B173" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D173" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E173" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F173" s="16">
+        <v>46134.580555555556</v>
+      </c>
+      <c r="G173" s="7">
+        <v>46164</v>
+      </c>
+      <c r="H173" s="15"/>
+      <c r="I173" s="15"/>
+      <c r="J173" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A174" s="19">
+        <v>202604013000188</v>
+      </c>
+      <c r="B174" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D174" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E174" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F174" s="14">
+        <v>46134.617361111108</v>
+      </c>
+      <c r="G174" s="6">
+        <v>46164</v>
+      </c>
+      <c r="H174" s="15"/>
+      <c r="I174" s="15"/>
+      <c r="J174" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A175" s="20">
+        <v>202604011000189</v>
+      </c>
+      <c r="B175" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C175" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D175" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E175" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F175" s="16">
+        <v>46134.622916666667</v>
+      </c>
+      <c r="G175" s="7">
+        <v>46164</v>
+      </c>
+      <c r="H175" s="17"/>
+      <c r="I175" s="15"/>
+      <c r="J175" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A176" s="19">
+        <v>202604003000190</v>
+      </c>
+      <c r="B176" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C176" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D176" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E176" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F176" s="14">
+        <v>46134.887499999997</v>
+      </c>
+      <c r="G176" s="6">
+        <v>46164</v>
+      </c>
+      <c r="H176" s="18">
+        <v>46135</v>
+      </c>
+      <c r="I176" s="13" t="str">
+        <f>IF(H176&lt;=G176,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J176" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A177" s="20">
+        <v>202604012000191</v>
+      </c>
+      <c r="B177" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C177" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D177" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E177" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F177" s="16">
+        <v>46135.404166666667</v>
+      </c>
+      <c r="G177" s="7">
+        <v>46165</v>
+      </c>
+      <c r="H177" s="18">
+        <v>46135</v>
+      </c>
+      <c r="I177" s="13" t="str">
+        <f>IF(H177&lt;=G177,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J177" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J169" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
+  <autoFilter ref="A1:J171" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J159">
     <sortCondition ref="F1:F159"/>
   </sortState>

--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BC586F-B907-4BF1-A607-6CC8AFF14FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66FC86A-6C40-49CB-8C8C-0921104E7991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="107">
   <si>
     <t>Protocolo</t>
   </si>
@@ -343,6 +343,12 @@
   </si>
   <si>
     <t>Regularização fundiária</t>
+  </si>
+  <si>
+    <t>Perturbação do sossego</t>
+  </si>
+  <si>
+    <t>Assuntos diversos</t>
   </si>
 </sst>
 </file>
@@ -457,7 +463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -536,6 +542,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -850,7 +859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J177"/>
+  <dimension ref="A1:J180"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -6559,6 +6568,90 @@
         <v>19</v>
       </c>
     </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A178" s="20">
+        <v>202604007000192</v>
+      </c>
+      <c r="B178" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C178" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D178" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E178" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F178" s="16">
+        <v>46136.633333333331</v>
+      </c>
+      <c r="G178" s="7">
+        <v>46166</v>
+      </c>
+      <c r="H178" s="15"/>
+      <c r="I178" s="15"/>
+      <c r="J178" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A179" s="19">
+        <v>202604012000193</v>
+      </c>
+      <c r="B179" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D179" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E179" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F179" s="14">
+        <v>46139.677083333336</v>
+      </c>
+      <c r="G179" s="6">
+        <v>46169</v>
+      </c>
+      <c r="H179" s="30"/>
+      <c r="I179" s="15"/>
+      <c r="J179" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A180" s="20">
+        <v>202604007000194</v>
+      </c>
+      <c r="B180" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C180" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D180" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E180" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F180" s="16">
+        <v>46141.64166666667</v>
+      </c>
+      <c r="G180" s="7">
+        <v>46171</v>
+      </c>
+      <c r="H180" s="17"/>
+      <c r="I180" s="15"/>
+      <c r="J180" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J171" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J159">

--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66FC86A-6C40-49CB-8C8C-0921104E7991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E2BF9D-03EB-49AF-B01A-F7FF85256E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Dash" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$186</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="108">
   <si>
     <t>Protocolo</t>
   </si>
@@ -349,6 +349,9 @@
   </si>
   <si>
     <t>Assuntos diversos</t>
+  </si>
+  <si>
+    <t>Limpeza de Vias Públicas</t>
   </si>
 </sst>
 </file>
@@ -859,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J180"/>
+  <dimension ref="A1:J186"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -3066,7 +3069,7 @@
         <v>45959</v>
       </c>
       <c r="I67" s="21" t="str">
-        <f t="shared" ref="I67:I87" si="1">IF(H67&lt;=G67,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I67:I89" si="1">IF(H67&lt;=G67,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J67" s="2" t="s">
@@ -3755,10 +3758,15 @@
       <c r="G88" s="7">
         <v>46009</v>
       </c>
-      <c r="H88" s="10"/>
-      <c r="I88" s="15"/>
-      <c r="J88" s="22" t="s">
-        <v>94</v>
+      <c r="H88" s="8">
+        <v>46156</v>
+      </c>
+      <c r="I88" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -3783,10 +3791,15 @@
       <c r="G89" s="6">
         <v>46009</v>
       </c>
-      <c r="H89" s="11"/>
-      <c r="I89" s="15"/>
-      <c r="J89" s="22" t="s">
-        <v>94</v>
+      <c r="H89" s="6">
+        <v>46156</v>
+      </c>
+      <c r="I89" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -4042,10 +4055,15 @@
       <c r="G97" s="6">
         <v>46017</v>
       </c>
-      <c r="H97" s="10"/>
-      <c r="I97" s="15"/>
-      <c r="J97" s="22" t="s">
-        <v>94</v>
+      <c r="H97" s="8">
+        <v>46149</v>
+      </c>
+      <c r="I97" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -4329,10 +4347,15 @@
       <c r="G106" s="7">
         <v>46023</v>
       </c>
-      <c r="H106" s="9"/>
-      <c r="I106" s="15"/>
-      <c r="J106" s="22" t="s">
-        <v>94</v>
+      <c r="H106" s="7">
+        <v>46149</v>
+      </c>
+      <c r="I106" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -4390,10 +4413,15 @@
       <c r="G108" s="7">
         <v>46023</v>
       </c>
-      <c r="H108" s="9"/>
-      <c r="I108" s="15"/>
-      <c r="J108" s="22" t="s">
-        <v>94</v>
+      <c r="H108" s="7">
+        <v>46156</v>
+      </c>
+      <c r="I108" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -4847,10 +4875,15 @@
       <c r="G122" s="7">
         <v>46057</v>
       </c>
-      <c r="H122" s="10"/>
-      <c r="I122" s="15"/>
-      <c r="J122" s="22" t="s">
-        <v>94</v>
+      <c r="H122" s="8">
+        <v>46156</v>
+      </c>
+      <c r="I122" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -5195,10 +5228,15 @@
       <c r="G133" s="6">
         <v>46080</v>
       </c>
-      <c r="H133" s="10"/>
-      <c r="I133" s="15"/>
-      <c r="J133" s="22" t="s">
-        <v>94</v>
+      <c r="H133" s="8">
+        <v>46156</v>
+      </c>
+      <c r="I133" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -5566,10 +5604,15 @@
       <c r="G145" s="6">
         <v>46102</v>
       </c>
-      <c r="H145" s="11"/>
-      <c r="I145" s="15"/>
-      <c r="J145" s="22" t="s">
-        <v>94</v>
+      <c r="H145" s="6">
+        <v>46149</v>
+      </c>
+      <c r="I145" s="13" t="str">
+        <f>IF(H145&lt;=G145,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J145" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -5688,10 +5731,15 @@
       <c r="G149" s="12">
         <v>46107</v>
       </c>
-      <c r="H149" s="12"/>
-      <c r="I149" s="13"/>
-      <c r="J149" s="22" t="s">
-        <v>94</v>
+      <c r="H149" s="12">
+        <v>46156</v>
+      </c>
+      <c r="I149" s="13" t="str">
+        <f>IF(H149&lt;=G149,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J149" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -5749,10 +5797,15 @@
       <c r="G151" s="12">
         <v>46107</v>
       </c>
-      <c r="H151" s="12"/>
-      <c r="I151" s="13"/>
-      <c r="J151" s="22" t="s">
-        <v>94</v>
+      <c r="H151" s="12">
+        <v>46149</v>
+      </c>
+      <c r="I151" s="13" t="str">
+        <f>IF(H151&lt;=G151,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J151" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -5809,7 +5862,7 @@
         <v>46091</v>
       </c>
       <c r="I153" s="13" t="str">
-        <f t="shared" ref="I153:I160" si="6">IF(H153&lt;=G153,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I153:I161" si="6">IF(H153&lt;=G153,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J153" s="4" t="s">
@@ -6069,10 +6122,15 @@
       <c r="G161" s="6">
         <v>46132</v>
       </c>
-      <c r="H161" s="15"/>
-      <c r="I161" s="15"/>
-      <c r="J161" s="22" t="s">
-        <v>94</v>
+      <c r="H161" s="13">
+        <v>46149</v>
+      </c>
+      <c r="I161" s="13" t="str">
+        <f t="shared" si="6"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J161" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
@@ -6259,8 +6317,8 @@
       </c>
       <c r="H167" s="29"/>
       <c r="I167" s="29"/>
-      <c r="J167" s="2" t="s">
-        <v>15</v>
+      <c r="J167" s="22" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
@@ -6646,14 +6704,202 @@
       <c r="G180" s="7">
         <v>46171</v>
       </c>
-      <c r="H180" s="17"/>
-      <c r="I180" s="15"/>
+      <c r="H180" s="18">
+        <v>46150</v>
+      </c>
+      <c r="I180" s="13" t="str">
+        <f>IF(H180&lt;=G180,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J180" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A181" s="19">
+        <v>202605015000195</v>
+      </c>
+      <c r="B181" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C181" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D181" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E181" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F181" s="14">
+        <v>46148.702777777777</v>
+      </c>
+      <c r="G181" s="6">
+        <v>46178</v>
+      </c>
+      <c r="H181" s="18">
+        <v>46148</v>
+      </c>
+      <c r="I181" s="13" t="str">
+        <f>IF(H181&lt;=G181,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J181" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A182" s="20">
+        <v>202605007000196</v>
+      </c>
+      <c r="B182" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C182" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D182" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E182" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F182" s="16">
+        <v>46149.384027777778</v>
+      </c>
+      <c r="G182" s="7">
+        <v>46179</v>
+      </c>
+      <c r="H182" s="18">
+        <v>46150</v>
+      </c>
+      <c r="I182" s="13" t="str">
+        <f>IF(H182&lt;=G182,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J182" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A183" s="19">
+        <v>202605007000197</v>
+      </c>
+      <c r="B183" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C183" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D183" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E183" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F183" s="14">
+        <v>46149.470833333333</v>
+      </c>
+      <c r="G183" s="6">
+        <v>46179</v>
+      </c>
+      <c r="H183" s="15"/>
+      <c r="I183" s="15"/>
+      <c r="J183" s="2" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A184" s="20">
+        <v>202605001000198</v>
+      </c>
+      <c r="B184" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C184" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D184" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E184" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F184" s="16">
+        <v>46149.476388888892</v>
+      </c>
+      <c r="G184" s="7">
+        <v>46179</v>
+      </c>
+      <c r="H184" s="15"/>
+      <c r="I184" s="15"/>
+      <c r="J184" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A185" s="19">
+        <v>202605007000199</v>
+      </c>
+      <c r="B185" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D185" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E185" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F185" s="14">
+        <v>46149.479861111111</v>
+      </c>
+      <c r="G185" s="6">
+        <v>46179</v>
+      </c>
+      <c r="H185" s="18">
+        <v>46150</v>
+      </c>
+      <c r="I185" s="13" t="str">
+        <f>IF(H185&lt;=G185,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J185" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A186" s="20">
+        <v>202605013000200</v>
+      </c>
+      <c r="B186" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C186" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D186" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E186" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F186" s="16">
+        <v>46150.495138888888</v>
+      </c>
+      <c r="G186" s="7">
+        <v>46180</v>
+      </c>
+      <c r="H186" s="15"/>
+      <c r="I186" s="15"/>
+      <c r="J186" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J171" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
+  <autoFilter ref="A1:J186" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J159">
     <sortCondition ref="F1:F159"/>
   </sortState>

--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E2BF9D-03EB-49AF-B01A-F7FF85256E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED1F91B-2105-4275-8B98-658D58D62A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Dash" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$190</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="108">
   <si>
     <t>Protocolo</t>
   </si>
@@ -466,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -492,9 +492,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -544,7 +541,6 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -862,7 +858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J186"/>
+  <dimension ref="A1:J190"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -909,7 +905,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="20">
+      <c r="A2" s="19">
         <v>202509001000009</v>
       </c>
       <c r="B2" s="9" t="s">
@@ -924,7 +920,7 @@
       <c r="E2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="15">
         <v>45915.636805555558</v>
       </c>
       <c r="G2" s="7">
@@ -933,7 +929,7 @@
       <c r="H2" s="7">
         <v>45931</v>
       </c>
-      <c r="I2" s="13" t="str">
+      <c r="I2" s="12" t="str">
         <f>IF(H2&lt;=G2,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
@@ -942,22 +938,22 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="19">
+      <c r="A3" s="18">
         <v>202509002000010</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="13">
         <v>45915.672222222223</v>
       </c>
       <c r="G3" s="6">
@@ -966,7 +962,7 @@
       <c r="H3" s="6">
         <v>45915</v>
       </c>
-      <c r="I3" s="13" t="str">
+      <c r="I3" s="12" t="str">
         <f t="shared" ref="I3:I66" si="0">IF(H3&lt;=G3,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
@@ -975,7 +971,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="20">
+      <c r="A4" s="19">
         <v>202509001000011</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -990,7 +986,7 @@
       <c r="E4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="15">
         <v>45916.34652777778</v>
       </c>
       <c r="G4" s="7">
@@ -999,7 +995,7 @@
       <c r="H4" s="7">
         <v>45931</v>
       </c>
-      <c r="I4" s="13" t="str">
+      <c r="I4" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1008,22 +1004,22 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="19">
+      <c r="A5" s="18">
         <v>202509001000012</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="11" t="s">
+      <c r="B5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="13">
         <v>45916.697916666664</v>
       </c>
       <c r="G5" s="6">
@@ -1032,7 +1028,7 @@
       <c r="H5" s="6">
         <v>45937</v>
       </c>
-      <c r="I5" s="13" t="str">
+      <c r="I5" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1041,7 +1037,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
+      <c r="A6" s="19">
         <v>202509011000013</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -1056,7 +1052,7 @@
       <c r="E6" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="15">
         <v>45917.379166666666</v>
       </c>
       <c r="G6" s="7">
@@ -1065,7 +1061,7 @@
       <c r="H6" s="7">
         <v>45943</v>
       </c>
-      <c r="I6" s="13" t="str">
+      <c r="I6" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1074,22 +1070,22 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="19">
+      <c r="A7" s="18">
         <v>202509011000014</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="13">
         <v>45917.64166666667</v>
       </c>
       <c r="G7" s="6">
@@ -1098,7 +1094,7 @@
       <c r="H7" s="6">
         <v>45939</v>
       </c>
-      <c r="I7" s="13" t="str">
+      <c r="I7" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1107,7 +1103,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="20">
+      <c r="A8" s="19">
         <v>202509001000015</v>
       </c>
       <c r="B8" s="9" t="s">
@@ -1122,7 +1118,7 @@
       <c r="E8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <v>45918.415277777778</v>
       </c>
       <c r="G8" s="7">
@@ -1131,7 +1127,7 @@
       <c r="H8" s="8">
         <v>45929</v>
       </c>
-      <c r="I8" s="13" t="str">
+      <c r="I8" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1140,22 +1136,22 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="19">
+      <c r="A9" s="18">
         <v>202509009000016</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="B9" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="13">
         <v>45919.35833333333</v>
       </c>
       <c r="G9" s="6">
@@ -1164,7 +1160,7 @@
       <c r="H9" s="6">
         <v>45919</v>
       </c>
-      <c r="I9" s="13" t="str">
+      <c r="I9" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1173,7 +1169,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="20">
+      <c r="A10" s="19">
         <v>202509001000017</v>
       </c>
       <c r="B10" s="9" t="s">
@@ -1188,7 +1184,7 @@
       <c r="E10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <v>45919.45</v>
       </c>
       <c r="G10" s="7">
@@ -1197,7 +1193,7 @@
       <c r="H10" s="7">
         <v>45933</v>
       </c>
-      <c r="I10" s="13" t="str">
+      <c r="I10" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1206,22 +1202,22 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="19">
+      <c r="A11" s="18">
         <v>202509003000018</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="11" t="s">
+      <c r="B11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="13">
         <v>45919.522222222222</v>
       </c>
       <c r="G11" s="6">
@@ -1230,7 +1226,7 @@
       <c r="H11" s="6">
         <v>45958</v>
       </c>
-      <c r="I11" s="13" t="str">
+      <c r="I11" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Fora do Prazo</v>
       </c>
@@ -1239,7 +1235,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="20">
+      <c r="A12" s="19">
         <v>202509011000019</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -1254,7 +1250,7 @@
       <c r="E12" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <v>45922.386805555558</v>
       </c>
       <c r="G12" s="7">
@@ -1263,7 +1259,7 @@
       <c r="H12" s="8">
         <v>46094</v>
       </c>
-      <c r="I12" s="13" t="str">
+      <c r="I12" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Fora do Prazo</v>
       </c>
@@ -1272,22 +1268,22 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="19">
+      <c r="A13" s="18">
         <v>202509011000020</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="13">
         <v>45923.649305555555</v>
       </c>
       <c r="G13" s="6">
@@ -1296,7 +1292,7 @@
       <c r="H13" s="6">
         <v>45968</v>
       </c>
-      <c r="I13" s="13" t="str">
+      <c r="I13" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Fora do Prazo</v>
       </c>
@@ -1305,7 +1301,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="20">
+      <c r="A14" s="19">
         <v>202509007000021</v>
       </c>
       <c r="B14" s="9" t="s">
@@ -1320,7 +1316,7 @@
       <c r="E14" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>45924.336111111108</v>
       </c>
       <c r="G14" s="7">
@@ -1329,7 +1325,7 @@
       <c r="H14" s="7">
         <v>45924</v>
       </c>
-      <c r="I14" s="21" t="str">
+      <c r="I14" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1338,22 +1334,22 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="19">
+      <c r="A15" s="18">
         <v>202509004000022</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="11" t="s">
+      <c r="B15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="13">
         <v>45924.671527777777</v>
       </c>
       <c r="G15" s="6">
@@ -1362,7 +1358,7 @@
       <c r="H15" s="8">
         <v>45924</v>
       </c>
-      <c r="I15" s="21" t="str">
+      <c r="I15" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1371,7 +1367,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="20">
+      <c r="A16" s="19">
         <v>202509001000023</v>
       </c>
       <c r="B16" s="9" t="s">
@@ -1386,7 +1382,7 @@
       <c r="E16" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="15">
         <v>45924.688888888886</v>
       </c>
       <c r="G16" s="7">
@@ -1395,7 +1391,7 @@
       <c r="H16" s="8">
         <v>45924</v>
       </c>
-      <c r="I16" s="21" t="str">
+      <c r="I16" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1404,22 +1400,22 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="19">
+      <c r="A17" s="18">
         <v>202509011000024</v>
       </c>
-      <c r="B17" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="11" t="s">
+      <c r="B17" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="13">
         <v>45925.611111111109</v>
       </c>
       <c r="G17" s="6">
@@ -1428,7 +1424,7 @@
       <c r="H17" s="6">
         <v>45968</v>
       </c>
-      <c r="I17" s="21" t="str">
+      <c r="I17" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Fora do Prazo</v>
       </c>
@@ -1437,7 +1433,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="20">
+      <c r="A18" s="19">
         <v>202509011000025</v>
       </c>
       <c r="B18" s="9" t="s">
@@ -1452,7 +1448,7 @@
       <c r="E18" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="15">
         <v>45930.364583333336</v>
       </c>
       <c r="G18" s="7">
@@ -1461,7 +1457,7 @@
       <c r="H18" s="7">
         <v>45930</v>
       </c>
-      <c r="I18" s="21" t="str">
+      <c r="I18" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1470,22 +1466,22 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="19">
+      <c r="A19" s="18">
         <v>202509015000026</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="11" t="s">
+      <c r="B19" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="13">
         <v>45930.580555555556</v>
       </c>
       <c r="G19" s="6">
@@ -1494,7 +1490,7 @@
       <c r="H19" s="6">
         <v>45930</v>
       </c>
-      <c r="I19" s="21" t="str">
+      <c r="I19" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1503,7 +1499,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="20">
+      <c r="A20" s="19">
         <v>202509001000027</v>
       </c>
       <c r="B20" s="9" t="s">
@@ -1518,7 +1514,7 @@
       <c r="E20" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="15">
         <v>45930.686111111114</v>
       </c>
       <c r="G20" s="7">
@@ -1527,7 +1523,7 @@
       <c r="H20" s="7">
         <v>45937</v>
       </c>
-      <c r="I20" s="21" t="str">
+      <c r="I20" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1536,22 +1532,22 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="19">
+      <c r="A21" s="18">
         <v>202510011000028</v>
       </c>
-      <c r="B21" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="11" t="s">
+      <c r="B21" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="13">
         <v>45931.661805555559</v>
       </c>
       <c r="G21" s="6">
@@ -1560,7 +1556,7 @@
       <c r="H21" s="6">
         <v>45939</v>
       </c>
-      <c r="I21" s="21" t="str">
+      <c r="I21" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1569,7 +1565,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="20">
+      <c r="A22" s="19">
         <v>202510009000029</v>
       </c>
       <c r="B22" s="9" t="s">
@@ -1584,7 +1580,7 @@
       <c r="E22" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="15">
         <v>45932.51458333333</v>
       </c>
       <c r="G22" s="7">
@@ -1593,7 +1589,7 @@
       <c r="H22" s="8">
         <v>45964</v>
       </c>
-      <c r="I22" s="21" t="str">
+      <c r="I22" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Fora do Prazo</v>
       </c>
@@ -1602,22 +1598,22 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="19">
+      <c r="A23" s="18">
         <v>202510001000030</v>
       </c>
-      <c r="B23" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="11" t="s">
+      <c r="B23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="13">
         <v>45932.663888888892</v>
       </c>
       <c r="G23" s="6">
@@ -1626,7 +1622,7 @@
       <c r="H23" s="8">
         <v>45958</v>
       </c>
-      <c r="I23" s="21" t="str">
+      <c r="I23" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1635,7 +1631,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="20">
+      <c r="A24" s="19">
         <v>202510001000031</v>
       </c>
       <c r="B24" s="9" t="s">
@@ -1650,7 +1646,7 @@
       <c r="E24" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="15">
         <v>45932.667361111111</v>
       </c>
       <c r="G24" s="7">
@@ -1659,7 +1655,7 @@
       <c r="H24" s="8">
         <v>45958</v>
       </c>
-      <c r="I24" s="21" t="str">
+      <c r="I24" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1668,22 +1664,22 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="19">
+      <c r="A25" s="18">
         <v>202510001000032</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="13">
         <v>45932.693749999999</v>
       </c>
       <c r="G25" s="6">
@@ -1692,7 +1688,7 @@
       <c r="H25" s="6">
         <v>45938</v>
       </c>
-      <c r="I25" s="21" t="str">
+      <c r="I25" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1701,7 +1697,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="20">
+      <c r="A26" s="19">
         <v>202510001000033</v>
       </c>
       <c r="B26" s="9" t="s">
@@ -1716,7 +1712,7 @@
       <c r="E26" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="15">
         <v>45933.671527777777</v>
       </c>
       <c r="G26" s="7">
@@ -1725,7 +1721,7 @@
       <c r="H26" s="7">
         <v>45933</v>
       </c>
-      <c r="I26" s="21" t="str">
+      <c r="I26" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1734,22 +1730,22 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="19">
+      <c r="A27" s="18">
         <v>202510007000034</v>
       </c>
-      <c r="B27" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="11" t="s">
+      <c r="B27" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="13">
         <v>45937.351388888892</v>
       </c>
       <c r="G27" s="6">
@@ -1758,7 +1754,7 @@
       <c r="H27" s="8">
         <v>45937</v>
       </c>
-      <c r="I27" s="21" t="str">
+      <c r="I27" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1767,7 +1763,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="20">
+      <c r="A28" s="19">
         <v>202510001000035</v>
       </c>
       <c r="B28" s="9" t="s">
@@ -1782,7 +1778,7 @@
       <c r="E28" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="15">
         <v>45937.370833333334</v>
       </c>
       <c r="G28" s="7">
@@ -1791,7 +1787,7 @@
       <c r="H28" s="7">
         <v>45937</v>
       </c>
-      <c r="I28" s="21" t="str">
+      <c r="I28" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1800,22 +1796,22 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="19">
+      <c r="A29" s="18">
         <v>202510015000036</v>
       </c>
-      <c r="B29" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="11" t="s">
+      <c r="B29" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="13">
         <v>45937.414583333331</v>
       </c>
       <c r="G29" s="6">
@@ -1824,7 +1820,7 @@
       <c r="H29" s="6">
         <v>45965</v>
       </c>
-      <c r="I29" s="21" t="str">
+      <c r="I29" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1833,7 +1829,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="20">
+      <c r="A30" s="19">
         <v>202510011000037</v>
       </c>
       <c r="B30" s="9" t="s">
@@ -1848,35 +1844,40 @@
       <c r="E30" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="15">
         <v>45937.469444444447</v>
       </c>
       <c r="G30" s="7">
         <v>45967</v>
       </c>
-      <c r="H30" s="9"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="22" t="s">
-        <v>94</v>
+      <c r="H30" s="7">
+        <v>46155</v>
+      </c>
+      <c r="I30" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="19">
+      <c r="A31" s="18">
         <v>202510003000038</v>
       </c>
-      <c r="B31" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" s="11" t="s">
+      <c r="B31" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="13">
         <v>45937.5</v>
       </c>
       <c r="G31" s="6">
@@ -1885,7 +1886,7 @@
       <c r="H31" s="8">
         <v>45960</v>
       </c>
-      <c r="I31" s="21" t="str">
+      <c r="I31" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1894,7 +1895,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="20">
+      <c r="A32" s="19">
         <v>202510011000039</v>
       </c>
       <c r="B32" s="9" t="s">
@@ -1909,7 +1910,7 @@
       <c r="E32" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="15">
         <v>45937.508333333331</v>
       </c>
       <c r="G32" s="7">
@@ -1918,7 +1919,7 @@
       <c r="H32" s="8">
         <v>45953</v>
       </c>
-      <c r="I32" s="21" t="str">
+      <c r="I32" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1927,22 +1928,22 @@
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="19">
+      <c r="A33" s="18">
         <v>202510004000040</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="13">
         <v>45937.513194444444</v>
       </c>
       <c r="G33" s="6">
@@ -1951,7 +1952,7 @@
       <c r="H33" s="8">
         <v>45937</v>
       </c>
-      <c r="I33" s="21" t="str">
+      <c r="I33" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1960,7 +1961,7 @@
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="20">
+      <c r="A34" s="19">
         <v>202510008000041</v>
       </c>
       <c r="B34" s="9" t="s">
@@ -1975,7 +1976,7 @@
       <c r="E34" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="15">
         <v>45938.362500000003</v>
       </c>
       <c r="G34" s="7">
@@ -1984,7 +1985,7 @@
       <c r="H34" s="8">
         <v>45938</v>
       </c>
-      <c r="I34" s="21" t="str">
+      <c r="I34" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1993,22 +1994,22 @@
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="19">
+      <c r="A35" s="18">
         <v>202510009000042</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" s="11" t="s">
+      <c r="B35" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="13">
         <v>45938.427083333336</v>
       </c>
       <c r="G35" s="6">
@@ -2017,7 +2018,7 @@
       <c r="H35" s="6">
         <v>45960</v>
       </c>
-      <c r="I35" s="21" t="str">
+      <c r="I35" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2026,7 +2027,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="20">
+      <c r="A36" s="19">
         <v>202510011000043</v>
       </c>
       <c r="B36" s="9" t="s">
@@ -2041,35 +2042,40 @@
       <c r="E36" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="15">
         <v>45938.615972222222</v>
       </c>
       <c r="G36" s="7">
         <v>45968</v>
       </c>
-      <c r="H36" s="9"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="22" t="s">
-        <v>94</v>
+      <c r="H36" s="7">
+        <v>46155</v>
+      </c>
+      <c r="I36" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="19">
+      <c r="A37" s="18">
         <v>202510004000044</v>
       </c>
-      <c r="B37" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" s="11" t="s">
+      <c r="B37" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="13">
         <v>45939.629861111112</v>
       </c>
       <c r="G37" s="6">
@@ -2078,7 +2084,7 @@
       <c r="H37" s="8">
         <v>45939</v>
       </c>
-      <c r="I37" s="21" t="str">
+      <c r="I37" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2087,7 +2093,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="20">
+      <c r="A38" s="19">
         <v>202510001000045</v>
       </c>
       <c r="B38" s="9" t="s">
@@ -2102,7 +2108,7 @@
       <c r="E38" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="15">
         <v>45940.345833333333</v>
       </c>
       <c r="G38" s="7">
@@ -2111,7 +2117,7 @@
       <c r="H38" s="7">
         <v>45943</v>
       </c>
-      <c r="I38" s="21" t="str">
+      <c r="I38" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2120,22 +2126,22 @@
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="19">
+      <c r="A39" s="18">
         <v>202510011000046</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E39" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="13">
         <v>45940.353472222225</v>
       </c>
       <c r="G39" s="6">
@@ -2144,7 +2150,7 @@
       <c r="H39" s="8">
         <v>45943</v>
       </c>
-      <c r="I39" s="21" t="str">
+      <c r="I39" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2153,7 +2159,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="20">
+      <c r="A40" s="19">
         <v>202510004000047</v>
       </c>
       <c r="B40" s="9" t="s">
@@ -2168,7 +2174,7 @@
       <c r="E40" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="15">
         <v>45940.359027777777</v>
       </c>
       <c r="G40" s="7">
@@ -2177,7 +2183,7 @@
       <c r="H40" s="7">
         <v>45943</v>
       </c>
-      <c r="I40" s="21" t="str">
+      <c r="I40" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2186,22 +2192,22 @@
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="19">
+      <c r="A41" s="18">
         <v>202510001000048</v>
       </c>
-      <c r="B41" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" s="11" t="s">
+      <c r="B41" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F41" s="14">
+      <c r="F41" s="13">
         <v>45940.463888888888</v>
       </c>
       <c r="G41" s="6">
@@ -2210,7 +2216,7 @@
       <c r="H41" s="6">
         <v>45940</v>
       </c>
-      <c r="I41" s="21" t="str">
+      <c r="I41" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2219,7 +2225,7 @@
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="20">
+      <c r="A42" s="19">
         <v>202510007000049</v>
       </c>
       <c r="B42" s="9" t="s">
@@ -2234,7 +2240,7 @@
       <c r="E42" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="15">
         <v>45940.499305555553</v>
       </c>
       <c r="G42" s="7">
@@ -2243,7 +2249,7 @@
       <c r="H42" s="7">
         <v>45943</v>
       </c>
-      <c r="I42" s="21" t="str">
+      <c r="I42" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2252,22 +2258,22 @@
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="19">
+      <c r="A43" s="18">
         <v>202510001000050</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D43" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E43" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F43" s="14">
+      <c r="F43" s="13">
         <v>45943.44027777778</v>
       </c>
       <c r="G43" s="6">
@@ -2276,7 +2282,7 @@
       <c r="H43" s="6">
         <v>45996</v>
       </c>
-      <c r="I43" s="21" t="str">
+      <c r="I43" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Fora do Prazo</v>
       </c>
@@ -2285,7 +2291,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="20">
+      <c r="A44" s="19">
         <v>202510001000051</v>
       </c>
       <c r="B44" s="9" t="s">
@@ -2300,7 +2306,7 @@
       <c r="E44" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="15">
         <v>45944.65347222222</v>
       </c>
       <c r="G44" s="7">
@@ -2309,7 +2315,7 @@
       <c r="H44" s="7">
         <v>45944</v>
       </c>
-      <c r="I44" s="21" t="str">
+      <c r="I44" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2318,22 +2324,22 @@
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="19">
+      <c r="A45" s="18">
         <v>202510001000052</v>
       </c>
-      <c r="B45" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" s="11" t="s">
+      <c r="B45" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D45" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E45" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F45" s="14">
+      <c r="F45" s="13">
         <v>45945.604166666664</v>
       </c>
       <c r="G45" s="6">
@@ -2342,7 +2348,7 @@
       <c r="H45" s="8">
         <v>45960</v>
       </c>
-      <c r="I45" s="21" t="str">
+      <c r="I45" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2351,7 +2357,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="20">
+      <c r="A46" s="19">
         <v>202510001000053</v>
       </c>
       <c r="B46" s="9" t="s">
@@ -2366,7 +2372,7 @@
       <c r="E46" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F46" s="16">
+      <c r="F46" s="15">
         <v>45945.618055555555</v>
       </c>
       <c r="G46" s="7">
@@ -2375,7 +2381,7 @@
       <c r="H46" s="8">
         <v>45961</v>
       </c>
-      <c r="I46" s="21" t="str">
+      <c r="I46" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2384,22 +2390,22 @@
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="19">
+      <c r="A47" s="18">
         <v>202510007000054</v>
       </c>
-      <c r="B47" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" s="11" t="s">
+      <c r="B47" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E47" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F47" s="14">
+      <c r="F47" s="13">
         <v>45945.644444444442</v>
       </c>
       <c r="G47" s="6">
@@ -2408,7 +2414,7 @@
       <c r="H47" s="8">
         <v>45953</v>
       </c>
-      <c r="I47" s="21" t="str">
+      <c r="I47" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2417,7 +2423,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="20">
+      <c r="A48" s="19">
         <v>202510015000055</v>
       </c>
       <c r="B48" s="9" t="s">
@@ -2432,7 +2438,7 @@
       <c r="E48" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F48" s="16">
+      <c r="F48" s="15">
         <v>45945.699305555558</v>
       </c>
       <c r="G48" s="7">
@@ -2441,7 +2447,7 @@
       <c r="H48" s="8">
         <v>45953</v>
       </c>
-      <c r="I48" s="21" t="str">
+      <c r="I48" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2450,22 +2456,22 @@
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="19">
+      <c r="A49" s="18">
         <v>202510011000056</v>
       </c>
-      <c r="B49" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" s="11" t="s">
+      <c r="B49" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E49" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F49" s="14">
+      <c r="F49" s="13">
         <v>45946.624305555553</v>
       </c>
       <c r="G49" s="6">
@@ -2474,7 +2480,7 @@
       <c r="H49" s="6">
         <v>45986</v>
       </c>
-      <c r="I49" s="21" t="str">
+      <c r="I49" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Fora do Prazo</v>
       </c>
@@ -2483,7 +2489,7 @@
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="20">
+      <c r="A50" s="19">
         <v>202510009000057</v>
       </c>
       <c r="B50" s="9" t="s">
@@ -2498,7 +2504,7 @@
       <c r="E50" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F50" s="16">
+      <c r="F50" s="15">
         <v>45947.603472222225</v>
       </c>
       <c r="G50" s="7">
@@ -2507,7 +2513,7 @@
       <c r="H50" s="8">
         <v>45953</v>
       </c>
-      <c r="I50" s="21" t="str">
+      <c r="I50" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2516,22 +2522,22 @@
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="19">
+      <c r="A51" s="18">
         <v>202510004000058</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E51" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F51" s="14">
+      <c r="F51" s="13">
         <v>45947.694444444445</v>
       </c>
       <c r="G51" s="6">
@@ -2540,7 +2546,7 @@
       <c r="H51" s="6">
         <v>45951</v>
       </c>
-      <c r="I51" s="21" t="str">
+      <c r="I51" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2549,7 +2555,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="20">
+      <c r="A52" s="19">
         <v>202510001000059</v>
       </c>
       <c r="B52" s="9" t="s">
@@ -2564,7 +2570,7 @@
       <c r="E52" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F52" s="16">
+      <c r="F52" s="15">
         <v>45950.616666666669</v>
       </c>
       <c r="G52" s="7">
@@ -2573,7 +2579,7 @@
       <c r="H52" s="7">
         <v>45972</v>
       </c>
-      <c r="I52" s="21" t="str">
+      <c r="I52" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2582,22 +2588,22 @@
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="19">
+      <c r="A53" s="18">
         <v>202510001000060</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E53" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F53" s="14">
+      <c r="F53" s="13">
         <v>45950.708333333336</v>
       </c>
       <c r="G53" s="6">
@@ -2606,7 +2612,7 @@
       <c r="H53" s="6">
         <v>45996</v>
       </c>
-      <c r="I53" s="21" t="str">
+      <c r="I53" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Fora do Prazo</v>
       </c>
@@ -2615,7 +2621,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="20">
+      <c r="A54" s="19">
         <v>202510001000061</v>
       </c>
       <c r="B54" s="9" t="s">
@@ -2630,7 +2636,7 @@
       <c r="E54" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F54" s="16">
+      <c r="F54" s="15">
         <v>45952.500694444447</v>
       </c>
       <c r="G54" s="7">
@@ -2639,7 +2645,7 @@
       <c r="H54" s="7">
         <v>45974</v>
       </c>
-      <c r="I54" s="21" t="str">
+      <c r="I54" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2648,22 +2654,22 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="19">
+      <c r="A55" s="18">
         <v>202510011000062</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E55" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F55" s="14">
+      <c r="F55" s="13">
         <v>45953.380555555559</v>
       </c>
       <c r="G55" s="6">
@@ -2672,7 +2678,7 @@
       <c r="H55" s="6">
         <v>45953</v>
       </c>
-      <c r="I55" s="21" t="str">
+      <c r="I55" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2681,7 +2687,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="20">
+      <c r="A56" s="19">
         <v>202510009000063</v>
       </c>
       <c r="B56" s="9" t="s">
@@ -2696,7 +2702,7 @@
       <c r="E56" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F56" s="16">
+      <c r="F56" s="15">
         <v>45953.43472222222</v>
       </c>
       <c r="G56" s="7">
@@ -2705,7 +2711,7 @@
       <c r="H56" s="7">
         <v>45954</v>
       </c>
-      <c r="I56" s="21" t="str">
+      <c r="I56" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2714,22 +2720,22 @@
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="19">
+      <c r="A57" s="18">
         <v>202510004000064</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D57" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E57" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F57" s="14">
+      <c r="F57" s="13">
         <v>45953.693055555559</v>
       </c>
       <c r="G57" s="6">
@@ -2738,7 +2744,7 @@
       <c r="H57" s="6">
         <v>45975</v>
       </c>
-      <c r="I57" s="21" t="str">
+      <c r="I57" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2747,7 +2753,7 @@
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="20">
+      <c r="A58" s="19">
         <v>202510009000065</v>
       </c>
       <c r="B58" s="9" t="s">
@@ -2762,7 +2768,7 @@
       <c r="E58" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F58" s="16">
+      <c r="F58" s="15">
         <v>45954.374305555553</v>
       </c>
       <c r="G58" s="7">
@@ -2771,7 +2777,7 @@
       <c r="H58" s="7">
         <v>45972</v>
       </c>
-      <c r="I58" s="21" t="str">
+      <c r="I58" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2780,22 +2786,22 @@
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="19">
+      <c r="A59" s="18">
         <v>202510001000066</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D59" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E59" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F59" s="14">
+      <c r="F59" s="13">
         <v>45954.409722222219</v>
       </c>
       <c r="G59" s="6">
@@ -2804,7 +2810,7 @@
       <c r="H59" s="8">
         <v>45966</v>
       </c>
-      <c r="I59" s="21" t="str">
+      <c r="I59" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2813,7 +2819,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="20">
+      <c r="A60" s="19">
         <v>202510008000067</v>
       </c>
       <c r="B60" s="9" t="s">
@@ -2828,7 +2834,7 @@
       <c r="E60" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F60" s="16">
+      <c r="F60" s="15">
         <v>45954.411111111112</v>
       </c>
       <c r="G60" s="7">
@@ -2837,7 +2843,7 @@
       <c r="H60" s="7">
         <v>45966</v>
       </c>
-      <c r="I60" s="21" t="str">
+      <c r="I60" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2846,22 +2852,22 @@
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="19">
+      <c r="A61" s="18">
         <v>202510001000068</v>
       </c>
-      <c r="B61" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" s="11" t="s">
+      <c r="B61" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D61" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E61" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F61" s="14">
+      <c r="F61" s="13">
         <v>45956.820138888892</v>
       </c>
       <c r="G61" s="6">
@@ -2870,7 +2876,7 @@
       <c r="H61" s="6">
         <v>45974</v>
       </c>
-      <c r="I61" s="21" t="str">
+      <c r="I61" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2879,7 +2885,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="20">
+      <c r="A62" s="19">
         <v>202510001000069</v>
       </c>
       <c r="B62" s="9" t="s">
@@ -2894,7 +2900,7 @@
       <c r="E62" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F62" s="16">
+      <c r="F62" s="15">
         <v>45957.559027777781</v>
       </c>
       <c r="G62" s="7">
@@ -2903,7 +2909,7 @@
       <c r="H62" s="7">
         <v>45958</v>
       </c>
-      <c r="I62" s="21" t="str">
+      <c r="I62" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2912,22 +2918,22 @@
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="19">
+      <c r="A63" s="18">
         <v>202510007000070</v>
       </c>
-      <c r="B63" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" s="11" t="s">
+      <c r="B63" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D63" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E63" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F63" s="14">
+      <c r="F63" s="13">
         <v>45958.375694444447</v>
       </c>
       <c r="G63" s="6">
@@ -2936,7 +2942,7 @@
       <c r="H63" s="6">
         <v>45958</v>
       </c>
-      <c r="I63" s="21" t="str">
+      <c r="I63" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2945,7 +2951,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="20">
+      <c r="A64" s="19">
         <v>202510004000071</v>
       </c>
       <c r="B64" s="9" t="s">
@@ -2960,7 +2966,7 @@
       <c r="E64" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F64" s="16">
+      <c r="F64" s="15">
         <v>45958.496527777781</v>
       </c>
       <c r="G64" s="7">
@@ -2969,7 +2975,7 @@
       <c r="H64" s="8">
         <v>45960</v>
       </c>
-      <c r="I64" s="21" t="str">
+      <c r="I64" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2978,22 +2984,22 @@
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="19">
+      <c r="A65" s="18">
         <v>202510011000072</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D65" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E65" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F65" s="14">
+      <c r="F65" s="13">
         <v>45959.40347222222</v>
       </c>
       <c r="G65" s="6">
@@ -3002,7 +3008,7 @@
       <c r="H65" s="8">
         <v>45994</v>
       </c>
-      <c r="I65" s="21" t="str">
+      <c r="I65" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3011,7 +3017,7 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="20">
+      <c r="A66" s="19">
         <v>202510001000073</v>
       </c>
       <c r="B66" s="9" t="s">
@@ -3026,7 +3032,7 @@
       <c r="E66" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F66" s="16">
+      <c r="F66" s="15">
         <v>45959.587500000001</v>
       </c>
       <c r="G66" s="7">
@@ -3035,7 +3041,7 @@
       <c r="H66" s="7">
         <v>45972</v>
       </c>
-      <c r="I66" s="21" t="str">
+      <c r="I66" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3044,22 +3050,22 @@
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="19">
+      <c r="A67" s="18">
         <v>202510004000074</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C67" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="D67" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E67" s="11" t="s">
+      <c r="E67" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F67" s="14">
+      <c r="F67" s="13">
         <v>45959.695833333331</v>
       </c>
       <c r="G67" s="6">
@@ -3068,7 +3074,7 @@
       <c r="H67" s="8">
         <v>45959</v>
       </c>
-      <c r="I67" s="21" t="str">
+      <c r="I67" s="20" t="str">
         <f t="shared" ref="I67:I89" si="1">IF(H67&lt;=G67,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
@@ -3077,7 +3083,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="20">
+      <c r="A68" s="19">
         <v>202510011000075</v>
       </c>
       <c r="B68" s="9" t="s">
@@ -3092,7 +3098,7 @@
       <c r="E68" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F68" s="16">
+      <c r="F68" s="15">
         <v>45959.704861111109</v>
       </c>
       <c r="G68" s="7">
@@ -3101,7 +3107,7 @@
       <c r="H68" s="8">
         <v>46027</v>
       </c>
-      <c r="I68" s="21" t="str">
+      <c r="I68" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3110,22 +3116,22 @@
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="19">
+      <c r="A69" s="18">
         <v>202510001000076</v>
       </c>
-      <c r="B69" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" s="11" t="s">
+      <c r="B69" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D69" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="E69" s="11" t="s">
+      <c r="E69" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F69" s="14">
+      <c r="F69" s="13">
         <v>45960.417361111111</v>
       </c>
       <c r="G69" s="6">
@@ -3134,7 +3140,7 @@
       <c r="H69" s="6">
         <v>45975</v>
       </c>
-      <c r="I69" s="21" t="str">
+      <c r="I69" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3143,7 +3149,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="20">
+      <c r="A70" s="19">
         <v>202510001000077</v>
       </c>
       <c r="B70" s="9" t="s">
@@ -3158,7 +3164,7 @@
       <c r="E70" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F70" s="16">
+      <c r="F70" s="15">
         <v>45960.429166666669</v>
       </c>
       <c r="G70" s="7">
@@ -3167,7 +3173,7 @@
       <c r="H70" s="8">
         <v>45975</v>
       </c>
-      <c r="I70" s="21" t="str">
+      <c r="I70" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3176,22 +3182,22 @@
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="19">
+      <c r="A71" s="18">
         <v>202510004000078</v>
       </c>
-      <c r="B71" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" s="11" t="s">
+      <c r="B71" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D71" s="11" t="s">
+      <c r="D71" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E71" s="11" t="s">
+      <c r="E71" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F71" s="14">
+      <c r="F71" s="13">
         <v>45960.4375</v>
       </c>
       <c r="G71" s="6">
@@ -3200,7 +3206,7 @@
       <c r="H71" s="8">
         <v>45975</v>
       </c>
-      <c r="I71" s="21" t="str">
+      <c r="I71" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3209,7 +3215,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" s="20">
+      <c r="A72" s="19">
         <v>202510001000079</v>
       </c>
       <c r="B72" s="9" t="s">
@@ -3224,7 +3230,7 @@
       <c r="E72" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F72" s="16">
+      <c r="F72" s="15">
         <v>45960.442361111112</v>
       </c>
       <c r="G72" s="7">
@@ -3233,7 +3239,7 @@
       <c r="H72" s="7">
         <v>45975</v>
       </c>
-      <c r="I72" s="21" t="str">
+      <c r="I72" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3242,22 +3248,22 @@
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="19">
+      <c r="A73" s="18">
         <v>202510016000080</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C73" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D73" s="11" t="s">
+      <c r="D73" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="E73" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="F73" s="14">
+      <c r="F73" s="13">
         <v>45961.374305555553</v>
       </c>
       <c r="G73" s="6">
@@ -3266,7 +3272,7 @@
       <c r="H73" s="8">
         <v>46062</v>
       </c>
-      <c r="I73" s="21" t="str">
+      <c r="I73" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3275,7 +3281,7 @@
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="20">
+      <c r="A74" s="19">
         <v>202510007000081</v>
       </c>
       <c r="B74" s="9" t="s">
@@ -3290,7 +3296,7 @@
       <c r="E74" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F74" s="16">
+      <c r="F74" s="15">
         <v>45961.45</v>
       </c>
       <c r="G74" s="7">
@@ -3299,7 +3305,7 @@
       <c r="H74" s="7">
         <v>45994</v>
       </c>
-      <c r="I74" s="21" t="str">
+      <c r="I74" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3308,22 +3314,22 @@
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="19">
+      <c r="A75" s="18">
         <v>202511011000082</v>
       </c>
-      <c r="B75" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" s="11" t="s">
+      <c r="B75" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D75" s="11" t="s">
+      <c r="D75" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="E75" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F75" s="14">
+      <c r="F75" s="13">
         <v>45964.479861111111</v>
       </c>
       <c r="G75" s="6">
@@ -3332,7 +3338,7 @@
       <c r="H75" s="8">
         <v>45978</v>
       </c>
-      <c r="I75" s="21" t="str">
+      <c r="I75" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3341,7 +3347,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="20">
+      <c r="A76" s="19">
         <v>202511007000083</v>
       </c>
       <c r="B76" s="9" t="s">
@@ -3356,7 +3362,7 @@
       <c r="E76" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F76" s="16">
+      <c r="F76" s="15">
         <v>45965.35833333333</v>
       </c>
       <c r="G76" s="7">
@@ -3365,7 +3371,7 @@
       <c r="H76" s="7">
         <v>45972</v>
       </c>
-      <c r="I76" s="21" t="str">
+      <c r="I76" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3374,22 +3380,22 @@
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="19">
+      <c r="A77" s="18">
         <v>202511015000084</v>
       </c>
-      <c r="B77" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" s="11" t="s">
+      <c r="B77" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D77" s="11" t="s">
+      <c r="D77" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E77" s="11" t="s">
+      <c r="E77" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F77" s="14">
+      <c r="F77" s="13">
         <v>45966.474305555559</v>
       </c>
       <c r="G77" s="6">
@@ -3398,7 +3404,7 @@
       <c r="H77" s="6">
         <v>45967</v>
       </c>
-      <c r="I77" s="21" t="str">
+      <c r="I77" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3407,7 +3413,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="20">
+      <c r="A78" s="19">
         <v>202511001000085</v>
       </c>
       <c r="B78" s="9" t="s">
@@ -3422,7 +3428,7 @@
       <c r="E78" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F78" s="16">
+      <c r="F78" s="15">
         <v>45966.668749999997</v>
       </c>
       <c r="G78" s="7">
@@ -3431,7 +3437,7 @@
       <c r="H78" s="8">
         <v>45999</v>
       </c>
-      <c r="I78" s="21" t="str">
+      <c r="I78" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3440,22 +3446,22 @@
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="19">
+      <c r="A79" s="18">
         <v>202511006000086</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C79" s="11" t="s">
+      <c r="C79" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D79" s="11" t="s">
+      <c r="D79" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E79" s="11" t="s">
+      <c r="E79" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="F79" s="14">
+      <c r="F79" s="13">
         <v>45967.488888888889</v>
       </c>
       <c r="G79" s="6">
@@ -3464,7 +3470,7 @@
       <c r="H79" s="6">
         <v>46062</v>
       </c>
-      <c r="I79" s="21" t="str">
+      <c r="I79" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3473,7 +3479,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="20">
+      <c r="A80" s="19">
         <v>202511004000087</v>
       </c>
       <c r="B80" s="9" t="s">
@@ -3488,7 +3494,7 @@
       <c r="E80" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F80" s="16">
+      <c r="F80" s="15">
         <v>45968.387499999997</v>
       </c>
       <c r="G80" s="7">
@@ -3497,7 +3503,7 @@
       <c r="H80" s="8">
         <v>45972</v>
       </c>
-      <c r="I80" s="21" t="str">
+      <c r="I80" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3506,22 +3512,22 @@
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81" s="19">
+      <c r="A81" s="18">
         <v>202511007000088</v>
       </c>
-      <c r="B81" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" s="11" t="s">
+      <c r="B81" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D81" s="11" t="s">
+      <c r="D81" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E81" s="11" t="s">
+      <c r="E81" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F81" s="14">
+      <c r="F81" s="13">
         <v>45968.465277777781</v>
       </c>
       <c r="G81" s="6">
@@ -3530,7 +3536,7 @@
       <c r="H81" s="8">
         <v>45971</v>
       </c>
-      <c r="I81" s="21" t="str">
+      <c r="I81" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3539,7 +3545,7 @@
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" s="20">
+      <c r="A82" s="19">
         <v>202511008000089</v>
       </c>
       <c r="B82" s="9" t="s">
@@ -3554,7 +3560,7 @@
       <c r="E82" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F82" s="16">
+      <c r="F82" s="15">
         <v>45968.493055555555</v>
       </c>
       <c r="G82" s="7">
@@ -3563,7 +3569,7 @@
       <c r="H82" s="8">
         <v>45971</v>
       </c>
-      <c r="I82" s="21" t="str">
+      <c r="I82" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3572,22 +3578,22 @@
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="19">
+      <c r="A83" s="18">
         <v>202511009000090</v>
       </c>
-      <c r="B83" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" s="11" t="s">
+      <c r="B83" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D83" s="11" t="s">
+      <c r="D83" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="E83" s="11" t="s">
+      <c r="E83" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F83" s="14">
+      <c r="F83" s="13">
         <v>45971.415277777778</v>
       </c>
       <c r="G83" s="6">
@@ -3596,7 +3602,7 @@
       <c r="H83" s="6">
         <v>45996</v>
       </c>
-      <c r="I83" s="21" t="str">
+      <c r="I83" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3605,7 +3611,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="20">
+      <c r="A84" s="19">
         <v>202511009000091</v>
       </c>
       <c r="B84" s="9" t="s">
@@ -3620,7 +3626,7 @@
       <c r="E84" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F84" s="16">
+      <c r="F84" s="15">
         <v>45971.454861111109</v>
       </c>
       <c r="G84" s="7">
@@ -3629,7 +3635,7 @@
       <c r="H84" s="7">
         <v>46006</v>
       </c>
-      <c r="I84" s="21" t="str">
+      <c r="I84" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3638,22 +3644,22 @@
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" s="19">
+      <c r="A85" s="18">
         <v>202511011000092</v>
       </c>
-      <c r="B85" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" s="11" t="s">
+      <c r="B85" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D85" s="11" t="s">
+      <c r="D85" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E85" s="11" t="s">
+      <c r="E85" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F85" s="14">
+      <c r="F85" s="13">
         <v>45972.674305555556</v>
       </c>
       <c r="G85" s="6">
@@ -3662,7 +3668,7 @@
       <c r="H85" s="8">
         <v>45978</v>
       </c>
-      <c r="I85" s="21" t="str">
+      <c r="I85" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3671,7 +3677,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="20">
+      <c r="A86" s="19">
         <v>202511011000093</v>
       </c>
       <c r="B86" s="9" t="s">
@@ -3686,7 +3692,7 @@
       <c r="E86" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F86" s="16">
+      <c r="F86" s="15">
         <v>45974.462500000001</v>
       </c>
       <c r="G86" s="7">
@@ -3695,7 +3701,7 @@
       <c r="H86" s="8">
         <v>46020</v>
       </c>
-      <c r="I86" s="21" t="str">
+      <c r="I86" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3704,22 +3710,22 @@
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" s="19">
+      <c r="A87" s="18">
         <v>202511004000094</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C87" s="11" t="s">
+      <c r="C87" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D87" s="11" t="s">
+      <c r="D87" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E87" s="11" t="s">
+      <c r="E87" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F87" s="14">
+      <c r="F87" s="13">
         <v>45974.622916666667</v>
       </c>
       <c r="G87" s="6">
@@ -3728,7 +3734,7 @@
       <c r="H87" s="6">
         <v>45974</v>
       </c>
-      <c r="I87" s="21" t="str">
+      <c r="I87" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3737,7 +3743,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="20">
+      <c r="A88" s="19">
         <v>202511011000095</v>
       </c>
       <c r="B88" s="9" t="s">
@@ -3752,7 +3758,7 @@
       <c r="E88" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F88" s="16">
+      <c r="F88" s="15">
         <v>45979.40902777778</v>
       </c>
       <c r="G88" s="7">
@@ -3761,7 +3767,7 @@
       <c r="H88" s="8">
         <v>46156</v>
       </c>
-      <c r="I88" s="21" t="str">
+      <c r="I88" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3770,22 +3776,22 @@
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" s="19">
+      <c r="A89" s="18">
         <v>202511011000096</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C89" s="11" t="s">
+      <c r="C89" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D89" s="11" t="s">
+      <c r="D89" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="E89" s="11" t="s">
+      <c r="E89" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F89" s="14">
+      <c r="F89" s="13">
         <v>45979.479861111111</v>
       </c>
       <c r="G89" s="6">
@@ -3794,7 +3800,7 @@
       <c r="H89" s="6">
         <v>46156</v>
       </c>
-      <c r="I89" s="21" t="str">
+      <c r="I89" s="20" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3803,7 +3809,7 @@
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A90" s="20">
+      <c r="A90" s="19">
         <v>202511001000097</v>
       </c>
       <c r="B90" s="9" t="s">
@@ -3818,7 +3824,7 @@
       <c r="E90" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F90" s="16">
+      <c r="F90" s="15">
         <v>45979.487500000003</v>
       </c>
       <c r="G90" s="7">
@@ -3827,7 +3833,7 @@
       <c r="H90" s="8">
         <v>46020</v>
       </c>
-      <c r="I90" s="21" t="str">
+      <c r="I90" s="20" t="str">
         <f t="shared" ref="I90:I117" si="2">IF(H90&lt;=G90,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Fora do Prazo</v>
       </c>
@@ -3836,22 +3842,22 @@
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91" s="19">
+      <c r="A91" s="18">
         <v>202511007000098</v>
       </c>
-      <c r="B91" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" s="11" t="s">
+      <c r="B91" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D91" s="11" t="s">
+      <c r="D91" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E91" s="11" t="s">
+      <c r="E91" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F91" s="14">
+      <c r="F91" s="13">
         <v>45980.656944444447</v>
       </c>
       <c r="G91" s="6">
@@ -3860,7 +3866,7 @@
       <c r="H91" s="8">
         <v>45994</v>
       </c>
-      <c r="I91" s="21" t="str">
+      <c r="I91" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3869,7 +3875,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92" s="20">
+      <c r="A92" s="19">
         <v>202511007000099</v>
       </c>
       <c r="B92" s="9" t="s">
@@ -3884,7 +3890,7 @@
       <c r="E92" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F92" s="16">
+      <c r="F92" s="15">
         <v>45982.683333333334</v>
       </c>
       <c r="G92" s="7">
@@ -3893,7 +3899,7 @@
       <c r="H92" s="8">
         <v>45994</v>
       </c>
-      <c r="I92" s="21" t="str">
+      <c r="I92" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3902,22 +3908,22 @@
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" s="19">
+      <c r="A93" s="18">
         <v>202511007000100</v>
       </c>
-      <c r="B93" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" s="11" t="s">
+      <c r="B93" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D93" s="11" t="s">
+      <c r="D93" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E93" s="11" t="s">
+      <c r="E93" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F93" s="14">
+      <c r="F93" s="13">
         <v>45982.686805555553</v>
       </c>
       <c r="G93" s="6">
@@ -3926,7 +3932,7 @@
       <c r="H93" s="8">
         <v>45995</v>
       </c>
-      <c r="I93" s="21" t="str">
+      <c r="I93" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3935,7 +3941,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" s="20">
+      <c r="A94" s="19">
         <v>202511011000101</v>
       </c>
       <c r="B94" s="9" t="s">
@@ -3950,7 +3956,7 @@
       <c r="E94" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F94" s="16">
+      <c r="F94" s="15">
         <v>45985.623611111114</v>
       </c>
       <c r="G94" s="7">
@@ -3959,7 +3965,7 @@
       <c r="H94" s="8">
         <v>46020</v>
       </c>
-      <c r="I94" s="21" t="str">
+      <c r="I94" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3968,22 +3974,22 @@
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="19">
+      <c r="A95" s="18">
         <v>202511009000102</v>
       </c>
-      <c r="B95" s="11" t="s">
+      <c r="B95" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C95" s="11" t="s">
+      <c r="C95" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D95" s="11" t="s">
+      <c r="D95" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="E95" s="11" t="s">
+      <c r="E95" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F95" s="14">
+      <c r="F95" s="13">
         <v>45986.402777777781</v>
       </c>
       <c r="G95" s="6">
@@ -3992,7 +3998,7 @@
       <c r="H95" s="6">
         <v>46000</v>
       </c>
-      <c r="I95" s="21" t="str">
+      <c r="I95" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4001,7 +4007,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A96" s="20">
+      <c r="A96" s="19">
         <v>202511001000103</v>
       </c>
       <c r="B96" s="9" t="s">
@@ -4016,7 +4022,7 @@
       <c r="E96" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F96" s="16">
+      <c r="F96" s="15">
         <v>45986.414583333331</v>
       </c>
       <c r="G96" s="7">
@@ -4025,7 +4031,7 @@
       <c r="H96" s="8">
         <v>46020</v>
       </c>
-      <c r="I96" s="21" t="str">
+      <c r="I96" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4034,22 +4040,22 @@
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A97" s="19">
+      <c r="A97" s="18">
         <v>202511007000104</v>
       </c>
-      <c r="B97" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" s="11" t="s">
+      <c r="B97" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D97" s="11" t="s">
+      <c r="D97" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="E97" s="11" t="s">
+      <c r="E97" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F97" s="14">
+      <c r="F97" s="13">
         <v>45987.506944444445</v>
       </c>
       <c r="G97" s="6">
@@ -4058,7 +4064,7 @@
       <c r="H97" s="8">
         <v>46149</v>
       </c>
-      <c r="I97" s="21" t="str">
+      <c r="I97" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4067,7 +4073,7 @@
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A98" s="20">
+      <c r="A98" s="19">
         <v>202511007000105</v>
       </c>
       <c r="B98" s="9" t="s">
@@ -4082,7 +4088,7 @@
       <c r="E98" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F98" s="16">
+      <c r="F98" s="15">
         <v>45988.619444444441</v>
       </c>
       <c r="G98" s="7">
@@ -4091,7 +4097,7 @@
       <c r="H98" s="7">
         <v>46027</v>
       </c>
-      <c r="I98" s="21" t="str">
+      <c r="I98" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4100,22 +4106,22 @@
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A99" s="19">
+      <c r="A99" s="18">
         <v>202511009000106</v>
       </c>
-      <c r="B99" s="11" t="s">
+      <c r="B99" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C99" s="11" t="s">
+      <c r="C99" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D99" s="11" t="s">
+      <c r="D99" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="E99" s="11" t="s">
+      <c r="E99" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F99" s="14">
+      <c r="F99" s="13">
         <v>45988.675000000003</v>
       </c>
       <c r="G99" s="6">
@@ -4124,7 +4130,7 @@
       <c r="H99" s="6">
         <v>45996</v>
       </c>
-      <c r="I99" s="21" t="str">
+      <c r="I99" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4133,7 +4139,7 @@
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A100" s="20">
+      <c r="A100" s="19">
         <v>202511001000107</v>
       </c>
       <c r="B100" s="9" t="s">
@@ -4148,7 +4154,7 @@
       <c r="E100" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F100" s="16">
+      <c r="F100" s="15">
         <v>45988.697916666664</v>
       </c>
       <c r="G100" s="7">
@@ -4157,7 +4163,7 @@
       <c r="H100" s="7">
         <v>46020</v>
       </c>
-      <c r="I100" s="21" t="str">
+      <c r="I100" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4166,22 +4172,22 @@
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A101" s="19">
+      <c r="A101" s="18">
         <v>202511009000108</v>
       </c>
-      <c r="B101" s="11" t="s">
+      <c r="B101" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C101" s="11" t="s">
+      <c r="C101" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D101" s="11" t="s">
+      <c r="D101" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="E101" s="11" t="s">
+      <c r="E101" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F101" s="14">
+      <c r="F101" s="13">
         <v>45989.461111111108</v>
       </c>
       <c r="G101" s="6">
@@ -4190,7 +4196,7 @@
       <c r="H101" s="8">
         <v>45992</v>
       </c>
-      <c r="I101" s="21" t="str">
+      <c r="I101" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4199,7 +4205,7 @@
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A102" s="20">
+      <c r="A102" s="19">
         <v>202511011000109</v>
       </c>
       <c r="B102" s="9" t="s">
@@ -4214,35 +4220,35 @@
       <c r="E102" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F102" s="16">
+      <c r="F102" s="15">
         <v>45989.697916666664</v>
       </c>
       <c r="G102" s="7">
         <v>46019</v>
       </c>
       <c r="H102" s="9"/>
-      <c r="I102" s="15"/>
-      <c r="J102" s="22" t="s">
+      <c r="I102" s="14"/>
+      <c r="J102" s="21" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A103" s="19">
+      <c r="A103" s="18">
         <v>202511001000110</v>
       </c>
-      <c r="B103" s="11" t="s">
+      <c r="B103" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C103" s="11" t="s">
+      <c r="C103" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D103" s="11" t="s">
+      <c r="D103" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E103" s="11" t="s">
+      <c r="E103" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F103" s="14">
+      <c r="F103" s="13">
         <v>45989.705555555556</v>
       </c>
       <c r="G103" s="6">
@@ -4251,7 +4257,7 @@
       <c r="H103" s="6">
         <v>45999</v>
       </c>
-      <c r="I103" s="21" t="str">
+      <c r="I103" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4260,7 +4266,7 @@
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A104" s="20">
+      <c r="A104" s="19">
         <v>202512011000111</v>
       </c>
       <c r="B104" s="9" t="s">
@@ -4275,7 +4281,7 @@
       <c r="E104" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F104" s="16">
+      <c r="F104" s="15">
         <v>45992.445138888892</v>
       </c>
       <c r="G104" s="7">
@@ -4284,7 +4290,7 @@
       <c r="H104" s="7">
         <v>46020</v>
       </c>
-      <c r="I104" s="21" t="str">
+      <c r="I104" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4293,22 +4299,22 @@
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A105" s="19">
+      <c r="A105" s="18">
         <v>202512015000112</v>
       </c>
-      <c r="B105" s="11" t="s">
+      <c r="B105" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C105" s="11" t="s">
+      <c r="C105" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D105" s="11" t="s">
+      <c r="D105" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E105" s="11" t="s">
+      <c r="E105" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F105" s="14">
+      <c r="F105" s="13">
         <v>45992.684027777781</v>
       </c>
       <c r="G105" s="6">
@@ -4317,7 +4323,7 @@
       <c r="H105" s="8">
         <v>45994</v>
       </c>
-      <c r="I105" s="21" t="str">
+      <c r="I105" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4326,7 +4332,7 @@
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" s="20">
+      <c r="A106" s="19">
         <v>202512015000113</v>
       </c>
       <c r="B106" s="9" t="s">
@@ -4341,7 +4347,7 @@
       <c r="E106" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F106" s="16">
+      <c r="F106" s="15">
         <v>45993.400694444441</v>
       </c>
       <c r="G106" s="7">
@@ -4350,7 +4356,7 @@
       <c r="H106" s="7">
         <v>46149</v>
       </c>
-      <c r="I106" s="21" t="str">
+      <c r="I106" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4359,22 +4365,22 @@
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A107" s="19">
+      <c r="A107" s="18">
         <v>202512008000114</v>
       </c>
-      <c r="B107" s="11" t="s">
+      <c r="B107" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C107" s="11" t="s">
+      <c r="C107" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="D107" s="11" t="s">
+      <c r="D107" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E107" s="11" t="s">
+      <c r="E107" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F107" s="14">
+      <c r="F107" s="13">
         <v>45993.460416666669</v>
       </c>
       <c r="G107" s="6">
@@ -4383,7 +4389,7 @@
       <c r="H107" s="6">
         <v>45993</v>
       </c>
-      <c r="I107" s="21" t="str">
+      <c r="I107" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4392,7 +4398,7 @@
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A108" s="20">
+      <c r="A108" s="19">
         <v>202512011000115</v>
       </c>
       <c r="B108" s="9" t="s">
@@ -4407,7 +4413,7 @@
       <c r="E108" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F108" s="16">
+      <c r="F108" s="15">
         <v>45993.638888888891</v>
       </c>
       <c r="G108" s="7">
@@ -4416,7 +4422,7 @@
       <c r="H108" s="7">
         <v>46156</v>
       </c>
-      <c r="I108" s="21" t="str">
+      <c r="I108" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4425,22 +4431,22 @@
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A109" s="19">
+      <c r="A109" s="18">
         <v>202512015000116</v>
       </c>
-      <c r="B109" s="11" t="s">
+      <c r="B109" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C109" s="11" t="s">
+      <c r="C109" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D109" s="11" t="s">
+      <c r="D109" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E109" s="11" t="s">
+      <c r="E109" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F109" s="14">
+      <c r="F109" s="13">
         <v>45993.895833333336</v>
       </c>
       <c r="G109" s="6">
@@ -4449,7 +4455,7 @@
       <c r="H109" s="6">
         <v>45994</v>
       </c>
-      <c r="I109" s="21" t="str">
+      <c r="I109" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4458,7 +4464,7 @@
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A110" s="20">
+      <c r="A110" s="19">
         <v>202512007000117</v>
       </c>
       <c r="B110" s="9" t="s">
@@ -4473,7 +4479,7 @@
       <c r="E110" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F110" s="16">
+      <c r="F110" s="15">
         <v>45994.686805555553</v>
       </c>
       <c r="G110" s="7">
@@ -4482,7 +4488,7 @@
       <c r="H110" s="8">
         <v>46062</v>
       </c>
-      <c r="I110" s="21" t="str">
+      <c r="I110" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4491,22 +4497,22 @@
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A111" s="19">
+      <c r="A111" s="18">
         <v>202512001000118</v>
       </c>
-      <c r="B111" s="11" t="s">
+      <c r="B111" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C111" s="11" t="s">
+      <c r="C111" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D111" s="11" t="s">
+      <c r="D111" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="E111" s="11" t="s">
+      <c r="E111" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F111" s="14">
+      <c r="F111" s="13">
         <v>45994.713194444441</v>
       </c>
       <c r="G111" s="6">
@@ -4515,7 +4521,7 @@
       <c r="H111" s="8">
         <v>46020</v>
       </c>
-      <c r="I111" s="21" t="str">
+      <c r="I111" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4524,7 +4530,7 @@
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" s="20">
+      <c r="A112" s="19">
         <v>202512009000119</v>
       </c>
       <c r="B112" s="9" t="s">
@@ -4539,7 +4545,7 @@
       <c r="E112" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F112" s="16">
+      <c r="F112" s="15">
         <v>45995.634027777778</v>
       </c>
       <c r="G112" s="7">
@@ -4548,7 +4554,7 @@
       <c r="H112" s="7">
         <v>45995</v>
       </c>
-      <c r="I112" s="21" t="str">
+      <c r="I112" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4557,22 +4563,22 @@
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A113" s="19">
+      <c r="A113" s="18">
         <v>202512011000120</v>
       </c>
-      <c r="B113" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" s="11" t="s">
+      <c r="B113" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D113" s="11" t="s">
+      <c r="D113" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E113" s="11" t="s">
+      <c r="E113" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F113" s="14">
+      <c r="F113" s="13">
         <v>45999.407638888886</v>
       </c>
       <c r="G113" s="6">
@@ -4581,7 +4587,7 @@
       <c r="H113" s="8">
         <v>45999</v>
       </c>
-      <c r="I113" s="21" t="str">
+      <c r="I113" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4590,7 +4596,7 @@
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A114" s="20">
+      <c r="A114" s="19">
         <v>202512011000121</v>
       </c>
       <c r="B114" s="9" t="s">
@@ -4605,7 +4611,7 @@
       <c r="E114" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F114" s="16">
+      <c r="F114" s="15">
         <v>46001.634722222225</v>
       </c>
       <c r="G114" s="7">
@@ -4614,7 +4620,7 @@
       <c r="H114" s="7">
         <v>46121</v>
       </c>
-      <c r="I114" s="21" t="str">
+      <c r="I114" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4623,22 +4629,22 @@
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A115" s="19">
+      <c r="A115" s="18">
         <v>202512011000122</v>
       </c>
-      <c r="B115" s="11" t="s">
+      <c r="B115" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C115" s="11" t="s">
+      <c r="C115" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D115" s="11" t="s">
+      <c r="D115" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E115" s="11" t="s">
+      <c r="E115" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F115" s="14">
+      <c r="F115" s="13">
         <v>46003.506944444445</v>
       </c>
       <c r="G115" s="6">
@@ -4647,7 +4653,7 @@
       <c r="H115" s="8">
         <v>46027</v>
       </c>
-      <c r="I115" s="21" t="str">
+      <c r="I115" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4656,7 +4662,7 @@
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A116" s="20">
+      <c r="A116" s="19">
         <v>202512007000123</v>
       </c>
       <c r="B116" s="9" t="s">
@@ -4671,7 +4677,7 @@
       <c r="E116" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F116" s="16">
+      <c r="F116" s="15">
         <v>46008.395138888889</v>
       </c>
       <c r="G116" s="7">
@@ -4680,7 +4686,7 @@
       <c r="H116" s="7">
         <v>46010</v>
       </c>
-      <c r="I116" s="21" t="str">
+      <c r="I116" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4689,22 +4695,22 @@
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A117" s="19">
+      <c r="A117" s="18">
         <v>202512001000124</v>
       </c>
-      <c r="B117" s="11" t="s">
+      <c r="B117" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C117" s="11" t="s">
+      <c r="C117" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D117" s="11" t="s">
+      <c r="D117" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E117" s="11" t="s">
+      <c r="E117" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F117" s="14">
+      <c r="F117" s="13">
         <v>46010.370138888888</v>
       </c>
       <c r="G117" s="6">
@@ -4713,7 +4719,7 @@
       <c r="H117" s="6">
         <v>46135</v>
       </c>
-      <c r="I117" s="21" t="str">
+      <c r="I117" s="20" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4722,7 +4728,7 @@
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A118" s="20">
+      <c r="A118" s="19">
         <v>202512015000125</v>
       </c>
       <c r="B118" s="9" t="s">
@@ -4737,7 +4743,7 @@
       <c r="E118" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F118" s="16">
+      <c r="F118" s="15">
         <v>46014.677777777775</v>
       </c>
       <c r="G118" s="7">
@@ -4746,7 +4752,7 @@
       <c r="H118" s="7">
         <v>46062</v>
       </c>
-      <c r="I118" s="21" t="str">
+      <c r="I118" s="20" t="str">
         <f t="shared" ref="I118:I135" si="3">IF(H118&lt;=G118,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Fora do Prazo</v>
       </c>
@@ -4755,22 +4761,22 @@
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A119" s="19">
+      <c r="A119" s="18">
         <v>202512001000126</v>
       </c>
-      <c r="B119" s="11" t="s">
+      <c r="B119" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C119" s="11" t="s">
+      <c r="C119" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D119" s="11" t="s">
+      <c r="D119" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E119" s="11" t="s">
+      <c r="E119" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F119" s="14">
+      <c r="F119" s="13">
         <v>46015.77847222222</v>
       </c>
       <c r="G119" s="6">
@@ -4779,7 +4785,7 @@
       <c r="H119" s="8">
         <v>46020</v>
       </c>
-      <c r="I119" s="21" t="str">
+      <c r="I119" s="20" t="str">
         <f t="shared" si="3"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4788,7 +4794,7 @@
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A120" s="20">
+      <c r="A120" s="19">
         <v>202512011000127</v>
       </c>
       <c r="B120" s="9" t="s">
@@ -4803,7 +4809,7 @@
       <c r="E120" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F120" s="16">
+      <c r="F120" s="15">
         <v>46019.70416666667</v>
       </c>
       <c r="G120" s="7">
@@ -4812,7 +4818,7 @@
       <c r="H120" s="8">
         <v>46027</v>
       </c>
-      <c r="I120" s="21" t="str">
+      <c r="I120" s="20" t="str">
         <f t="shared" si="3"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4821,22 +4827,22 @@
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A121" s="19">
+      <c r="A121" s="18">
         <v>202601011000128</v>
       </c>
-      <c r="B121" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" s="11" t="s">
+      <c r="B121" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D121" s="11" t="s">
+      <c r="D121" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E121" s="11" t="s">
+      <c r="E121" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F121" s="14">
+      <c r="F121" s="13">
         <v>46024.73333333333</v>
       </c>
       <c r="G121" s="6">
@@ -4845,7 +4851,7 @@
       <c r="H121" s="8">
         <v>46062</v>
       </c>
-      <c r="I121" s="21" t="str">
+      <c r="I121" s="20" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4854,7 +4860,7 @@
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A122" s="20">
+      <c r="A122" s="19">
         <v>202601003000129</v>
       </c>
       <c r="B122" s="9" t="s">
@@ -4869,7 +4875,7 @@
       <c r="E122" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F122" s="16">
+      <c r="F122" s="15">
         <v>46027.561805555553</v>
       </c>
       <c r="G122" s="7">
@@ -4878,7 +4884,7 @@
       <c r="H122" s="8">
         <v>46156</v>
       </c>
-      <c r="I122" s="21" t="str">
+      <c r="I122" s="20" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4887,22 +4893,22 @@
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A123" s="19">
+      <c r="A123" s="18">
         <v>202601011000130</v>
       </c>
-      <c r="B123" s="11" t="s">
+      <c r="B123" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C123" s="11" t="s">
+      <c r="C123" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D123" s="11" t="s">
+      <c r="D123" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E123" s="11" t="s">
+      <c r="E123" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F123" s="14">
+      <c r="F123" s="13">
         <v>46030.428472222222</v>
       </c>
       <c r="G123" s="6">
@@ -4911,7 +4917,7 @@
       <c r="H123" s="8">
         <v>46050</v>
       </c>
-      <c r="I123" s="21" t="str">
+      <c r="I123" s="20" t="str">
         <f t="shared" si="3"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4920,7 +4926,7 @@
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A124" s="20">
+      <c r="A124" s="19">
         <v>202601003000131</v>
       </c>
       <c r="B124" s="9" t="s">
@@ -4935,35 +4941,40 @@
       <c r="E124" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F124" s="16">
+      <c r="F124" s="15">
         <v>46030.569444444445</v>
       </c>
       <c r="G124" s="7">
         <v>46060</v>
       </c>
-      <c r="H124" s="10"/>
-      <c r="I124" s="15"/>
-      <c r="J124" s="22" t="s">
-        <v>94</v>
+      <c r="H124" s="8">
+        <v>46157</v>
+      </c>
+      <c r="I124" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A125" s="19">
+      <c r="A125" s="18">
         <v>202601007000132</v>
       </c>
-      <c r="B125" s="11" t="s">
+      <c r="B125" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C125" s="11" t="s">
+      <c r="C125" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D125" s="11" t="s">
+      <c r="D125" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E125" s="11" t="s">
+      <c r="E125" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F125" s="14">
+      <c r="F125" s="13">
         <v>46031.270833333336</v>
       </c>
       <c r="G125" s="6">
@@ -4972,7 +4983,7 @@
       <c r="H125" s="6">
         <v>46031</v>
       </c>
-      <c r="I125" s="21" t="str">
+      <c r="I125" s="20" t="str">
         <f t="shared" si="3"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4981,7 +4992,7 @@
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A126" s="20">
+      <c r="A126" s="19">
         <v>202601007000133</v>
       </c>
       <c r="B126" s="9" t="s">
@@ -4996,35 +5007,40 @@
       <c r="E126" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F126" s="16">
+      <c r="F126" s="15">
         <v>46032.509722222225</v>
       </c>
       <c r="G126" s="7">
         <v>46062</v>
       </c>
-      <c r="H126" s="10"/>
-      <c r="I126" s="15"/>
-      <c r="J126" s="22" t="s">
-        <v>94</v>
+      <c r="H126" s="8">
+        <v>46157</v>
+      </c>
+      <c r="I126" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J126" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A127" s="19">
+      <c r="A127" s="18">
         <v>202601009000134</v>
       </c>
-      <c r="B127" s="11" t="s">
+      <c r="B127" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C127" s="11" t="s">
+      <c r="C127" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D127" s="11" t="s">
+      <c r="D127" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E127" s="11" t="s">
+      <c r="E127" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F127" s="14">
+      <c r="F127" s="13">
         <v>46034.411805555559</v>
       </c>
       <c r="G127" s="6">
@@ -5033,7 +5049,7 @@
       <c r="H127" s="8">
         <v>46071</v>
       </c>
-      <c r="I127" s="21" t="str">
+      <c r="I127" s="20" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -5042,7 +5058,7 @@
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A128" s="20">
+      <c r="A128" s="19">
         <v>202601011000135</v>
       </c>
       <c r="B128" s="9" t="s">
@@ -5057,7 +5073,7 @@
       <c r="E128" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F128" s="16">
+      <c r="F128" s="15">
         <v>46034.448611111111</v>
       </c>
       <c r="G128" s="7">
@@ -5066,7 +5082,7 @@
       <c r="H128" s="8">
         <v>46127</v>
       </c>
-      <c r="I128" s="21" t="str">
+      <c r="I128" s="20" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -5075,22 +5091,22 @@
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A129" s="19">
+      <c r="A129" s="18">
         <v>202601001000136</v>
       </c>
-      <c r="B129" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" s="11" t="s">
+      <c r="B129" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D129" s="11" t="s">
+      <c r="D129" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E129" s="11" t="s">
+      <c r="E129" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F129" s="14">
+      <c r="F129" s="13">
         <v>46035.555555555555</v>
       </c>
       <c r="G129" s="6">
@@ -5099,7 +5115,7 @@
       <c r="H129" s="8">
         <v>46071</v>
       </c>
-      <c r="I129" s="21" t="str">
+      <c r="I129" s="20" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -5108,7 +5124,7 @@
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A130" s="20">
+      <c r="A130" s="19">
         <v>202601001000137</v>
       </c>
       <c r="B130" s="9" t="s">
@@ -5123,7 +5139,7 @@
       <c r="E130" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F130" s="16">
+      <c r="F130" s="15">
         <v>46036.696527777778</v>
       </c>
       <c r="G130" s="7">
@@ -5132,7 +5148,7 @@
       <c r="H130" s="7">
         <v>46066</v>
       </c>
-      <c r="I130" s="21" t="str">
+      <c r="I130" s="20" t="str">
         <f t="shared" si="3"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -5141,22 +5157,22 @@
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A131" s="19">
+      <c r="A131" s="18">
         <v>202601007000138</v>
       </c>
-      <c r="B131" s="11" t="s">
+      <c r="B131" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C131" s="11" t="s">
+      <c r="C131" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D131" s="11" t="s">
+      <c r="D131" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E131" s="11" t="s">
+      <c r="E131" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F131" s="14">
+      <c r="F131" s="13">
         <v>46037.330555555556</v>
       </c>
       <c r="G131" s="6">
@@ -5165,7 +5181,7 @@
       <c r="H131" s="6">
         <v>46037</v>
       </c>
-      <c r="I131" s="21" t="str">
+      <c r="I131" s="20" t="str">
         <f t="shared" si="3"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -5174,7 +5190,7 @@
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A132" s="20">
+      <c r="A132" s="19">
         <v>202601007000141</v>
       </c>
       <c r="B132" s="9" t="s">
@@ -5189,7 +5205,7 @@
       <c r="E132" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F132" s="16">
+      <c r="F132" s="15">
         <v>46048.584722222222</v>
       </c>
       <c r="G132" s="7">
@@ -5198,7 +5214,7 @@
       <c r="H132" s="7">
         <v>46048</v>
       </c>
-      <c r="I132" s="21" t="str">
+      <c r="I132" s="20" t="str">
         <f t="shared" si="3"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -5207,22 +5223,22 @@
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A133" s="19">
+      <c r="A133" s="18">
         <v>202601013000142</v>
       </c>
-      <c r="B133" s="11" t="s">
+      <c r="B133" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C133" s="11" t="s">
+      <c r="C133" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D133" s="11" t="s">
+      <c r="D133" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E133" s="11" t="s">
+      <c r="E133" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F133" s="14">
+      <c r="F133" s="13">
         <v>46050.702777777777</v>
       </c>
       <c r="G133" s="6">
@@ -5231,7 +5247,7 @@
       <c r="H133" s="8">
         <v>46156</v>
       </c>
-      <c r="I133" s="21" t="str">
+      <c r="I133" s="20" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -5240,7 +5256,7 @@
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A134" s="20">
+      <c r="A134" s="19">
         <v>202601007000143</v>
       </c>
       <c r="B134" s="9" t="s">
@@ -5255,7 +5271,7 @@
       <c r="E134" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F134" s="16">
+      <c r="F134" s="15">
         <v>46051.736111111109</v>
       </c>
       <c r="G134" s="7">
@@ -5264,7 +5280,7 @@
       <c r="H134" s="8">
         <v>46125</v>
       </c>
-      <c r="I134" s="21" t="str">
+      <c r="I134" s="20" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -5273,22 +5289,22 @@
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A135" s="19">
+      <c r="A135" s="18">
         <v>202602012000144</v>
       </c>
-      <c r="B135" s="11" t="s">
+      <c r="B135" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C135" s="11" t="s">
+      <c r="C135" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D135" s="11" t="s">
+      <c r="D135" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E135" s="11" t="s">
+      <c r="E135" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F135" s="14">
+      <c r="F135" s="13">
         <v>46058.554861111108</v>
       </c>
       <c r="G135" s="6">
@@ -5297,7 +5313,7 @@
       <c r="H135" s="6">
         <v>46135</v>
       </c>
-      <c r="I135" s="21" t="str">
+      <c r="I135" s="20" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -5306,7 +5322,7 @@
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A136" s="20">
+      <c r="A136" s="19">
         <v>202602007000145</v>
       </c>
       <c r="B136" s="9" t="s">
@@ -5321,7 +5337,7 @@
       <c r="E136" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F136" s="16">
+      <c r="F136" s="15">
         <v>46062.308333333334</v>
       </c>
       <c r="G136" s="7">
@@ -5330,7 +5346,7 @@
       <c r="H136" s="8">
         <v>46062</v>
       </c>
-      <c r="I136" s="21" t="str">
+      <c r="I136" s="20" t="str">
         <f t="shared" ref="I136:I137" si="4">IF(H136&lt;=G136,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
@@ -5339,22 +5355,22 @@
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A137" s="19">
+      <c r="A137" s="18">
         <v>202602007000146</v>
       </c>
-      <c r="B137" s="11" t="s">
+      <c r="B137" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C137" s="11" t="s">
+      <c r="C137" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D137" s="11" t="s">
+      <c r="D137" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E137" s="11" t="s">
+      <c r="E137" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F137" s="14">
+      <c r="F137" s="13">
         <v>46062.349305555559</v>
       </c>
       <c r="G137" s="6">
@@ -5363,7 +5379,7 @@
       <c r="H137" s="6">
         <v>46062</v>
       </c>
-      <c r="I137" s="21" t="str">
+      <c r="I137" s="20" t="str">
         <f t="shared" si="4"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -5372,7 +5388,7 @@
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A138" s="20">
+      <c r="A138" s="19">
         <v>202602001000147</v>
       </c>
       <c r="B138" s="9" t="s">
@@ -5387,48 +5403,48 @@
       <c r="E138" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F138" s="16">
+      <c r="F138" s="15">
         <v>46064.45208333333</v>
       </c>
       <c r="G138" s="7">
         <v>46094</v>
       </c>
-      <c r="H138" s="21"/>
-      <c r="I138" s="15"/>
-      <c r="J138" s="22" t="s">
+      <c r="H138" s="20"/>
+      <c r="I138" s="14"/>
+      <c r="J138" s="21" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A139" s="19">
+      <c r="A139" s="18">
         <v>202602006000148</v>
       </c>
-      <c r="B139" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" s="11" t="s">
+      <c r="B139" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D139" s="11" t="s">
+      <c r="D139" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E139" s="11" t="s">
+      <c r="E139" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="F139" s="14">
+      <c r="F139" s="13">
         <v>46066.445833333331</v>
       </c>
       <c r="G139" s="6">
         <v>46096</v>
       </c>
-      <c r="H139" s="21"/>
-      <c r="I139" s="15"/>
-      <c r="J139" s="22" t="s">
+      <c r="H139" s="20"/>
+      <c r="I139" s="14"/>
+      <c r="J139" s="21" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A140" s="20">
+      <c r="A140" s="19">
         <v>202602007000149</v>
       </c>
       <c r="B140" s="9" t="s">
@@ -5443,7 +5459,7 @@
       <c r="E140" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F140" s="16">
+      <c r="F140" s="15">
         <v>46066.645833333336</v>
       </c>
       <c r="G140" s="7">
@@ -5452,7 +5468,7 @@
       <c r="H140" s="7">
         <v>46125</v>
       </c>
-      <c r="I140" s="21" t="str">
+      <c r="I140" s="20" t="str">
         <f t="shared" ref="I140" si="5">IF(H140&lt;=G140,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Fora do Prazo</v>
       </c>
@@ -5461,35 +5477,35 @@
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A141" s="19">
+      <c r="A141" s="18">
         <v>202602007000150</v>
       </c>
-      <c r="B141" s="11" t="s">
+      <c r="B141" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C141" s="11" t="s">
+      <c r="C141" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D141" s="11" t="s">
+      <c r="D141" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E141" s="11" t="s">
+      <c r="E141" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F141" s="14">
+      <c r="F141" s="13">
         <v>46068.59375</v>
       </c>
       <c r="G141" s="6">
         <v>46098</v>
       </c>
-      <c r="H141" s="21"/>
-      <c r="I141" s="15"/>
-      <c r="J141" s="22" t="s">
+      <c r="H141" s="20"/>
+      <c r="I141" s="14"/>
+      <c r="J141" s="21" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A142" s="20">
+      <c r="A142" s="19">
         <v>202602001000151</v>
       </c>
       <c r="B142" s="9" t="s">
@@ -5504,7 +5520,7 @@
       <c r="E142" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F142" s="16">
+      <c r="F142" s="15">
         <v>46071.643750000003</v>
       </c>
       <c r="G142" s="7">
@@ -5513,8 +5529,8 @@
       <c r="H142" s="7">
         <v>46071</v>
       </c>
-      <c r="I142" s="13" t="str">
-        <f>IF(H142&lt;=G142,"Dentro do Prazo","Fora do Prazo")</f>
+      <c r="I142" s="12" t="str">
+        <f t="shared" ref="I142:I147" si="6">IF(H142&lt;=G142,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J142" s="2" t="s">
@@ -5522,35 +5538,40 @@
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A143" s="19">
+      <c r="A143" s="18">
         <v>202602012000152</v>
       </c>
-      <c r="B143" s="11" t="s">
+      <c r="B143" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C143" s="11" t="s">
+      <c r="C143" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D143" s="11" t="s">
+      <c r="D143" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E143" s="11" t="s">
+      <c r="E143" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F143" s="14">
+      <c r="F143" s="13">
         <v>46071.645833333336</v>
       </c>
       <c r="G143" s="6">
         <v>46101</v>
       </c>
-      <c r="H143" s="10"/>
-      <c r="I143" s="15"/>
-      <c r="J143" s="22" t="s">
-        <v>94</v>
+      <c r="H143" s="8">
+        <v>46156</v>
+      </c>
+      <c r="I143" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J143" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A144" s="20">
+      <c r="A144" s="19">
         <v>202602001000153</v>
       </c>
       <c r="B144" s="9" t="s">
@@ -5565,7 +5586,7 @@
       <c r="E144" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F144" s="16">
+      <c r="F144" s="15">
         <v>46071.646527777775</v>
       </c>
       <c r="G144" s="7">
@@ -5574,8 +5595,8 @@
       <c r="H144" s="8">
         <v>46073</v>
       </c>
-      <c r="I144" s="13" t="str">
-        <f>IF(H144&lt;=G144,"Dentro do Prazo","Fora do Prazo")</f>
+      <c r="I144" s="12" t="str">
+        <f t="shared" si="6"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J144" s="2" t="s">
@@ -5583,22 +5604,22 @@
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A145" s="19">
+      <c r="A145" s="18">
         <v>202602009000154</v>
       </c>
-      <c r="B145" s="11" t="s">
+      <c r="B145" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C145" s="11" t="s">
+      <c r="C145" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D145" s="11" t="s">
+      <c r="D145" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E145" s="11" t="s">
+      <c r="E145" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F145" s="14">
+      <c r="F145" s="13">
         <v>46072.405555555553</v>
       </c>
       <c r="G145" s="6">
@@ -5607,8 +5628,8 @@
       <c r="H145" s="6">
         <v>46149</v>
       </c>
-      <c r="I145" s="13" t="str">
-        <f>IF(H145&lt;=G145,"Dentro do Prazo","Fora do Prazo")</f>
+      <c r="I145" s="12" t="str">
+        <f t="shared" si="6"/>
         <v>Fora do Prazo</v>
       </c>
       <c r="J145" s="2" t="s">
@@ -5616,7 +5637,7 @@
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A146" s="20">
+      <c r="A146" s="19">
         <v>202602007000155</v>
       </c>
       <c r="B146" s="9" t="s">
@@ -5631,7 +5652,7 @@
       <c r="E146" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F146" s="16">
+      <c r="F146" s="15">
         <v>46073.628472222219</v>
       </c>
       <c r="G146" s="7">
@@ -5640,8 +5661,8 @@
       <c r="H146" s="8">
         <v>46125</v>
       </c>
-      <c r="I146" s="13" t="str">
-        <f>IF(H146&lt;=G146,"Dentro do Prazo","Fora do Prazo")</f>
+      <c r="I146" s="12" t="str">
+        <f t="shared" si="6"/>
         <v>Fora do Prazo</v>
       </c>
       <c r="J146" s="2" t="s">
@@ -5649,22 +5670,22 @@
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A147" s="19">
+      <c r="A147" s="18">
         <v>202602007000156</v>
       </c>
-      <c r="B147" s="11" t="s">
+      <c r="B147" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C147" s="11" t="s">
+      <c r="C147" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D147" s="11" t="s">
+      <c r="D147" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E147" s="11" t="s">
+      <c r="E147" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F147" s="14">
+      <c r="F147" s="13">
         <v>46073.695138888892</v>
       </c>
       <c r="G147" s="6">
@@ -5673,8 +5694,8 @@
       <c r="H147" s="8">
         <v>46076</v>
       </c>
-      <c r="I147" s="13" t="str">
-        <f>IF(H147&lt;=G147,"Dentro do Prazo","Fora do Prazo")</f>
+      <c r="I147" s="12" t="str">
+        <f t="shared" si="6"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J147" s="2" t="s">
@@ -5682,7 +5703,7 @@
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A148" s="20">
+      <c r="A148" s="19">
         <v>202602007000157</v>
       </c>
       <c r="B148" s="9" t="s">
@@ -5697,20 +5718,20 @@
       <c r="E148" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F148" s="16">
+      <c r="F148" s="15">
         <v>46075.175694444442</v>
       </c>
       <c r="G148" s="7">
         <v>46105</v>
       </c>
       <c r="H148" s="9"/>
-      <c r="I148" s="15"/>
-      <c r="J148" s="22" t="s">
+      <c r="I148" s="14"/>
+      <c r="J148" s="21" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A149" s="23">
+      <c r="A149" s="22">
         <v>202602013000158</v>
       </c>
       <c r="B149" s="4" t="s">
@@ -5725,16 +5746,16 @@
       <c r="E149" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F149" s="24">
+      <c r="F149" s="23">
         <v>46077.315972222219</v>
       </c>
-      <c r="G149" s="12">
+      <c r="G149" s="11">
         <v>46107</v>
       </c>
-      <c r="H149" s="12">
+      <c r="H149" s="11">
         <v>46156</v>
       </c>
-      <c r="I149" s="13" t="str">
+      <c r="I149" s="12" t="str">
         <f>IF(H149&lt;=G149,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Fora do Prazo</v>
       </c>
@@ -5743,31 +5764,31 @@
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A150" s="25">
+      <c r="A150" s="24">
         <v>202602001000159</v>
       </c>
-      <c r="B150" s="26" t="s">
+      <c r="B150" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C150" s="26" t="s">
+      <c r="C150" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="D150" s="26" t="s">
+      <c r="D150" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="E150" s="26" t="s">
+      <c r="E150" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="F150" s="27">
+      <c r="F150" s="26">
         <v>46077.550694444442</v>
       </c>
-      <c r="G150" s="13">
+      <c r="G150" s="12">
         <v>46107</v>
       </c>
-      <c r="H150" s="13">
+      <c r="H150" s="12">
         <v>46078</v>
       </c>
-      <c r="I150" s="13" t="str">
+      <c r="I150" s="12" t="str">
         <f>IF(H150&lt;=G150,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
@@ -5776,7 +5797,7 @@
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A151" s="23">
+      <c r="A151" s="22">
         <v>202602015000160</v>
       </c>
       <c r="B151" s="4" t="s">
@@ -5791,16 +5812,16 @@
       <c r="E151" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F151" s="24">
+      <c r="F151" s="23">
         <v>46077.585416666669</v>
       </c>
-      <c r="G151" s="12">
+      <c r="G151" s="11">
         <v>46107</v>
       </c>
-      <c r="H151" s="12">
+      <c r="H151" s="11">
         <v>46149</v>
       </c>
-      <c r="I151" s="13" t="str">
+      <c r="I151" s="12" t="str">
         <f>IF(H151&lt;=G151,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Fora do Prazo</v>
       </c>
@@ -5809,35 +5830,35 @@
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A152" s="25">
+      <c r="A152" s="24">
         <v>202602007000161</v>
       </c>
-      <c r="B152" s="26" t="s">
+      <c r="B152" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C152" s="26" t="s">
+      <c r="C152" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D152" s="26" t="s">
+      <c r="D152" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E152" s="26" t="s">
+      <c r="E152" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="F152" s="27">
+      <c r="F152" s="26">
         <v>46079.628472222219</v>
       </c>
-      <c r="G152" s="13">
+      <c r="G152" s="12">
         <v>46109</v>
       </c>
-      <c r="H152" s="13"/>
-      <c r="I152" s="13"/>
-      <c r="J152" s="22" t="s">
+      <c r="H152" s="12"/>
+      <c r="I152" s="12"/>
+      <c r="J152" s="21" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A153" s="23">
+      <c r="A153" s="22">
         <v>202603012000162</v>
       </c>
       <c r="B153" s="4" t="s">
@@ -5852,17 +5873,17 @@
       <c r="E153" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F153" s="24">
+      <c r="F153" s="23">
         <v>46084.686805555553</v>
       </c>
-      <c r="G153" s="12">
+      <c r="G153" s="11">
         <v>46114</v>
       </c>
-      <c r="H153" s="12">
+      <c r="H153" s="11">
         <v>46091</v>
       </c>
-      <c r="I153" s="13" t="str">
-        <f t="shared" ref="I153:I161" si="6">IF(H153&lt;=G153,"Dentro do Prazo","Fora do Prazo")</f>
+      <c r="I153" s="12" t="str">
+        <f t="shared" ref="I153:I162" si="7">IF(H153&lt;=G153,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J153" s="4" t="s">
@@ -5870,32 +5891,32 @@
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A154" s="25">
+      <c r="A154" s="24">
         <v>202603012000163</v>
       </c>
-      <c r="B154" s="26" t="s">
+      <c r="B154" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C154" s="26" t="s">
+      <c r="C154" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D154" s="26" t="s">
+      <c r="D154" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="E154" s="26" t="s">
+      <c r="E154" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F154" s="27">
+      <c r="F154" s="26">
         <v>46087.588194444441</v>
       </c>
-      <c r="G154" s="13">
+      <c r="G154" s="12">
         <v>46117</v>
       </c>
-      <c r="H154" s="13">
+      <c r="H154" s="12">
         <v>46104</v>
       </c>
-      <c r="I154" s="13" t="str">
-        <f t="shared" si="6"/>
+      <c r="I154" s="12" t="str">
+        <f t="shared" si="7"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J154" s="4" t="s">
@@ -5903,7 +5924,7 @@
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A155" s="23">
+      <c r="A155" s="22">
         <v>202603001000165</v>
       </c>
       <c r="B155" s="4" t="s">
@@ -5918,17 +5939,17 @@
       <c r="E155" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F155" s="24">
+      <c r="F155" s="23">
         <v>46092.779166666667</v>
       </c>
-      <c r="G155" s="12">
+      <c r="G155" s="11">
         <v>46122</v>
       </c>
-      <c r="H155" s="12">
+      <c r="H155" s="11">
         <v>46093</v>
       </c>
-      <c r="I155" s="13" t="str">
-        <f t="shared" si="6"/>
+      <c r="I155" s="12" t="str">
+        <f t="shared" si="7"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J155" s="3" t="s">
@@ -5936,32 +5957,32 @@
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A156" s="25">
+      <c r="A156" s="24">
         <v>202603004000166</v>
       </c>
-      <c r="B156" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" s="26" t="s">
+      <c r="B156" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D156" s="26" t="s">
+      <c r="D156" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E156" s="26" t="s">
+      <c r="E156" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="F156" s="27">
+      <c r="F156" s="26">
         <v>46093.43472222222</v>
       </c>
-      <c r="G156" s="13">
+      <c r="G156" s="12">
         <v>46123</v>
       </c>
-      <c r="H156" s="13">
+      <c r="H156" s="12">
         <v>46099</v>
       </c>
-      <c r="I156" s="13" t="str">
-        <f t="shared" si="6"/>
+      <c r="I156" s="12" t="str">
+        <f t="shared" si="7"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J156" s="2" t="s">
@@ -5969,7 +5990,7 @@
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A157" s="23">
+      <c r="A157" s="22">
         <v>202603007000167</v>
       </c>
       <c r="B157" s="4" t="s">
@@ -5984,17 +6005,17 @@
       <c r="E157" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F157" s="24">
+      <c r="F157" s="23">
         <v>46093.443055555559</v>
       </c>
-      <c r="G157" s="12">
+      <c r="G157" s="11">
         <v>46123</v>
       </c>
-      <c r="H157" s="13">
+      <c r="H157" s="12">
         <v>46118</v>
       </c>
-      <c r="I157" s="13" t="str">
-        <f t="shared" si="6"/>
+      <c r="I157" s="12" t="str">
+        <f t="shared" si="7"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J157" s="2" t="s">
@@ -6002,32 +6023,32 @@
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A158" s="25">
+      <c r="A158" s="24">
         <v>202603001000168</v>
       </c>
-      <c r="B158" s="26" t="s">
+      <c r="B158" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C158" s="26" t="s">
+      <c r="C158" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="D158" s="26" t="s">
+      <c r="D158" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="E158" s="26" t="s">
+      <c r="E158" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="F158" s="27">
+      <c r="F158" s="26">
         <v>46094.668749999997</v>
       </c>
-      <c r="G158" s="13">
+      <c r="G158" s="12">
         <v>46124</v>
       </c>
-      <c r="H158" s="13">
+      <c r="H158" s="12">
         <v>46113</v>
       </c>
-      <c r="I158" s="13" t="str">
-        <f t="shared" si="6"/>
+      <c r="I158" s="12" t="str">
+        <f t="shared" si="7"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J158" s="2" t="s">
@@ -6035,7 +6056,7 @@
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A159" s="23">
+      <c r="A159" s="22">
         <v>202603001000170</v>
       </c>
       <c r="B159" s="4" t="s">
@@ -6050,17 +6071,17 @@
       <c r="E159" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F159" s="24">
+      <c r="F159" s="23">
         <v>46097.759722222225</v>
       </c>
-      <c r="G159" s="12">
+      <c r="G159" s="11">
         <v>46127</v>
       </c>
-      <c r="H159" s="12">
+      <c r="H159" s="11">
         <v>46101</v>
       </c>
-      <c r="I159" s="13" t="str">
-        <f t="shared" si="6"/>
+      <c r="I159" s="12" t="str">
+        <f t="shared" si="7"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J159" s="2" t="s">
@@ -6068,7 +6089,7 @@
       </c>
     </row>
     <row r="160" spans="1:10" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A160" s="20">
+      <c r="A160" s="19">
         <v>202603001000171</v>
       </c>
       <c r="B160" s="9" t="s">
@@ -6083,17 +6104,17 @@
       <c r="E160" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F160" s="16">
+      <c r="F160" s="15">
         <v>46101.40347222222</v>
       </c>
       <c r="G160" s="7">
         <v>46131</v>
       </c>
-      <c r="H160" s="13">
+      <c r="H160" s="12">
         <v>46101</v>
       </c>
-      <c r="I160" s="13" t="str">
-        <f t="shared" si="6"/>
+      <c r="I160" s="12" t="str">
+        <f t="shared" si="7"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J160" s="2" t="s">
@@ -6101,32 +6122,32 @@
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A161" s="19">
+      <c r="A161" s="18">
         <v>202603007000172</v>
       </c>
-      <c r="B161" s="11" t="s">
+      <c r="B161" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C161" s="11" t="s">
+      <c r="C161" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D161" s="11" t="s">
+      <c r="D161" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="E161" s="11" t="s">
+      <c r="E161" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F161" s="14">
+      <c r="F161" s="13">
         <v>46102.166666666664</v>
       </c>
       <c r="G161" s="6">
         <v>46132</v>
       </c>
-      <c r="H161" s="13">
+      <c r="H161" s="12">
         <v>46149</v>
       </c>
-      <c r="I161" s="13" t="str">
-        <f t="shared" si="6"/>
+      <c r="I161" s="12" t="str">
+        <f t="shared" si="7"/>
         <v>Fora do Prazo</v>
       </c>
       <c r="J161" s="2" t="s">
@@ -6134,7 +6155,7 @@
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A162" s="20">
+      <c r="A162" s="19">
         <v>202603012000173</v>
       </c>
       <c r="B162" s="9" t="s">
@@ -6149,20 +6170,25 @@
       <c r="E162" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F162" s="16">
+      <c r="F162" s="15">
         <v>46104.602777777778</v>
       </c>
       <c r="G162" s="7">
         <v>46134</v>
       </c>
-      <c r="H162" s="17"/>
-      <c r="I162" s="15"/>
-      <c r="J162" s="22" t="s">
-        <v>94</v>
+      <c r="H162" s="17">
+        <v>46156</v>
+      </c>
+      <c r="I162" s="12" t="str">
+        <f t="shared" si="7"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J162" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A163" s="20">
+      <c r="A163" s="19">
         <v>202603001000174</v>
       </c>
       <c r="B163" s="9" t="s">
@@ -6177,17 +6203,17 @@
       <c r="E163" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F163" s="16">
+      <c r="F163" s="15">
         <v>46106.566666666666</v>
       </c>
       <c r="G163" s="7">
         <v>46116</v>
       </c>
-      <c r="H163" s="18">
+      <c r="H163" s="17">
         <v>46107</v>
       </c>
-      <c r="I163" s="13" t="str">
-        <f>IF(H163&lt;=G163,"Dentro do Prazo","Fora do Prazo")</f>
+      <c r="I163" s="12" t="str">
+        <f t="shared" ref="I163:I171" si="8">IF(H163&lt;=G163,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J163" s="2" t="s">
@@ -6195,32 +6221,32 @@
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A164" s="19">
+      <c r="A164" s="18">
         <v>202603001000175</v>
       </c>
-      <c r="B164" s="11" t="s">
+      <c r="B164" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C164" s="11" t="s">
+      <c r="C164" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D164" s="11" t="s">
+      <c r="D164" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="E164" s="11" t="s">
+      <c r="E164" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F164" s="14">
+      <c r="F164" s="13">
         <v>46108.686805555553</v>
       </c>
-      <c r="G164" s="28">
+      <c r="G164" s="27">
         <v>46138</v>
       </c>
-      <c r="H164" s="18">
+      <c r="H164" s="17">
         <v>46118</v>
       </c>
-      <c r="I164" s="13" t="str">
-        <f>IF(H164&lt;=G164,"Dentro do Prazo","Fora do Prazo")</f>
+      <c r="I164" s="12" t="str">
+        <f t="shared" si="8"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J164" s="2" t="s">
@@ -6228,13 +6254,13 @@
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A165" s="20">
+      <c r="A165" s="19">
         <v>202603001000179</v>
       </c>
       <c r="B165" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C165" s="21" t="s">
+      <c r="C165" s="20" t="s">
         <v>43</v>
       </c>
       <c r="D165" s="9" t="s">
@@ -6243,17 +6269,17 @@
       <c r="E165" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F165" s="16">
+      <c r="F165" s="15">
         <v>46111.413888888892</v>
       </c>
       <c r="G165" s="7">
         <v>46141</v>
       </c>
-      <c r="H165" s="18">
+      <c r="H165" s="17">
         <v>46113</v>
       </c>
-      <c r="I165" s="13" t="str">
-        <f>IF(H165&lt;=G165,"Dentro do Prazo","Fora do Prazo")</f>
+      <c r="I165" s="12" t="str">
+        <f t="shared" si="8"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J165" s="2" t="s">
@@ -6261,32 +6287,32 @@
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A166" s="19">
+      <c r="A166" s="18">
         <v>202603012000180</v>
       </c>
-      <c r="B166" s="11" t="s">
+      <c r="B166" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C166" s="11" t="s">
+      <c r="C166" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D166" s="11" t="s">
+      <c r="D166" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E166" s="11" t="s">
+      <c r="E166" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F166" s="14">
+      <c r="F166" s="13">
         <v>46111.465277777781</v>
       </c>
       <c r="G166" s="6">
         <v>46141</v>
       </c>
-      <c r="H166" s="18">
+      <c r="H166" s="17">
         <v>46119</v>
       </c>
-      <c r="I166" s="13" t="str">
-        <f>IF(H166&lt;=G166,"Dentro do Prazo","Fora do Prazo")</f>
+      <c r="I166" s="12" t="str">
+        <f t="shared" si="8"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J166" s="2" t="s">
@@ -6294,7 +6320,7 @@
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A167" s="20">
+      <c r="A167" s="19">
         <v>202603007000181</v>
       </c>
       <c r="B167" s="9" t="s">
@@ -6309,20 +6335,25 @@
       <c r="E167" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F167" s="16">
+      <c r="F167" s="15">
         <v>46111.618750000001</v>
       </c>
       <c r="G167" s="7">
         <v>46141</v>
       </c>
-      <c r="H167" s="29"/>
-      <c r="I167" s="29"/>
-      <c r="J167" s="22" t="s">
-        <v>94</v>
+      <c r="H167" s="17">
+        <v>46160</v>
+      </c>
+      <c r="I167" s="12" t="str">
+        <f t="shared" si="8"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J167" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A168" s="20">
+      <c r="A168" s="19">
         <v>202604012000182</v>
       </c>
       <c r="B168" s="9" t="s">
@@ -6337,17 +6368,17 @@
       <c r="E168" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F168" s="16">
+      <c r="F168" s="15">
         <v>46113.658333333333</v>
       </c>
       <c r="G168" s="7">
         <v>46143</v>
       </c>
-      <c r="H168" s="18">
+      <c r="H168" s="17">
         <v>46125</v>
       </c>
-      <c r="I168" s="13" t="str">
-        <f>IF(H168&lt;=G168,"Dentro do Prazo","Fora do Prazo")</f>
+      <c r="I168" s="12" t="str">
+        <f t="shared" si="8"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J168" s="2" t="s">
@@ -6355,7 +6386,7 @@
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A169" s="20">
+      <c r="A169" s="19">
         <v>202604013000183</v>
       </c>
       <c r="B169" s="9" t="s">
@@ -6370,17 +6401,17 @@
       <c r="E169" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="F169" s="16">
+      <c r="F169" s="15">
         <v>46119.414583333331</v>
       </c>
       <c r="G169" s="7">
         <v>46149</v>
       </c>
-      <c r="H169" s="18">
+      <c r="H169" s="17">
         <v>46121</v>
       </c>
-      <c r="I169" s="13" t="str">
-        <f>IF(H169&lt;=G169,"Dentro do Prazo","Fora do Prazo")</f>
+      <c r="I169" s="12" t="str">
+        <f t="shared" si="8"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J169" s="2" t="s">
@@ -6388,7 +6419,7 @@
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A170" s="20">
+      <c r="A170" s="19">
         <v>202604004000184</v>
       </c>
       <c r="B170" s="9" t="s">
@@ -6403,17 +6434,17 @@
       <c r="E170" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F170" s="16">
+      <c r="F170" s="15">
         <v>46122.668055555558</v>
       </c>
       <c r="G170" s="7">
         <v>46152</v>
       </c>
-      <c r="H170" s="18">
+      <c r="H170" s="17">
         <v>46127</v>
       </c>
-      <c r="I170" s="13" t="str">
-        <f>IF(H170&lt;=G170,"Dentro do Prazo","Fora do Prazo")</f>
+      <c r="I170" s="12" t="str">
+        <f t="shared" si="8"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J170" s="2" t="s">
@@ -6421,7 +6452,7 @@
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A171" s="20">
+      <c r="A171" s="19">
         <v>202604007000185</v>
       </c>
       <c r="B171" s="9" t="s">
@@ -6436,48 +6467,53 @@
       <c r="E171" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F171" s="16">
+      <c r="F171" s="15">
         <v>46127.354166666664</v>
       </c>
       <c r="G171" s="7">
         <v>46157</v>
       </c>
-      <c r="H171" s="17"/>
-      <c r="I171" s="15"/>
+      <c r="H171" s="17">
+        <v>46157</v>
+      </c>
+      <c r="I171" s="12" t="str">
+        <f t="shared" si="8"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J171" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A172" s="19">
+      <c r="A172" s="18">
         <v>202604011000186</v>
       </c>
-      <c r="B172" s="11" t="s">
+      <c r="B172" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C172" s="11" t="s">
+      <c r="C172" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D172" s="11" t="s">
+      <c r="D172" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E172" s="11" t="s">
+      <c r="E172" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F172" s="14">
+      <c r="F172" s="13">
         <v>46128.45416666667</v>
       </c>
       <c r="G172" s="6">
         <v>46158</v>
       </c>
-      <c r="H172" s="15"/>
-      <c r="I172" s="15"/>
-      <c r="J172" s="2" t="s">
-        <v>15</v>
+      <c r="H172" s="14"/>
+      <c r="I172" s="14"/>
+      <c r="J172" s="21" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A173" s="20">
+      <c r="A173" s="19">
         <v>202604013000187</v>
       </c>
       <c r="B173" s="9" t="s">
@@ -6492,48 +6528,58 @@
       <c r="E173" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F173" s="16">
+      <c r="F173" s="15">
         <v>46134.580555555556</v>
       </c>
       <c r="G173" s="7">
         <v>46164</v>
       </c>
-      <c r="H173" s="15"/>
-      <c r="I173" s="15"/>
+      <c r="H173" s="17">
+        <v>46161</v>
+      </c>
+      <c r="I173" s="12" t="str">
+        <f>IF(H173&lt;=G173,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J173" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A174" s="19">
+      <c r="A174" s="18">
         <v>202604013000188</v>
       </c>
-      <c r="B174" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" s="11" t="s">
+      <c r="B174" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D174" s="11" t="s">
+      <c r="D174" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="E174" s="11" t="s">
+      <c r="E174" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F174" s="14">
+      <c r="F174" s="13">
         <v>46134.617361111108</v>
       </c>
       <c r="G174" s="6">
         <v>46164</v>
       </c>
-      <c r="H174" s="15"/>
-      <c r="I174" s="15"/>
+      <c r="H174" s="17">
+        <v>46156</v>
+      </c>
+      <c r="I174" s="12" t="str">
+        <f>IF(H174&lt;=G174,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J174" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A175" s="20">
+      <c r="A175" s="19">
         <v>202604011000189</v>
       </c>
       <c r="B175" s="9" t="s">
@@ -6548,44 +6594,44 @@
       <c r="E175" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F175" s="16">
+      <c r="F175" s="15">
         <v>46134.622916666667</v>
       </c>
       <c r="G175" s="7">
         <v>46164</v>
       </c>
-      <c r="H175" s="17"/>
-      <c r="I175" s="15"/>
+      <c r="H175" s="16"/>
+      <c r="I175" s="14"/>
       <c r="J175" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A176" s="19">
+      <c r="A176" s="18">
         <v>202604003000190</v>
       </c>
-      <c r="B176" s="11" t="s">
+      <c r="B176" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C176" s="11" t="s">
+      <c r="C176" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="D176" s="11" t="s">
+      <c r="D176" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="E176" s="11" t="s">
+      <c r="E176" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="F176" s="14">
+      <c r="F176" s="13">
         <v>46134.887499999997</v>
       </c>
       <c r="G176" s="6">
         <v>46164</v>
       </c>
-      <c r="H176" s="18">
+      <c r="H176" s="17">
         <v>46135</v>
       </c>
-      <c r="I176" s="13" t="str">
+      <c r="I176" s="12" t="str">
         <f>IF(H176&lt;=G176,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
@@ -6594,7 +6640,7 @@
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A177" s="20">
+      <c r="A177" s="19">
         <v>202604012000191</v>
       </c>
       <c r="B177" s="9" t="s">
@@ -6609,16 +6655,16 @@
       <c r="E177" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F177" s="16">
+      <c r="F177" s="15">
         <v>46135.404166666667</v>
       </c>
       <c r="G177" s="7">
         <v>46165</v>
       </c>
-      <c r="H177" s="18">
+      <c r="H177" s="17">
         <v>46135</v>
       </c>
-      <c r="I177" s="13" t="str">
+      <c r="I177" s="12" t="str">
         <f>IF(H177&lt;=G177,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
@@ -6627,7 +6673,7 @@
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A178" s="20">
+      <c r="A178" s="19">
         <v>202604007000192</v>
       </c>
       <c r="B178" s="9" t="s">
@@ -6642,48 +6688,48 @@
       <c r="E178" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F178" s="16">
+      <c r="F178" s="15">
         <v>46136.633333333331</v>
       </c>
       <c r="G178" s="7">
         <v>46166</v>
       </c>
-      <c r="H178" s="15"/>
-      <c r="I178" s="15"/>
+      <c r="H178" s="14"/>
+      <c r="I178" s="14"/>
       <c r="J178" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A179" s="19">
+      <c r="A179" s="18">
         <v>202604012000193</v>
       </c>
-      <c r="B179" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" s="11" t="s">
+      <c r="B179" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D179" s="11" t="s">
+      <c r="D179" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E179" s="11" t="s">
+      <c r="E179" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F179" s="14">
+      <c r="F179" s="13">
         <v>46139.677083333336</v>
       </c>
       <c r="G179" s="6">
         <v>46169</v>
       </c>
-      <c r="H179" s="30"/>
-      <c r="I179" s="15"/>
+      <c r="H179" s="28"/>
+      <c r="I179" s="14"/>
       <c r="J179" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A180" s="20">
+      <c r="A180" s="19">
         <v>202604007000194</v>
       </c>
       <c r="B180" s="9" t="s">
@@ -6698,16 +6744,16 @@
       <c r="E180" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F180" s="16">
+      <c r="F180" s="15">
         <v>46141.64166666667</v>
       </c>
       <c r="G180" s="7">
         <v>46171</v>
       </c>
-      <c r="H180" s="18">
+      <c r="H180" s="17">
         <v>46150</v>
       </c>
-      <c r="I180" s="13" t="str">
+      <c r="I180" s="12" t="str">
         <f>IF(H180&lt;=G180,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
@@ -6716,31 +6762,31 @@
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A181" s="19">
+      <c r="A181" s="18">
         <v>202605015000195</v>
       </c>
-      <c r="B181" s="11" t="s">
+      <c r="B181" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C181" s="11" t="s">
+      <c r="C181" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D181" s="11" t="s">
+      <c r="D181" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E181" s="11" t="s">
+      <c r="E181" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F181" s="14">
+      <c r="F181" s="13">
         <v>46148.702777777777</v>
       </c>
       <c r="G181" s="6">
         <v>46178</v>
       </c>
-      <c r="H181" s="18">
+      <c r="H181" s="17">
         <v>46148</v>
       </c>
-      <c r="I181" s="13" t="str">
+      <c r="I181" s="12" t="str">
         <f>IF(H181&lt;=G181,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
@@ -6749,7 +6795,7 @@
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A182" s="20">
+      <c r="A182" s="19">
         <v>202605007000196</v>
       </c>
       <c r="B182" s="9" t="s">
@@ -6764,16 +6810,16 @@
       <c r="E182" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F182" s="16">
+      <c r="F182" s="15">
         <v>46149.384027777778</v>
       </c>
       <c r="G182" s="7">
         <v>46179</v>
       </c>
-      <c r="H182" s="18">
+      <c r="H182" s="17">
         <v>46150</v>
       </c>
-      <c r="I182" s="13" t="str">
+      <c r="I182" s="12" t="str">
         <f>IF(H182&lt;=G182,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
@@ -6782,35 +6828,35 @@
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A183" s="19">
+      <c r="A183" s="18">
         <v>202605007000197</v>
       </c>
-      <c r="B183" s="11" t="s">
+      <c r="B183" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C183" s="11" t="s">
+      <c r="C183" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D183" s="11" t="s">
+      <c r="D183" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E183" s="11" t="s">
+      <c r="E183" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F183" s="14">
+      <c r="F183" s="13">
         <v>46149.470833333333</v>
       </c>
       <c r="G183" s="6">
         <v>46179</v>
       </c>
-      <c r="H183" s="15"/>
-      <c r="I183" s="15"/>
+      <c r="H183" s="14"/>
+      <c r="I183" s="14"/>
       <c r="J183" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A184" s="20">
+      <c r="A184" s="19">
         <v>202605001000198</v>
       </c>
       <c r="B184" s="9" t="s">
@@ -6825,44 +6871,44 @@
       <c r="E184" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F184" s="16">
+      <c r="F184" s="15">
         <v>46149.476388888892</v>
       </c>
       <c r="G184" s="7">
         <v>46179</v>
       </c>
-      <c r="H184" s="15"/>
-      <c r="I184" s="15"/>
+      <c r="H184" s="14"/>
+      <c r="I184" s="14"/>
       <c r="J184" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A185" s="19">
+      <c r="A185" s="18">
         <v>202605007000199</v>
       </c>
-      <c r="B185" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" s="11" t="s">
+      <c r="B185" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D185" s="11" t="s">
+      <c r="D185" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E185" s="11" t="s">
+      <c r="E185" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F185" s="14">
+      <c r="F185" s="13">
         <v>46149.479861111111</v>
       </c>
       <c r="G185" s="6">
         <v>46179</v>
       </c>
-      <c r="H185" s="18">
+      <c r="H185" s="17">
         <v>46150</v>
       </c>
-      <c r="I185" s="13" t="str">
+      <c r="I185" s="12" t="str">
         <f>IF(H185&lt;=G185,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
@@ -6871,7 +6917,7 @@
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A186" s="20">
+      <c r="A186" s="19">
         <v>202605013000200</v>
       </c>
       <c r="B186" s="9" t="s">
@@ -6886,20 +6932,137 @@
       <c r="E186" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="F186" s="16">
+      <c r="F186" s="15">
         <v>46150.495138888888</v>
       </c>
       <c r="G186" s="7">
         <v>46180</v>
       </c>
-      <c r="H186" s="15"/>
-      <c r="I186" s="15"/>
+      <c r="H186" s="14"/>
+      <c r="I186" s="14"/>
       <c r="J186" s="2" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A187" s="18">
+        <v>202605011000201</v>
+      </c>
+      <c r="B187" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C187" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D187" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E187" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F187" s="13">
+        <v>46156.37222222222</v>
+      </c>
+      <c r="G187" s="6">
+        <v>46186</v>
+      </c>
+      <c r="H187" s="28"/>
+      <c r="I187" s="14"/>
+      <c r="J187" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A188" s="19">
+        <v>202605007000202</v>
+      </c>
+      <c r="B188" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C188" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D188" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E188" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F188" s="15">
+        <v>46157.449305555558</v>
+      </c>
+      <c r="G188" s="7">
+        <v>46187</v>
+      </c>
+      <c r="H188" s="14"/>
+      <c r="I188" s="14"/>
+      <c r="J188" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A189" s="18">
+        <v>202605007000203</v>
+      </c>
+      <c r="B189" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C189" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D189" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E189" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F189" s="13">
+        <v>46160.354861111111</v>
+      </c>
+      <c r="G189" s="6">
+        <v>46190</v>
+      </c>
+      <c r="H189" s="14"/>
+      <c r="I189" s="14"/>
+      <c r="J189" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A190" s="19">
+        <v>202605013000204</v>
+      </c>
+      <c r="B190" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C190" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D190" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E190" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F190" s="15">
+        <v>46160.613888888889</v>
+      </c>
+      <c r="G190" s="7">
+        <v>46190</v>
+      </c>
+      <c r="H190" s="17">
+        <v>46160</v>
+      </c>
+      <c r="I190" s="12" t="str">
+        <f>IF(H190&lt;=G190,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J190" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J186" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
+  <autoFilter ref="A1:J190" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J159">
     <sortCondition ref="F1:F159"/>
   </sortState>

--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED1F91B-2105-4275-8B98-658D58D62A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDC33DE-7935-4DAA-A177-C478CEA0E1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Dash" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$194</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="110">
   <si>
     <t>Protocolo</t>
   </si>
@@ -352,6 +352,12 @@
   </si>
   <si>
     <t>Limpeza de Vias Públicas</t>
+  </si>
+  <si>
+    <t>Vida funcional do servidor público</t>
+  </si>
+  <si>
+    <t>Programas habitacionais</t>
   </si>
 </sst>
 </file>
@@ -466,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -542,6 +548,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -858,7 +867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J190"/>
+  <dimension ref="A1:J194"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -5469,7 +5478,7 @@
         <v>46125</v>
       </c>
       <c r="I140" s="20" t="str">
-        <f t="shared" ref="I140" si="5">IF(H140&lt;=G140,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I140:I141" si="5">IF(H140&lt;=G140,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Fora do Prazo</v>
       </c>
       <c r="J140" s="2" t="s">
@@ -5498,10 +5507,15 @@
       <c r="G141" s="6">
         <v>46098</v>
       </c>
-      <c r="H141" s="20"/>
-      <c r="I141" s="14"/>
-      <c r="J141" s="21" t="s">
-        <v>94</v>
+      <c r="H141" s="7">
+        <v>46125</v>
+      </c>
+      <c r="I141" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J141" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -6602,8 +6616,8 @@
       </c>
       <c r="H175" s="16"/>
       <c r="I175" s="14"/>
-      <c r="J175" s="2" t="s">
-        <v>15</v>
+      <c r="J175" s="21" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -6694,10 +6708,15 @@
       <c r="G178" s="7">
         <v>46166</v>
       </c>
-      <c r="H178" s="14"/>
-      <c r="I178" s="14"/>
+      <c r="H178" s="29">
+        <v>46167</v>
+      </c>
+      <c r="I178" s="12" t="str">
+        <f>IF(H178&lt;=G178,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Fora do Prazo</v>
+      </c>
       <c r="J178" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
@@ -6724,8 +6743,8 @@
       </c>
       <c r="H179" s="28"/>
       <c r="I179" s="14"/>
-      <c r="J179" s="2" t="s">
-        <v>15</v>
+      <c r="J179" s="21" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -6877,10 +6896,15 @@
       <c r="G184" s="7">
         <v>46179</v>
       </c>
-      <c r="H184" s="14"/>
-      <c r="I184" s="14"/>
+      <c r="H184" s="29">
+        <v>46167</v>
+      </c>
+      <c r="I184" s="12" t="str">
+        <f>IF(H184&lt;=G184,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J184" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
@@ -7061,8 +7085,130 @@
         <v>19</v>
       </c>
     </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A191" s="18">
+        <v>202605011000205</v>
+      </c>
+      <c r="B191" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C191" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D191" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E191" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F191" s="13">
+        <v>46161.55</v>
+      </c>
+      <c r="G191" s="6">
+        <v>46191</v>
+      </c>
+      <c r="H191" s="29">
+        <v>46167</v>
+      </c>
+      <c r="I191" s="12" t="str">
+        <f>IF(H191&lt;=G191,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J191" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A192" s="19">
+        <v>202605001000206</v>
+      </c>
+      <c r="B192" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C192" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D192" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E192" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F192" s="15">
+        <v>46162.354861111111</v>
+      </c>
+      <c r="G192" s="7">
+        <v>46192</v>
+      </c>
+      <c r="H192" s="14"/>
+      <c r="I192" s="14"/>
+      <c r="J192" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A193" s="18">
+        <v>202605003000207</v>
+      </c>
+      <c r="B193" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D193" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="E193" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F193" s="13">
+        <v>46162.605555555558</v>
+      </c>
+      <c r="G193" s="6">
+        <v>46192</v>
+      </c>
+      <c r="H193" s="29">
+        <v>46167</v>
+      </c>
+      <c r="I193" s="12" t="str">
+        <f>IF(H193&lt;=G193,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J193" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A194" s="19">
+        <v>202605011000208</v>
+      </c>
+      <c r="B194" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C194" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D194" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E194" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F194" s="15">
+        <v>46162.652083333334</v>
+      </c>
+      <c r="G194" s="7">
+        <v>46192</v>
+      </c>
+      <c r="H194" s="14"/>
+      <c r="I194" s="14"/>
+      <c r="J194" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J190" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
+  <autoFilter ref="A1:J194" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J159">
     <sortCondition ref="F1:F159"/>
   </sortState>

--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDC33DE-7935-4DAA-A177-C478CEA0E1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61664B58-44C1-4073-B561-C483397F2E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Dash" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$196</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="112">
   <si>
     <t>Protocolo</t>
   </si>
@@ -358,13 +358,19 @@
   </si>
   <si>
     <t>Programas habitacionais</t>
+  </si>
+  <si>
+    <t>Transporte público</t>
+  </si>
+  <si>
+    <t>Licitação</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -403,6 +409,18 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -472,7 +490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -551,6 +569,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -867,7 +900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J194"/>
+  <dimension ref="A1:J197"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -5446,10 +5479,15 @@
       <c r="G139" s="6">
         <v>46096</v>
       </c>
-      <c r="H139" s="20"/>
-      <c r="I139" s="14"/>
-      <c r="J139" s="21" t="s">
-        <v>94</v>
+      <c r="H139" s="7">
+        <v>46168</v>
+      </c>
+      <c r="I139" s="20" t="str">
+        <f t="shared" ref="I139:I141" si="5">IF(H139&lt;=G139,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J139" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -5478,7 +5516,7 @@
         <v>46125</v>
       </c>
       <c r="I140" s="20" t="str">
-        <f t="shared" ref="I140:I141" si="5">IF(H140&lt;=G140,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="5"/>
         <v>Fora do Prazo</v>
       </c>
       <c r="J140" s="2" t="s">
@@ -6646,7 +6684,7 @@
         <v>46135</v>
       </c>
       <c r="I176" s="12" t="str">
-        <f>IF(H176&lt;=G176,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I176:I182" si="9">IF(H176&lt;=G176,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J176" s="2" t="s">
@@ -6679,7 +6717,7 @@
         <v>46135</v>
       </c>
       <c r="I177" s="12" t="str">
-        <f>IF(H177&lt;=G177,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="9"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J177" s="2" t="s">
@@ -6712,7 +6750,7 @@
         <v>46167</v>
       </c>
       <c r="I178" s="12" t="str">
-        <f>IF(H178&lt;=G178,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="9"/>
         <v>Fora do Prazo</v>
       </c>
       <c r="J178" s="2" t="s">
@@ -6741,10 +6779,15 @@
       <c r="G179" s="6">
         <v>46169</v>
       </c>
-      <c r="H179" s="28"/>
-      <c r="I179" s="14"/>
-      <c r="J179" s="21" t="s">
-        <v>94</v>
+      <c r="H179" s="29">
+        <v>46141</v>
+      </c>
+      <c r="I179" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J179" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -6773,7 +6816,7 @@
         <v>46150</v>
       </c>
       <c r="I180" s="12" t="str">
-        <f>IF(H180&lt;=G180,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="9"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J180" s="2" t="s">
@@ -6806,7 +6849,7 @@
         <v>46148</v>
       </c>
       <c r="I181" s="12" t="str">
-        <f>IF(H181&lt;=G181,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="9"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J181" s="2" t="s">
@@ -6839,7 +6882,7 @@
         <v>46150</v>
       </c>
       <c r="I182" s="12" t="str">
-        <f>IF(H182&lt;=G182,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="9"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J182" s="2" t="s">
@@ -6962,10 +7005,15 @@
       <c r="G186" s="7">
         <v>46180</v>
       </c>
-      <c r="H186" s="14"/>
-      <c r="I186" s="14"/>
+      <c r="H186" s="17">
+        <v>46153</v>
+      </c>
+      <c r="I186" s="12" t="str">
+        <f>IF(H186&lt;=G186,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J186" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
@@ -7207,8 +7255,97 @@
         <v>15</v>
       </c>
     </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A195" s="18">
+        <v>202605007000209</v>
+      </c>
+      <c r="B195" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D195" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E195" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F195" s="13">
+        <v>46164.400694444441</v>
+      </c>
+      <c r="G195" s="6">
+        <v>46194</v>
+      </c>
+      <c r="H195" s="28"/>
+      <c r="I195" s="14"/>
+      <c r="J195" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A196" s="19">
+        <v>202605007000210</v>
+      </c>
+      <c r="B196" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C196" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D196" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E196" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F196" s="15">
+        <v>46164.458333333336</v>
+      </c>
+      <c r="G196" s="7">
+        <v>46194</v>
+      </c>
+      <c r="H196" s="16"/>
+      <c r="I196" s="14"/>
+      <c r="J196" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A197" s="33">
+        <v>202605001000211</v>
+      </c>
+      <c r="B197" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C197" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D197" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="E197" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F197" s="31">
+        <v>46168.666666666664</v>
+      </c>
+      <c r="G197" s="32">
+        <v>46198</v>
+      </c>
+      <c r="H197" s="34">
+        <v>46168</v>
+      </c>
+      <c r="I197" s="12" t="str">
+        <f>IF(H197&lt;=G197,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J197" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J194" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
+  <autoFilter ref="A1:J196" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J159">
     <sortCondition ref="F1:F159"/>
   </sortState>

--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61664B58-44C1-4073-B561-C483397F2E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02EFC4AB-C295-4654-8849-223F45842579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="113">
   <si>
     <t>Protocolo</t>
   </si>
@@ -364,6 +364,9 @@
   </si>
   <si>
     <t>Licitação</t>
+  </si>
+  <si>
+    <t>Construção irregular</t>
   </si>
 </sst>
 </file>
@@ -900,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J197"/>
+  <dimension ref="A1:J201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -5582,7 +5585,7 @@
         <v>46071</v>
       </c>
       <c r="I142" s="12" t="str">
-        <f t="shared" ref="I142:I147" si="6">IF(H142&lt;=G142,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I142:I148" si="6">IF(H142&lt;=G142,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J142" s="2" t="s">
@@ -5776,10 +5779,15 @@
       <c r="G148" s="7">
         <v>46105</v>
       </c>
-      <c r="H148" s="9"/>
-      <c r="I148" s="14"/>
-      <c r="J148" s="21" t="s">
-        <v>94</v>
+      <c r="H148" s="7">
+        <v>46176</v>
+      </c>
+      <c r="I148" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -6265,7 +6273,7 @@
         <v>46107</v>
       </c>
       <c r="I163" s="12" t="str">
-        <f t="shared" ref="I163:I171" si="8">IF(H163&lt;=G163,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I163:I172" si="8">IF(H163&lt;=G163,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J163" s="2" t="s">
@@ -6558,10 +6566,15 @@
       <c r="G172" s="6">
         <v>46158</v>
       </c>
-      <c r="H172" s="14"/>
-      <c r="I172" s="14"/>
-      <c r="J172" s="21" t="s">
-        <v>94</v>
+      <c r="H172" s="17">
+        <v>46176</v>
+      </c>
+      <c r="I172" s="12" t="str">
+        <f t="shared" si="8"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J172" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
@@ -6652,10 +6665,15 @@
       <c r="G175" s="7">
         <v>46164</v>
       </c>
-      <c r="H175" s="16"/>
-      <c r="I175" s="14"/>
-      <c r="J175" s="21" t="s">
-        <v>94</v>
+      <c r="H175" s="17">
+        <v>46176</v>
+      </c>
+      <c r="I175" s="12" t="str">
+        <f>IF(H175&lt;=G175,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J175" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -6684,7 +6702,7 @@
         <v>46135</v>
       </c>
       <c r="I176" s="12" t="str">
-        <f t="shared" ref="I176:I182" si="9">IF(H176&lt;=G176,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I176:I183" si="9">IF(H176&lt;=G176,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J176" s="2" t="s">
@@ -6911,10 +6929,15 @@
       <c r="G183" s="6">
         <v>46179</v>
       </c>
-      <c r="H183" s="14"/>
-      <c r="I183" s="14"/>
+      <c r="H183" s="17">
+        <v>46176</v>
+      </c>
+      <c r="I183" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J183" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
@@ -7038,10 +7061,15 @@
       <c r="G187" s="6">
         <v>46186</v>
       </c>
-      <c r="H187" s="28"/>
-      <c r="I187" s="14"/>
+      <c r="H187" s="17">
+        <v>46176</v>
+      </c>
+      <c r="I187" s="12" t="str">
+        <f>IF(H187&lt;=G187,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J187" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
@@ -7342,6 +7370,118 @@
       </c>
       <c r="J197" s="2" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A198" s="18">
+        <v>202605007000212</v>
+      </c>
+      <c r="B198" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C198" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D198" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E198" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F198" s="13">
+        <v>46169.625694444447</v>
+      </c>
+      <c r="G198" s="6">
+        <v>46199</v>
+      </c>
+      <c r="H198" s="28"/>
+      <c r="I198" s="14"/>
+      <c r="J198" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A199" s="19">
+        <v>202605007000213</v>
+      </c>
+      <c r="B199" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C199" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D199" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E199" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F199" s="15">
+        <v>46171.566666666666</v>
+      </c>
+      <c r="G199" s="7">
+        <v>46201</v>
+      </c>
+      <c r="H199" s="14"/>
+      <c r="I199" s="14"/>
+      <c r="J199" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A200" s="18">
+        <v>202606012000214</v>
+      </c>
+      <c r="B200" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D200" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E200" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F200" s="13">
+        <v>46176.40625</v>
+      </c>
+      <c r="G200" s="6">
+        <v>46206</v>
+      </c>
+      <c r="H200" s="14"/>
+      <c r="I200" s="14"/>
+      <c r="J200" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A201" s="19">
+        <v>202606011000215</v>
+      </c>
+      <c r="B201" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D201" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E201" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F201" s="15">
+        <v>46176.411111111112</v>
+      </c>
+      <c r="G201" s="7">
+        <v>46206</v>
+      </c>
+      <c r="H201" s="14"/>
+      <c r="I201" s="14"/>
+      <c r="J201" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02EFC4AB-C295-4654-8849-223F45842579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7D8472-32EE-4B0D-8EAC-D5DFA68352F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Dash" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$206</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="114">
   <si>
     <t>Protocolo</t>
   </si>
@@ -367,6 +367,9 @@
   </si>
   <si>
     <t>Construção irregular</t>
+  </si>
+  <si>
+    <t>Poda de árvore em áreas públicas</t>
   </si>
 </sst>
 </file>
@@ -903,7 +906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J201"/>
+  <dimension ref="A1:J206"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -7096,8 +7099,8 @@
       </c>
       <c r="H188" s="14"/>
       <c r="I188" s="14"/>
-      <c r="J188" s="2" t="s">
-        <v>15</v>
+      <c r="J188" s="21" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
@@ -7394,10 +7397,15 @@
       <c r="G198" s="6">
         <v>46199</v>
       </c>
-      <c r="H198" s="28"/>
-      <c r="I198" s="14"/>
+      <c r="H198" s="29">
+        <v>46181</v>
+      </c>
+      <c r="I198" s="12" t="str">
+        <f>IF(H198&lt;=G198,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J198" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
@@ -7484,8 +7492,153 @@
         <v>15</v>
       </c>
     </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A202" s="19">
+        <v>202606007000216</v>
+      </c>
+      <c r="B202" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C202" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D202" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E202" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F202" s="15">
+        <v>46181.669444444444</v>
+      </c>
+      <c r="G202" s="7">
+        <v>46211</v>
+      </c>
+      <c r="H202" s="17">
+        <v>46181</v>
+      </c>
+      <c r="I202" s="12" t="str">
+        <f>IF(H202&lt;=G202,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J202" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A203" s="18">
+        <v>202606012000217</v>
+      </c>
+      <c r="B203" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C203" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D203" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E203" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F203" s="13">
+        <v>46183.588888888888</v>
+      </c>
+      <c r="G203" s="6">
+        <v>46213</v>
+      </c>
+      <c r="H203" s="14"/>
+      <c r="I203" s="14"/>
+      <c r="J203" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A204" s="19">
+        <v>202606009000218</v>
+      </c>
+      <c r="B204" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C204" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D204" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E204" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F204" s="15">
+        <v>46183.612500000003</v>
+      </c>
+      <c r="G204" s="7">
+        <v>46213</v>
+      </c>
+      <c r="H204" s="16"/>
+      <c r="I204" s="14"/>
+      <c r="J204" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A205" s="18">
+        <v>202606016000219</v>
+      </c>
+      <c r="B205" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C205" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D205" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E205" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F205" s="13">
+        <v>46184.546527777777</v>
+      </c>
+      <c r="G205" s="6">
+        <v>46214</v>
+      </c>
+      <c r="H205" s="28"/>
+      <c r="I205" s="14"/>
+      <c r="J205" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A206" s="19">
+        <v>202606002000220</v>
+      </c>
+      <c r="B206" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C206" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D206" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E206" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F206" s="15">
+        <v>46185.423611111109</v>
+      </c>
+      <c r="G206" s="7">
+        <v>46215</v>
+      </c>
+      <c r="H206" s="14"/>
+      <c r="I206" s="14"/>
+      <c r="J206" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J196" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
+  <autoFilter ref="A1:J206" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J159">
     <sortCondition ref="F1:F159"/>
   </sortState>

--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7D8472-32EE-4B0D-8EAC-D5DFA68352F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5674A29-C10A-4DBF-A541-4C8686B96E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Dash" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$214</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="116">
   <si>
     <t>Protocolo</t>
   </si>
@@ -370,6 +370,12 @@
   </si>
   <si>
     <t>Poda de árvore em áreas públicas</t>
+  </si>
+  <si>
+    <t>Consultas/ especialidade</t>
+  </si>
+  <si>
+    <t>Mulher</t>
   </si>
 </sst>
 </file>
@@ -496,7 +502,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -537,9 +543,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="22" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -906,7 +909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J206"/>
+  <dimension ref="A1:J214"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -953,7 +956,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="19">
+      <c r="A2" s="18">
         <v>202509001000009</v>
       </c>
       <c r="B2" s="9" t="s">
@@ -986,7 +989,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="18">
+      <c r="A3" s="17">
         <v>202509002000010</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -1019,7 +1022,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="19">
+      <c r="A4" s="18">
         <v>202509001000011</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -1052,7 +1055,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="18">
+      <c r="A5" s="17">
         <v>202509001000012</v>
       </c>
       <c r="B5" s="10" t="s">
@@ -1085,7 +1088,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>202509011000013</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -1118,7 +1121,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="18">
+      <c r="A7" s="17">
         <v>202509011000014</v>
       </c>
       <c r="B7" s="10" t="s">
@@ -1151,7 +1154,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="19">
+      <c r="A8" s="18">
         <v>202509001000015</v>
       </c>
       <c r="B8" s="9" t="s">
@@ -1184,7 +1187,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="18">
+      <c r="A9" s="17">
         <v>202509009000016</v>
       </c>
       <c r="B9" s="10" t="s">
@@ -1217,7 +1220,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="19">
+      <c r="A10" s="18">
         <v>202509001000017</v>
       </c>
       <c r="B10" s="9" t="s">
@@ -1250,7 +1253,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="18">
+      <c r="A11" s="17">
         <v>202509003000018</v>
       </c>
       <c r="B11" s="10" t="s">
@@ -1283,7 +1286,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="19">
+      <c r="A12" s="18">
         <v>202509011000019</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -1316,7 +1319,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="18">
+      <c r="A13" s="17">
         <v>202509011000020</v>
       </c>
       <c r="B13" s="10" t="s">
@@ -1349,7 +1352,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="19">
+      <c r="A14" s="18">
         <v>202509007000021</v>
       </c>
       <c r="B14" s="9" t="s">
@@ -1373,7 +1376,7 @@
       <c r="H14" s="7">
         <v>45924</v>
       </c>
-      <c r="I14" s="20" t="str">
+      <c r="I14" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1382,7 +1385,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="18">
+      <c r="A15" s="17">
         <v>202509004000022</v>
       </c>
       <c r="B15" s="10" t="s">
@@ -1406,7 +1409,7 @@
       <c r="H15" s="8">
         <v>45924</v>
       </c>
-      <c r="I15" s="20" t="str">
+      <c r="I15" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1415,7 +1418,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="19">
+      <c r="A16" s="18">
         <v>202509001000023</v>
       </c>
       <c r="B16" s="9" t="s">
@@ -1439,7 +1442,7 @@
       <c r="H16" s="8">
         <v>45924</v>
       </c>
-      <c r="I16" s="20" t="str">
+      <c r="I16" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1448,7 +1451,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="18">
+      <c r="A17" s="17">
         <v>202509011000024</v>
       </c>
       <c r="B17" s="10" t="s">
@@ -1472,7 +1475,7 @@
       <c r="H17" s="6">
         <v>45968</v>
       </c>
-      <c r="I17" s="20" t="str">
+      <c r="I17" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Fora do Prazo</v>
       </c>
@@ -1481,7 +1484,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="19">
+      <c r="A18" s="18">
         <v>202509011000025</v>
       </c>
       <c r="B18" s="9" t="s">
@@ -1505,7 +1508,7 @@
       <c r="H18" s="7">
         <v>45930</v>
       </c>
-      <c r="I18" s="20" t="str">
+      <c r="I18" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1514,7 +1517,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="18">
+      <c r="A19" s="17">
         <v>202509015000026</v>
       </c>
       <c r="B19" s="10" t="s">
@@ -1538,7 +1541,7 @@
       <c r="H19" s="6">
         <v>45930</v>
       </c>
-      <c r="I19" s="20" t="str">
+      <c r="I19" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1547,7 +1550,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="19">
+      <c r="A20" s="18">
         <v>202509001000027</v>
       </c>
       <c r="B20" s="9" t="s">
@@ -1571,7 +1574,7 @@
       <c r="H20" s="7">
         <v>45937</v>
       </c>
-      <c r="I20" s="20" t="str">
+      <c r="I20" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1580,7 +1583,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="18">
+      <c r="A21" s="17">
         <v>202510011000028</v>
       </c>
       <c r="B21" s="10" t="s">
@@ -1604,7 +1607,7 @@
       <c r="H21" s="6">
         <v>45939</v>
       </c>
-      <c r="I21" s="20" t="str">
+      <c r="I21" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1613,7 +1616,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="19">
+      <c r="A22" s="18">
         <v>202510009000029</v>
       </c>
       <c r="B22" s="9" t="s">
@@ -1637,7 +1640,7 @@
       <c r="H22" s="8">
         <v>45964</v>
       </c>
-      <c r="I22" s="20" t="str">
+      <c r="I22" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Fora do Prazo</v>
       </c>
@@ -1646,7 +1649,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="18">
+      <c r="A23" s="17">
         <v>202510001000030</v>
       </c>
       <c r="B23" s="10" t="s">
@@ -1670,7 +1673,7 @@
       <c r="H23" s="8">
         <v>45958</v>
       </c>
-      <c r="I23" s="20" t="str">
+      <c r="I23" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1679,7 +1682,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="19">
+      <c r="A24" s="18">
         <v>202510001000031</v>
       </c>
       <c r="B24" s="9" t="s">
@@ -1703,7 +1706,7 @@
       <c r="H24" s="8">
         <v>45958</v>
       </c>
-      <c r="I24" s="20" t="str">
+      <c r="I24" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1712,7 +1715,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="18">
+      <c r="A25" s="17">
         <v>202510001000032</v>
       </c>
       <c r="B25" s="10" t="s">
@@ -1736,7 +1739,7 @@
       <c r="H25" s="6">
         <v>45938</v>
       </c>
-      <c r="I25" s="20" t="str">
+      <c r="I25" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1745,7 +1748,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="19">
+      <c r="A26" s="18">
         <v>202510001000033</v>
       </c>
       <c r="B26" s="9" t="s">
@@ -1769,7 +1772,7 @@
       <c r="H26" s="7">
         <v>45933</v>
       </c>
-      <c r="I26" s="20" t="str">
+      <c r="I26" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1778,7 +1781,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="18">
+      <c r="A27" s="17">
         <v>202510007000034</v>
       </c>
       <c r="B27" s="10" t="s">
@@ -1802,7 +1805,7 @@
       <c r="H27" s="8">
         <v>45937</v>
       </c>
-      <c r="I27" s="20" t="str">
+      <c r="I27" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1811,7 +1814,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="19">
+      <c r="A28" s="18">
         <v>202510001000035</v>
       </c>
       <c r="B28" s="9" t="s">
@@ -1835,7 +1838,7 @@
       <c r="H28" s="7">
         <v>45937</v>
       </c>
-      <c r="I28" s="20" t="str">
+      <c r="I28" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1844,7 +1847,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="18">
+      <c r="A29" s="17">
         <v>202510015000036</v>
       </c>
       <c r="B29" s="10" t="s">
@@ -1868,7 +1871,7 @@
       <c r="H29" s="6">
         <v>45965</v>
       </c>
-      <c r="I29" s="20" t="str">
+      <c r="I29" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1877,7 +1880,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="19">
+      <c r="A30" s="18">
         <v>202510011000037</v>
       </c>
       <c r="B30" s="9" t="s">
@@ -1901,7 +1904,7 @@
       <c r="H30" s="7">
         <v>46155</v>
       </c>
-      <c r="I30" s="20" t="str">
+      <c r="I30" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Fora do Prazo</v>
       </c>
@@ -1910,7 +1913,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="18">
+      <c r="A31" s="17">
         <v>202510003000038</v>
       </c>
       <c r="B31" s="10" t="s">
@@ -1934,7 +1937,7 @@
       <c r="H31" s="8">
         <v>45960</v>
       </c>
-      <c r="I31" s="20" t="str">
+      <c r="I31" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1943,7 +1946,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="19">
+      <c r="A32" s="18">
         <v>202510011000039</v>
       </c>
       <c r="B32" s="9" t="s">
@@ -1967,7 +1970,7 @@
       <c r="H32" s="8">
         <v>45953</v>
       </c>
-      <c r="I32" s="20" t="str">
+      <c r="I32" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -1976,7 +1979,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="18">
+      <c r="A33" s="17">
         <v>202510004000040</v>
       </c>
       <c r="B33" s="10" t="s">
@@ -2000,7 +2003,7 @@
       <c r="H33" s="8">
         <v>45937</v>
       </c>
-      <c r="I33" s="20" t="str">
+      <c r="I33" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2009,7 +2012,7 @@
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="19">
+      <c r="A34" s="18">
         <v>202510008000041</v>
       </c>
       <c r="B34" s="9" t="s">
@@ -2033,7 +2036,7 @@
       <c r="H34" s="8">
         <v>45938</v>
       </c>
-      <c r="I34" s="20" t="str">
+      <c r="I34" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2042,7 +2045,7 @@
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="18">
+      <c r="A35" s="17">
         <v>202510009000042</v>
       </c>
       <c r="B35" s="10" t="s">
@@ -2066,7 +2069,7 @@
       <c r="H35" s="6">
         <v>45960</v>
       </c>
-      <c r="I35" s="20" t="str">
+      <c r="I35" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2075,7 +2078,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="19">
+      <c r="A36" s="18">
         <v>202510011000043</v>
       </c>
       <c r="B36" s="9" t="s">
@@ -2099,7 +2102,7 @@
       <c r="H36" s="7">
         <v>46155</v>
       </c>
-      <c r="I36" s="20" t="str">
+      <c r="I36" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Fora do Prazo</v>
       </c>
@@ -2108,7 +2111,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="18">
+      <c r="A37" s="17">
         <v>202510004000044</v>
       </c>
       <c r="B37" s="10" t="s">
@@ -2132,7 +2135,7 @@
       <c r="H37" s="8">
         <v>45939</v>
       </c>
-      <c r="I37" s="20" t="str">
+      <c r="I37" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2141,7 +2144,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="19">
+      <c r="A38" s="18">
         <v>202510001000045</v>
       </c>
       <c r="B38" s="9" t="s">
@@ -2165,7 +2168,7 @@
       <c r="H38" s="7">
         <v>45943</v>
       </c>
-      <c r="I38" s="20" t="str">
+      <c r="I38" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2174,7 +2177,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="18">
+      <c r="A39" s="17">
         <v>202510011000046</v>
       </c>
       <c r="B39" s="10" t="s">
@@ -2198,7 +2201,7 @@
       <c r="H39" s="8">
         <v>45943</v>
       </c>
-      <c r="I39" s="20" t="str">
+      <c r="I39" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2207,7 +2210,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="19">
+      <c r="A40" s="18">
         <v>202510004000047</v>
       </c>
       <c r="B40" s="9" t="s">
@@ -2231,7 +2234,7 @@
       <c r="H40" s="7">
         <v>45943</v>
       </c>
-      <c r="I40" s="20" t="str">
+      <c r="I40" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2240,7 +2243,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="18">
+      <c r="A41" s="17">
         <v>202510001000048</v>
       </c>
       <c r="B41" s="10" t="s">
@@ -2264,7 +2267,7 @@
       <c r="H41" s="6">
         <v>45940</v>
       </c>
-      <c r="I41" s="20" t="str">
+      <c r="I41" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2273,7 +2276,7 @@
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="19">
+      <c r="A42" s="18">
         <v>202510007000049</v>
       </c>
       <c r="B42" s="9" t="s">
@@ -2297,7 +2300,7 @@
       <c r="H42" s="7">
         <v>45943</v>
       </c>
-      <c r="I42" s="20" t="str">
+      <c r="I42" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2306,7 +2309,7 @@
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="18">
+      <c r="A43" s="17">
         <v>202510001000050</v>
       </c>
       <c r="B43" s="10" t="s">
@@ -2330,7 +2333,7 @@
       <c r="H43" s="6">
         <v>45996</v>
       </c>
-      <c r="I43" s="20" t="str">
+      <c r="I43" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Fora do Prazo</v>
       </c>
@@ -2339,7 +2342,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="19">
+      <c r="A44" s="18">
         <v>202510001000051</v>
       </c>
       <c r="B44" s="9" t="s">
@@ -2363,7 +2366,7 @@
       <c r="H44" s="7">
         <v>45944</v>
       </c>
-      <c r="I44" s="20" t="str">
+      <c r="I44" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2372,7 +2375,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="18">
+      <c r="A45" s="17">
         <v>202510001000052</v>
       </c>
       <c r="B45" s="10" t="s">
@@ -2396,7 +2399,7 @@
       <c r="H45" s="8">
         <v>45960</v>
       </c>
-      <c r="I45" s="20" t="str">
+      <c r="I45" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2405,7 +2408,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="19">
+      <c r="A46" s="18">
         <v>202510001000053</v>
       </c>
       <c r="B46" s="9" t="s">
@@ -2429,7 +2432,7 @@
       <c r="H46" s="8">
         <v>45961</v>
       </c>
-      <c r="I46" s="20" t="str">
+      <c r="I46" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2438,7 +2441,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="18">
+      <c r="A47" s="17">
         <v>202510007000054</v>
       </c>
       <c r="B47" s="10" t="s">
@@ -2462,7 +2465,7 @@
       <c r="H47" s="8">
         <v>45953</v>
       </c>
-      <c r="I47" s="20" t="str">
+      <c r="I47" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2471,7 +2474,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="19">
+      <c r="A48" s="18">
         <v>202510015000055</v>
       </c>
       <c r="B48" s="9" t="s">
@@ -2495,7 +2498,7 @@
       <c r="H48" s="8">
         <v>45953</v>
       </c>
-      <c r="I48" s="20" t="str">
+      <c r="I48" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2504,7 +2507,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="18">
+      <c r="A49" s="17">
         <v>202510011000056</v>
       </c>
       <c r="B49" s="10" t="s">
@@ -2528,7 +2531,7 @@
       <c r="H49" s="6">
         <v>45986</v>
       </c>
-      <c r="I49" s="20" t="str">
+      <c r="I49" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Fora do Prazo</v>
       </c>
@@ -2537,7 +2540,7 @@
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="19">
+      <c r="A50" s="18">
         <v>202510009000057</v>
       </c>
       <c r="B50" s="9" t="s">
@@ -2561,7 +2564,7 @@
       <c r="H50" s="8">
         <v>45953</v>
       </c>
-      <c r="I50" s="20" t="str">
+      <c r="I50" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2570,7 +2573,7 @@
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="18">
+      <c r="A51" s="17">
         <v>202510004000058</v>
       </c>
       <c r="B51" s="10" t="s">
@@ -2594,7 +2597,7 @@
       <c r="H51" s="6">
         <v>45951</v>
       </c>
-      <c r="I51" s="20" t="str">
+      <c r="I51" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2603,7 +2606,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="19">
+      <c r="A52" s="18">
         <v>202510001000059</v>
       </c>
       <c r="B52" s="9" t="s">
@@ -2627,7 +2630,7 @@
       <c r="H52" s="7">
         <v>45972</v>
       </c>
-      <c r="I52" s="20" t="str">
+      <c r="I52" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2636,7 +2639,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="18">
+      <c r="A53" s="17">
         <v>202510001000060</v>
       </c>
       <c r="B53" s="10" t="s">
@@ -2660,7 +2663,7 @@
       <c r="H53" s="6">
         <v>45996</v>
       </c>
-      <c r="I53" s="20" t="str">
+      <c r="I53" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Fora do Prazo</v>
       </c>
@@ -2669,7 +2672,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="19">
+      <c r="A54" s="18">
         <v>202510001000061</v>
       </c>
       <c r="B54" s="9" t="s">
@@ -2693,7 +2696,7 @@
       <c r="H54" s="7">
         <v>45974</v>
       </c>
-      <c r="I54" s="20" t="str">
+      <c r="I54" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2702,7 +2705,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="18">
+      <c r="A55" s="17">
         <v>202510011000062</v>
       </c>
       <c r="B55" s="10" t="s">
@@ -2726,7 +2729,7 @@
       <c r="H55" s="6">
         <v>45953</v>
       </c>
-      <c r="I55" s="20" t="str">
+      <c r="I55" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2735,7 +2738,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="19">
+      <c r="A56" s="18">
         <v>202510009000063</v>
       </c>
       <c r="B56" s="9" t="s">
@@ -2759,7 +2762,7 @@
       <c r="H56" s="7">
         <v>45954</v>
       </c>
-      <c r="I56" s="20" t="str">
+      <c r="I56" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2768,7 +2771,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="18">
+      <c r="A57" s="17">
         <v>202510004000064</v>
       </c>
       <c r="B57" s="10" t="s">
@@ -2792,7 +2795,7 @@
       <c r="H57" s="6">
         <v>45975</v>
       </c>
-      <c r="I57" s="20" t="str">
+      <c r="I57" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2801,7 +2804,7 @@
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="19">
+      <c r="A58" s="18">
         <v>202510009000065</v>
       </c>
       <c r="B58" s="9" t="s">
@@ -2825,7 +2828,7 @@
       <c r="H58" s="7">
         <v>45972</v>
       </c>
-      <c r="I58" s="20" t="str">
+      <c r="I58" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2834,7 +2837,7 @@
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="18">
+      <c r="A59" s="17">
         <v>202510001000066</v>
       </c>
       <c r="B59" s="10" t="s">
@@ -2858,7 +2861,7 @@
       <c r="H59" s="8">
         <v>45966</v>
       </c>
-      <c r="I59" s="20" t="str">
+      <c r="I59" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2867,7 +2870,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="19">
+      <c r="A60" s="18">
         <v>202510008000067</v>
       </c>
       <c r="B60" s="9" t="s">
@@ -2891,7 +2894,7 @@
       <c r="H60" s="7">
         <v>45966</v>
       </c>
-      <c r="I60" s="20" t="str">
+      <c r="I60" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2900,7 +2903,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="18">
+      <c r="A61" s="17">
         <v>202510001000068</v>
       </c>
       <c r="B61" s="10" t="s">
@@ -2924,7 +2927,7 @@
       <c r="H61" s="6">
         <v>45974</v>
       </c>
-      <c r="I61" s="20" t="str">
+      <c r="I61" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2933,7 +2936,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="19">
+      <c r="A62" s="18">
         <v>202510001000069</v>
       </c>
       <c r="B62" s="9" t="s">
@@ -2957,7 +2960,7 @@
       <c r="H62" s="7">
         <v>45958</v>
       </c>
-      <c r="I62" s="20" t="str">
+      <c r="I62" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2966,7 +2969,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="18">
+      <c r="A63" s="17">
         <v>202510007000070</v>
       </c>
       <c r="B63" s="10" t="s">
@@ -2990,7 +2993,7 @@
       <c r="H63" s="6">
         <v>45958</v>
       </c>
-      <c r="I63" s="20" t="str">
+      <c r="I63" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -2999,7 +3002,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="19">
+      <c r="A64" s="18">
         <v>202510004000071</v>
       </c>
       <c r="B64" s="9" t="s">
@@ -3023,7 +3026,7 @@
       <c r="H64" s="8">
         <v>45960</v>
       </c>
-      <c r="I64" s="20" t="str">
+      <c r="I64" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3032,7 +3035,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="18">
+      <c r="A65" s="17">
         <v>202510011000072</v>
       </c>
       <c r="B65" s="10" t="s">
@@ -3056,7 +3059,7 @@
       <c r="H65" s="8">
         <v>45994</v>
       </c>
-      <c r="I65" s="20" t="str">
+      <c r="I65" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3065,7 +3068,7 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="19">
+      <c r="A66" s="18">
         <v>202510001000073</v>
       </c>
       <c r="B66" s="9" t="s">
@@ -3089,7 +3092,7 @@
       <c r="H66" s="7">
         <v>45972</v>
       </c>
-      <c r="I66" s="20" t="str">
+      <c r="I66" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3098,7 +3101,7 @@
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="18">
+      <c r="A67" s="17">
         <v>202510004000074</v>
       </c>
       <c r="B67" s="10" t="s">
@@ -3122,7 +3125,7 @@
       <c r="H67" s="8">
         <v>45959</v>
       </c>
-      <c r="I67" s="20" t="str">
+      <c r="I67" s="19" t="str">
         <f t="shared" ref="I67:I89" si="1">IF(H67&lt;=G67,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
@@ -3131,7 +3134,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="19">
+      <c r="A68" s="18">
         <v>202510011000075</v>
       </c>
       <c r="B68" s="9" t="s">
@@ -3155,7 +3158,7 @@
       <c r="H68" s="8">
         <v>46027</v>
       </c>
-      <c r="I68" s="20" t="str">
+      <c r="I68" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3164,7 +3167,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="18">
+      <c r="A69" s="17">
         <v>202510001000076</v>
       </c>
       <c r="B69" s="10" t="s">
@@ -3188,7 +3191,7 @@
       <c r="H69" s="6">
         <v>45975</v>
       </c>
-      <c r="I69" s="20" t="str">
+      <c r="I69" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3197,7 +3200,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="19">
+      <c r="A70" s="18">
         <v>202510001000077</v>
       </c>
       <c r="B70" s="9" t="s">
@@ -3221,7 +3224,7 @@
       <c r="H70" s="8">
         <v>45975</v>
       </c>
-      <c r="I70" s="20" t="str">
+      <c r="I70" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3230,7 +3233,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="18">
+      <c r="A71" s="17">
         <v>202510004000078</v>
       </c>
       <c r="B71" s="10" t="s">
@@ -3254,7 +3257,7 @@
       <c r="H71" s="8">
         <v>45975</v>
       </c>
-      <c r="I71" s="20" t="str">
+      <c r="I71" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3263,7 +3266,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" s="19">
+      <c r="A72" s="18">
         <v>202510001000079</v>
       </c>
       <c r="B72" s="9" t="s">
@@ -3287,7 +3290,7 @@
       <c r="H72" s="7">
         <v>45975</v>
       </c>
-      <c r="I72" s="20" t="str">
+      <c r="I72" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3296,7 +3299,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="18">
+      <c r="A73" s="17">
         <v>202510016000080</v>
       </c>
       <c r="B73" s="10" t="s">
@@ -3320,7 +3323,7 @@
       <c r="H73" s="8">
         <v>46062</v>
       </c>
-      <c r="I73" s="20" t="str">
+      <c r="I73" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3329,7 +3332,7 @@
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="19">
+      <c r="A74" s="18">
         <v>202510007000081</v>
       </c>
       <c r="B74" s="9" t="s">
@@ -3353,7 +3356,7 @@
       <c r="H74" s="7">
         <v>45994</v>
       </c>
-      <c r="I74" s="20" t="str">
+      <c r="I74" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3362,7 +3365,7 @@
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="18">
+      <c r="A75" s="17">
         <v>202511011000082</v>
       </c>
       <c r="B75" s="10" t="s">
@@ -3386,7 +3389,7 @@
       <c r="H75" s="8">
         <v>45978</v>
       </c>
-      <c r="I75" s="20" t="str">
+      <c r="I75" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3395,7 +3398,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="19">
+      <c r="A76" s="18">
         <v>202511007000083</v>
       </c>
       <c r="B76" s="9" t="s">
@@ -3419,7 +3422,7 @@
       <c r="H76" s="7">
         <v>45972</v>
       </c>
-      <c r="I76" s="20" t="str">
+      <c r="I76" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3428,7 +3431,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="18">
+      <c r="A77" s="17">
         <v>202511015000084</v>
       </c>
       <c r="B77" s="10" t="s">
@@ -3452,7 +3455,7 @@
       <c r="H77" s="6">
         <v>45967</v>
       </c>
-      <c r="I77" s="20" t="str">
+      <c r="I77" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3461,7 +3464,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="19">
+      <c r="A78" s="18">
         <v>202511001000085</v>
       </c>
       <c r="B78" s="9" t="s">
@@ -3485,7 +3488,7 @@
       <c r="H78" s="8">
         <v>45999</v>
       </c>
-      <c r="I78" s="20" t="str">
+      <c r="I78" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3494,7 +3497,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="18">
+      <c r="A79" s="17">
         <v>202511006000086</v>
       </c>
       <c r="B79" s="10" t="s">
@@ -3518,7 +3521,7 @@
       <c r="H79" s="6">
         <v>46062</v>
       </c>
-      <c r="I79" s="20" t="str">
+      <c r="I79" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3527,7 +3530,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="19">
+      <c r="A80" s="18">
         <v>202511004000087</v>
       </c>
       <c r="B80" s="9" t="s">
@@ -3551,7 +3554,7 @@
       <c r="H80" s="8">
         <v>45972</v>
       </c>
-      <c r="I80" s="20" t="str">
+      <c r="I80" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3560,7 +3563,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81" s="18">
+      <c r="A81" s="17">
         <v>202511007000088</v>
       </c>
       <c r="B81" s="10" t="s">
@@ -3584,7 +3587,7 @@
       <c r="H81" s="8">
         <v>45971</v>
       </c>
-      <c r="I81" s="20" t="str">
+      <c r="I81" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3593,7 +3596,7 @@
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" s="19">
+      <c r="A82" s="18">
         <v>202511008000089</v>
       </c>
       <c r="B82" s="9" t="s">
@@ -3617,7 +3620,7 @@
       <c r="H82" s="8">
         <v>45971</v>
       </c>
-      <c r="I82" s="20" t="str">
+      <c r="I82" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3626,7 +3629,7 @@
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="18">
+      <c r="A83" s="17">
         <v>202511009000090</v>
       </c>
       <c r="B83" s="10" t="s">
@@ -3650,7 +3653,7 @@
       <c r="H83" s="6">
         <v>45996</v>
       </c>
-      <c r="I83" s="20" t="str">
+      <c r="I83" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3659,7 +3662,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="19">
+      <c r="A84" s="18">
         <v>202511009000091</v>
       </c>
       <c r="B84" s="9" t="s">
@@ -3683,7 +3686,7 @@
       <c r="H84" s="7">
         <v>46006</v>
       </c>
-      <c r="I84" s="20" t="str">
+      <c r="I84" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3692,7 +3695,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" s="18">
+      <c r="A85" s="17">
         <v>202511011000092</v>
       </c>
       <c r="B85" s="10" t="s">
@@ -3716,7 +3719,7 @@
       <c r="H85" s="8">
         <v>45978</v>
       </c>
-      <c r="I85" s="20" t="str">
+      <c r="I85" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3725,7 +3728,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="19">
+      <c r="A86" s="18">
         <v>202511011000093</v>
       </c>
       <c r="B86" s="9" t="s">
@@ -3749,7 +3752,7 @@
       <c r="H86" s="8">
         <v>46020</v>
       </c>
-      <c r="I86" s="20" t="str">
+      <c r="I86" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3758,7 +3761,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" s="18">
+      <c r="A87" s="17">
         <v>202511004000094</v>
       </c>
       <c r="B87" s="10" t="s">
@@ -3782,7 +3785,7 @@
       <c r="H87" s="6">
         <v>45974</v>
       </c>
-      <c r="I87" s="20" t="str">
+      <c r="I87" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3791,7 +3794,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="19">
+      <c r="A88" s="18">
         <v>202511011000095</v>
       </c>
       <c r="B88" s="9" t="s">
@@ -3815,7 +3818,7 @@
       <c r="H88" s="8">
         <v>46156</v>
       </c>
-      <c r="I88" s="20" t="str">
+      <c r="I88" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3824,7 +3827,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" s="18">
+      <c r="A89" s="17">
         <v>202511011000096</v>
       </c>
       <c r="B89" s="10" t="s">
@@ -3848,7 +3851,7 @@
       <c r="H89" s="6">
         <v>46156</v>
       </c>
-      <c r="I89" s="20" t="str">
+      <c r="I89" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Fora do Prazo</v>
       </c>
@@ -3857,7 +3860,7 @@
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A90" s="19">
+      <c r="A90" s="18">
         <v>202511001000097</v>
       </c>
       <c r="B90" s="9" t="s">
@@ -3881,7 +3884,7 @@
       <c r="H90" s="8">
         <v>46020</v>
       </c>
-      <c r="I90" s="20" t="str">
+      <c r="I90" s="19" t="str">
         <f t="shared" ref="I90:I117" si="2">IF(H90&lt;=G90,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Fora do Prazo</v>
       </c>
@@ -3890,7 +3893,7 @@
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91" s="18">
+      <c r="A91" s="17">
         <v>202511007000098</v>
       </c>
       <c r="B91" s="10" t="s">
@@ -3914,7 +3917,7 @@
       <c r="H91" s="8">
         <v>45994</v>
       </c>
-      <c r="I91" s="20" t="str">
+      <c r="I91" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3923,7 +3926,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92" s="19">
+      <c r="A92" s="18">
         <v>202511007000099</v>
       </c>
       <c r="B92" s="9" t="s">
@@ -3947,7 +3950,7 @@
       <c r="H92" s="8">
         <v>45994</v>
       </c>
-      <c r="I92" s="20" t="str">
+      <c r="I92" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3956,7 +3959,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" s="18">
+      <c r="A93" s="17">
         <v>202511007000100</v>
       </c>
       <c r="B93" s="10" t="s">
@@ -3980,7 +3983,7 @@
       <c r="H93" s="8">
         <v>45995</v>
       </c>
-      <c r="I93" s="20" t="str">
+      <c r="I93" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -3989,7 +3992,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" s="19">
+      <c r="A94" s="18">
         <v>202511011000101</v>
       </c>
       <c r="B94" s="9" t="s">
@@ -4013,7 +4016,7 @@
       <c r="H94" s="8">
         <v>46020</v>
       </c>
-      <c r="I94" s="20" t="str">
+      <c r="I94" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4022,7 +4025,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="18">
+      <c r="A95" s="17">
         <v>202511009000102</v>
       </c>
       <c r="B95" s="10" t="s">
@@ -4046,7 +4049,7 @@
       <c r="H95" s="6">
         <v>46000</v>
       </c>
-      <c r="I95" s="20" t="str">
+      <c r="I95" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4055,7 +4058,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A96" s="19">
+      <c r="A96" s="18">
         <v>202511001000103</v>
       </c>
       <c r="B96" s="9" t="s">
@@ -4079,7 +4082,7 @@
       <c r="H96" s="8">
         <v>46020</v>
       </c>
-      <c r="I96" s="20" t="str">
+      <c r="I96" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4088,7 +4091,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A97" s="18">
+      <c r="A97" s="17">
         <v>202511007000104</v>
       </c>
       <c r="B97" s="10" t="s">
@@ -4112,7 +4115,7 @@
       <c r="H97" s="8">
         <v>46149</v>
       </c>
-      <c r="I97" s="20" t="str">
+      <c r="I97" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4121,7 +4124,7 @@
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A98" s="19">
+      <c r="A98" s="18">
         <v>202511007000105</v>
       </c>
       <c r="B98" s="9" t="s">
@@ -4145,7 +4148,7 @@
       <c r="H98" s="7">
         <v>46027</v>
       </c>
-      <c r="I98" s="20" t="str">
+      <c r="I98" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4154,7 +4157,7 @@
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A99" s="18">
+      <c r="A99" s="17">
         <v>202511009000106</v>
       </c>
       <c r="B99" s="10" t="s">
@@ -4178,7 +4181,7 @@
       <c r="H99" s="6">
         <v>45996</v>
       </c>
-      <c r="I99" s="20" t="str">
+      <c r="I99" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4187,7 +4190,7 @@
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A100" s="19">
+      <c r="A100" s="18">
         <v>202511001000107</v>
       </c>
       <c r="B100" s="9" t="s">
@@ -4211,7 +4214,7 @@
       <c r="H100" s="7">
         <v>46020</v>
       </c>
-      <c r="I100" s="20" t="str">
+      <c r="I100" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4220,7 +4223,7 @@
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A101" s="18">
+      <c r="A101" s="17">
         <v>202511009000108</v>
       </c>
       <c r="B101" s="10" t="s">
@@ -4244,7 +4247,7 @@
       <c r="H101" s="8">
         <v>45992</v>
       </c>
-      <c r="I101" s="20" t="str">
+      <c r="I101" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4253,7 +4256,7 @@
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A102" s="19">
+      <c r="A102" s="18">
         <v>202511011000109</v>
       </c>
       <c r="B102" s="9" t="s">
@@ -4276,12 +4279,12 @@
       </c>
       <c r="H102" s="9"/>
       <c r="I102" s="14"/>
-      <c r="J102" s="21" t="s">
+      <c r="J102" s="20" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A103" s="18">
+      <c r="A103" s="17">
         <v>202511001000110</v>
       </c>
       <c r="B103" s="10" t="s">
@@ -4305,7 +4308,7 @@
       <c r="H103" s="6">
         <v>45999</v>
       </c>
-      <c r="I103" s="20" t="str">
+      <c r="I103" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4314,7 +4317,7 @@
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A104" s="19">
+      <c r="A104" s="18">
         <v>202512011000111</v>
       </c>
       <c r="B104" s="9" t="s">
@@ -4338,7 +4341,7 @@
       <c r="H104" s="7">
         <v>46020</v>
       </c>
-      <c r="I104" s="20" t="str">
+      <c r="I104" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4347,7 +4350,7 @@
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A105" s="18">
+      <c r="A105" s="17">
         <v>202512015000112</v>
       </c>
       <c r="B105" s="10" t="s">
@@ -4371,7 +4374,7 @@
       <c r="H105" s="8">
         <v>45994</v>
       </c>
-      <c r="I105" s="20" t="str">
+      <c r="I105" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4380,7 +4383,7 @@
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" s="19">
+      <c r="A106" s="18">
         <v>202512015000113</v>
       </c>
       <c r="B106" s="9" t="s">
@@ -4404,7 +4407,7 @@
       <c r="H106" s="7">
         <v>46149</v>
       </c>
-      <c r="I106" s="20" t="str">
+      <c r="I106" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4413,7 +4416,7 @@
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A107" s="18">
+      <c r="A107" s="17">
         <v>202512008000114</v>
       </c>
       <c r="B107" s="10" t="s">
@@ -4437,7 +4440,7 @@
       <c r="H107" s="6">
         <v>45993</v>
       </c>
-      <c r="I107" s="20" t="str">
+      <c r="I107" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4446,7 +4449,7 @@
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A108" s="19">
+      <c r="A108" s="18">
         <v>202512011000115</v>
       </c>
       <c r="B108" s="9" t="s">
@@ -4470,7 +4473,7 @@
       <c r="H108" s="7">
         <v>46156</v>
       </c>
-      <c r="I108" s="20" t="str">
+      <c r="I108" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4479,7 +4482,7 @@
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A109" s="18">
+      <c r="A109" s="17">
         <v>202512015000116</v>
       </c>
       <c r="B109" s="10" t="s">
@@ -4503,7 +4506,7 @@
       <c r="H109" s="6">
         <v>45994</v>
       </c>
-      <c r="I109" s="20" t="str">
+      <c r="I109" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4512,7 +4515,7 @@
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A110" s="19">
+      <c r="A110" s="18">
         <v>202512007000117</v>
       </c>
       <c r="B110" s="9" t="s">
@@ -4536,7 +4539,7 @@
       <c r="H110" s="8">
         <v>46062</v>
       </c>
-      <c r="I110" s="20" t="str">
+      <c r="I110" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4545,7 +4548,7 @@
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A111" s="18">
+      <c r="A111" s="17">
         <v>202512001000118</v>
       </c>
       <c r="B111" s="10" t="s">
@@ -4569,7 +4572,7 @@
       <c r="H111" s="8">
         <v>46020</v>
       </c>
-      <c r="I111" s="20" t="str">
+      <c r="I111" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4578,7 +4581,7 @@
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" s="19">
+      <c r="A112" s="18">
         <v>202512009000119</v>
       </c>
       <c r="B112" s="9" t="s">
@@ -4602,7 +4605,7 @@
       <c r="H112" s="7">
         <v>45995</v>
       </c>
-      <c r="I112" s="20" t="str">
+      <c r="I112" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4611,7 +4614,7 @@
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A113" s="18">
+      <c r="A113" s="17">
         <v>202512011000120</v>
       </c>
       <c r="B113" s="10" t="s">
@@ -4635,7 +4638,7 @@
       <c r="H113" s="8">
         <v>45999</v>
       </c>
-      <c r="I113" s="20" t="str">
+      <c r="I113" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4644,7 +4647,7 @@
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A114" s="19">
+      <c r="A114" s="18">
         <v>202512011000121</v>
       </c>
       <c r="B114" s="9" t="s">
@@ -4668,7 +4671,7 @@
       <c r="H114" s="7">
         <v>46121</v>
       </c>
-      <c r="I114" s="20" t="str">
+      <c r="I114" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4677,7 +4680,7 @@
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A115" s="18">
+      <c r="A115" s="17">
         <v>202512011000122</v>
       </c>
       <c r="B115" s="10" t="s">
@@ -4701,7 +4704,7 @@
       <c r="H115" s="8">
         <v>46027</v>
       </c>
-      <c r="I115" s="20" t="str">
+      <c r="I115" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4710,7 +4713,7 @@
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A116" s="19">
+      <c r="A116" s="18">
         <v>202512007000123</v>
       </c>
       <c r="B116" s="9" t="s">
@@ -4734,7 +4737,7 @@
       <c r="H116" s="7">
         <v>46010</v>
       </c>
-      <c r="I116" s="20" t="str">
+      <c r="I116" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4743,7 +4746,7 @@
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A117" s="18">
+      <c r="A117" s="17">
         <v>202512001000124</v>
       </c>
       <c r="B117" s="10" t="s">
@@ -4767,7 +4770,7 @@
       <c r="H117" s="6">
         <v>46135</v>
       </c>
-      <c r="I117" s="20" t="str">
+      <c r="I117" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4776,7 +4779,7 @@
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A118" s="19">
+      <c r="A118" s="18">
         <v>202512015000125</v>
       </c>
       <c r="B118" s="9" t="s">
@@ -4800,7 +4803,7 @@
       <c r="H118" s="7">
         <v>46062</v>
       </c>
-      <c r="I118" s="20" t="str">
+      <c r="I118" s="19" t="str">
         <f t="shared" ref="I118:I135" si="3">IF(H118&lt;=G118,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Fora do Prazo</v>
       </c>
@@ -4809,7 +4812,7 @@
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A119" s="18">
+      <c r="A119" s="17">
         <v>202512001000126</v>
       </c>
       <c r="B119" s="10" t="s">
@@ -4833,7 +4836,7 @@
       <c r="H119" s="8">
         <v>46020</v>
       </c>
-      <c r="I119" s="20" t="str">
+      <c r="I119" s="19" t="str">
         <f t="shared" si="3"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4842,7 +4845,7 @@
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A120" s="19">
+      <c r="A120" s="18">
         <v>202512011000127</v>
       </c>
       <c r="B120" s="9" t="s">
@@ -4866,7 +4869,7 @@
       <c r="H120" s="8">
         <v>46027</v>
       </c>
-      <c r="I120" s="20" t="str">
+      <c r="I120" s="19" t="str">
         <f t="shared" si="3"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4875,7 +4878,7 @@
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A121" s="18">
+      <c r="A121" s="17">
         <v>202601011000128</v>
       </c>
       <c r="B121" s="10" t="s">
@@ -4899,7 +4902,7 @@
       <c r="H121" s="8">
         <v>46062</v>
       </c>
-      <c r="I121" s="20" t="str">
+      <c r="I121" s="19" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4908,7 +4911,7 @@
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A122" s="19">
+      <c r="A122" s="18">
         <v>202601003000129</v>
       </c>
       <c r="B122" s="9" t="s">
@@ -4932,7 +4935,7 @@
       <c r="H122" s="8">
         <v>46156</v>
       </c>
-      <c r="I122" s="20" t="str">
+      <c r="I122" s="19" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -4941,7 +4944,7 @@
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A123" s="18">
+      <c r="A123" s="17">
         <v>202601011000130</v>
       </c>
       <c r="B123" s="10" t="s">
@@ -4965,7 +4968,7 @@
       <c r="H123" s="8">
         <v>46050</v>
       </c>
-      <c r="I123" s="20" t="str">
+      <c r="I123" s="19" t="str">
         <f t="shared" si="3"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -4974,7 +4977,7 @@
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A124" s="19">
+      <c r="A124" s="18">
         <v>202601003000131</v>
       </c>
       <c r="B124" s="9" t="s">
@@ -4998,7 +5001,7 @@
       <c r="H124" s="8">
         <v>46157</v>
       </c>
-      <c r="I124" s="20" t="str">
+      <c r="I124" s="19" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -5007,7 +5010,7 @@
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A125" s="18">
+      <c r="A125" s="17">
         <v>202601007000132</v>
       </c>
       <c r="B125" s="10" t="s">
@@ -5031,7 +5034,7 @@
       <c r="H125" s="6">
         <v>46031</v>
       </c>
-      <c r="I125" s="20" t="str">
+      <c r="I125" s="19" t="str">
         <f t="shared" si="3"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -5040,7 +5043,7 @@
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A126" s="19">
+      <c r="A126" s="18">
         <v>202601007000133</v>
       </c>
       <c r="B126" s="9" t="s">
@@ -5064,7 +5067,7 @@
       <c r="H126" s="8">
         <v>46157</v>
       </c>
-      <c r="I126" s="20" t="str">
+      <c r="I126" s="19" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -5073,7 +5076,7 @@
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A127" s="18">
+      <c r="A127" s="17">
         <v>202601009000134</v>
       </c>
       <c r="B127" s="10" t="s">
@@ -5097,7 +5100,7 @@
       <c r="H127" s="8">
         <v>46071</v>
       </c>
-      <c r="I127" s="20" t="str">
+      <c r="I127" s="19" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -5106,7 +5109,7 @@
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A128" s="19">
+      <c r="A128" s="18">
         <v>202601011000135</v>
       </c>
       <c r="B128" s="9" t="s">
@@ -5130,7 +5133,7 @@
       <c r="H128" s="8">
         <v>46127</v>
       </c>
-      <c r="I128" s="20" t="str">
+      <c r="I128" s="19" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -5139,7 +5142,7 @@
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A129" s="18">
+      <c r="A129" s="17">
         <v>202601001000136</v>
       </c>
       <c r="B129" s="10" t="s">
@@ -5163,7 +5166,7 @@
       <c r="H129" s="8">
         <v>46071</v>
       </c>
-      <c r="I129" s="20" t="str">
+      <c r="I129" s="19" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -5172,7 +5175,7 @@
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A130" s="19">
+      <c r="A130" s="18">
         <v>202601001000137</v>
       </c>
       <c r="B130" s="9" t="s">
@@ -5196,7 +5199,7 @@
       <c r="H130" s="7">
         <v>46066</v>
       </c>
-      <c r="I130" s="20" t="str">
+      <c r="I130" s="19" t="str">
         <f t="shared" si="3"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -5205,7 +5208,7 @@
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A131" s="18">
+      <c r="A131" s="17">
         <v>202601007000138</v>
       </c>
       <c r="B131" s="10" t="s">
@@ -5229,7 +5232,7 @@
       <c r="H131" s="6">
         <v>46037</v>
       </c>
-      <c r="I131" s="20" t="str">
+      <c r="I131" s="19" t="str">
         <f t="shared" si="3"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -5238,7 +5241,7 @@
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A132" s="19">
+      <c r="A132" s="18">
         <v>202601007000141</v>
       </c>
       <c r="B132" s="9" t="s">
@@ -5262,7 +5265,7 @@
       <c r="H132" s="7">
         <v>46048</v>
       </c>
-      <c r="I132" s="20" t="str">
+      <c r="I132" s="19" t="str">
         <f t="shared" si="3"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -5271,7 +5274,7 @@
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A133" s="18">
+      <c r="A133" s="17">
         <v>202601013000142</v>
       </c>
       <c r="B133" s="10" t="s">
@@ -5295,7 +5298,7 @@
       <c r="H133" s="8">
         <v>46156</v>
       </c>
-      <c r="I133" s="20" t="str">
+      <c r="I133" s="19" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -5304,7 +5307,7 @@
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A134" s="19">
+      <c r="A134" s="18">
         <v>202601007000143</v>
       </c>
       <c r="B134" s="9" t="s">
@@ -5328,7 +5331,7 @@
       <c r="H134" s="8">
         <v>46125</v>
       </c>
-      <c r="I134" s="20" t="str">
+      <c r="I134" s="19" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -5337,7 +5340,7 @@
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A135" s="18">
+      <c r="A135" s="17">
         <v>202602012000144</v>
       </c>
       <c r="B135" s="10" t="s">
@@ -5361,7 +5364,7 @@
       <c r="H135" s="6">
         <v>46135</v>
       </c>
-      <c r="I135" s="20" t="str">
+      <c r="I135" s="19" t="str">
         <f t="shared" si="3"/>
         <v>Fora do Prazo</v>
       </c>
@@ -5370,7 +5373,7 @@
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A136" s="19">
+      <c r="A136" s="18">
         <v>202602007000145</v>
       </c>
       <c r="B136" s="9" t="s">
@@ -5394,7 +5397,7 @@
       <c r="H136" s="8">
         <v>46062</v>
       </c>
-      <c r="I136" s="20" t="str">
+      <c r="I136" s="19" t="str">
         <f t="shared" ref="I136:I137" si="4">IF(H136&lt;=G136,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
@@ -5403,7 +5406,7 @@
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A137" s="18">
+      <c r="A137" s="17">
         <v>202602007000146</v>
       </c>
       <c r="B137" s="10" t="s">
@@ -5427,7 +5430,7 @@
       <c r="H137" s="6">
         <v>46062</v>
       </c>
-      <c r="I137" s="20" t="str">
+      <c r="I137" s="19" t="str">
         <f t="shared" si="4"/>
         <v>Dentro do Prazo</v>
       </c>
@@ -5436,7 +5439,7 @@
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A138" s="19">
+      <c r="A138" s="18">
         <v>202602001000147</v>
       </c>
       <c r="B138" s="9" t="s">
@@ -5457,14 +5460,14 @@
       <c r="G138" s="7">
         <v>46094</v>
       </c>
-      <c r="H138" s="20"/>
+      <c r="H138" s="19"/>
       <c r="I138" s="14"/>
-      <c r="J138" s="21" t="s">
+      <c r="J138" s="20" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A139" s="18">
+      <c r="A139" s="17">
         <v>202602006000148</v>
       </c>
       <c r="B139" s="10" t="s">
@@ -5488,7 +5491,7 @@
       <c r="H139" s="7">
         <v>46168</v>
       </c>
-      <c r="I139" s="20" t="str">
+      <c r="I139" s="19" t="str">
         <f t="shared" ref="I139:I141" si="5">IF(H139&lt;=G139,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Fora do Prazo</v>
       </c>
@@ -5497,7 +5500,7 @@
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A140" s="19">
+      <c r="A140" s="18">
         <v>202602007000149</v>
       </c>
       <c r="B140" s="9" t="s">
@@ -5521,7 +5524,7 @@
       <c r="H140" s="7">
         <v>46125</v>
       </c>
-      <c r="I140" s="20" t="str">
+      <c r="I140" s="19" t="str">
         <f t="shared" si="5"/>
         <v>Fora do Prazo</v>
       </c>
@@ -5530,7 +5533,7 @@
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A141" s="18">
+      <c r="A141" s="17">
         <v>202602007000150</v>
       </c>
       <c r="B141" s="10" t="s">
@@ -5554,7 +5557,7 @@
       <c r="H141" s="7">
         <v>46125</v>
       </c>
-      <c r="I141" s="20" t="str">
+      <c r="I141" s="19" t="str">
         <f t="shared" si="5"/>
         <v>Fora do Prazo</v>
       </c>
@@ -5563,7 +5566,7 @@
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A142" s="19">
+      <c r="A142" s="18">
         <v>202602001000151</v>
       </c>
       <c r="B142" s="9" t="s">
@@ -5596,7 +5599,7 @@
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A143" s="18">
+      <c r="A143" s="17">
         <v>202602012000152</v>
       </c>
       <c r="B143" s="10" t="s">
@@ -5629,7 +5632,7 @@
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A144" s="19">
+      <c r="A144" s="18">
         <v>202602001000153</v>
       </c>
       <c r="B144" s="9" t="s">
@@ -5662,7 +5665,7 @@
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A145" s="18">
+      <c r="A145" s="17">
         <v>202602009000154</v>
       </c>
       <c r="B145" s="10" t="s">
@@ -5695,7 +5698,7 @@
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A146" s="19">
+      <c r="A146" s="18">
         <v>202602007000155</v>
       </c>
       <c r="B146" s="9" t="s">
@@ -5728,7 +5731,7 @@
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A147" s="18">
+      <c r="A147" s="17">
         <v>202602007000156</v>
       </c>
       <c r="B147" s="10" t="s">
@@ -5761,7 +5764,7 @@
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A148" s="19">
+      <c r="A148" s="18">
         <v>202602007000157</v>
       </c>
       <c r="B148" s="9" t="s">
@@ -5794,7 +5797,7 @@
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A149" s="22">
+      <c r="A149" s="21">
         <v>202602013000158</v>
       </c>
       <c r="B149" s="4" t="s">
@@ -5809,7 +5812,7 @@
       <c r="E149" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F149" s="23">
+      <c r="F149" s="22">
         <v>46077.315972222219</v>
       </c>
       <c r="G149" s="11">
@@ -5827,22 +5830,22 @@
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A150" s="24">
+      <c r="A150" s="23">
         <v>202602001000159</v>
       </c>
-      <c r="B150" s="25" t="s">
+      <c r="B150" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C150" s="25" t="s">
+      <c r="C150" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D150" s="25" t="s">
+      <c r="D150" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E150" s="25" t="s">
+      <c r="E150" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F150" s="26">
+      <c r="F150" s="25">
         <v>46077.550694444442</v>
       </c>
       <c r="G150" s="12">
@@ -5860,7 +5863,7 @@
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A151" s="22">
+      <c r="A151" s="21">
         <v>202602015000160</v>
       </c>
       <c r="B151" s="4" t="s">
@@ -5875,7 +5878,7 @@
       <c r="E151" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F151" s="23">
+      <c r="F151" s="22">
         <v>46077.585416666669</v>
       </c>
       <c r="G151" s="11">
@@ -5893,22 +5896,22 @@
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A152" s="24">
+      <c r="A152" s="23">
         <v>202602007000161</v>
       </c>
-      <c r="B152" s="25" t="s">
+      <c r="B152" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C152" s="25" t="s">
+      <c r="C152" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D152" s="25" t="s">
+      <c r="D152" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E152" s="25" t="s">
+      <c r="E152" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="F152" s="26">
+      <c r="F152" s="25">
         <v>46079.628472222219</v>
       </c>
       <c r="G152" s="12">
@@ -5916,12 +5919,12 @@
       </c>
       <c r="H152" s="12"/>
       <c r="I152" s="12"/>
-      <c r="J152" s="21" t="s">
+      <c r="J152" s="20" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A153" s="22">
+      <c r="A153" s="21">
         <v>202603012000162</v>
       </c>
       <c r="B153" s="4" t="s">
@@ -5936,7 +5939,7 @@
       <c r="E153" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F153" s="23">
+      <c r="F153" s="22">
         <v>46084.686805555553</v>
       </c>
       <c r="G153" s="11">
@@ -5954,22 +5957,22 @@
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A154" s="24">
+      <c r="A154" s="23">
         <v>202603012000163</v>
       </c>
-      <c r="B154" s="25" t="s">
+      <c r="B154" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C154" s="25" t="s">
+      <c r="C154" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="D154" s="25" t="s">
+      <c r="D154" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="E154" s="25" t="s">
+      <c r="E154" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="F154" s="26">
+      <c r="F154" s="25">
         <v>46087.588194444441</v>
       </c>
       <c r="G154" s="12">
@@ -5987,7 +5990,7 @@
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A155" s="22">
+      <c r="A155" s="21">
         <v>202603001000165</v>
       </c>
       <c r="B155" s="4" t="s">
@@ -6002,7 +6005,7 @@
       <c r="E155" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F155" s="23">
+      <c r="F155" s="22">
         <v>46092.779166666667</v>
       </c>
       <c r="G155" s="11">
@@ -6020,22 +6023,22 @@
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A156" s="24">
+      <c r="A156" s="23">
         <v>202603004000166</v>
       </c>
-      <c r="B156" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" s="25" t="s">
+      <c r="B156" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="D156" s="25" t="s">
+      <c r="D156" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="E156" s="25" t="s">
+      <c r="E156" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="F156" s="26">
+      <c r="F156" s="25">
         <v>46093.43472222222</v>
       </c>
       <c r="G156" s="12">
@@ -6053,7 +6056,7 @@
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A157" s="22">
+      <c r="A157" s="21">
         <v>202603007000167</v>
       </c>
       <c r="B157" s="4" t="s">
@@ -6068,7 +6071,7 @@
       <c r="E157" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F157" s="23">
+      <c r="F157" s="22">
         <v>46093.443055555559</v>
       </c>
       <c r="G157" s="11">
@@ -6086,22 +6089,22 @@
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A158" s="24">
+      <c r="A158" s="23">
         <v>202603001000168</v>
       </c>
-      <c r="B158" s="25" t="s">
+      <c r="B158" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C158" s="25" t="s">
+      <c r="C158" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D158" s="25" t="s">
+      <c r="D158" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E158" s="25" t="s">
+      <c r="E158" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F158" s="26">
+      <c r="F158" s="25">
         <v>46094.668749999997</v>
       </c>
       <c r="G158" s="12">
@@ -6119,7 +6122,7 @@
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A159" s="22">
+      <c r="A159" s="21">
         <v>202603001000170</v>
       </c>
       <c r="B159" s="4" t="s">
@@ -6134,7 +6137,7 @@
       <c r="E159" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F159" s="23">
+      <c r="F159" s="22">
         <v>46097.759722222225</v>
       </c>
       <c r="G159" s="11">
@@ -6152,7 +6155,7 @@
       </c>
     </row>
     <row r="160" spans="1:10" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A160" s="19">
+      <c r="A160" s="18">
         <v>202603001000171</v>
       </c>
       <c r="B160" s="9" t="s">
@@ -6185,7 +6188,7 @@
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A161" s="18">
+      <c r="A161" s="17">
         <v>202603007000172</v>
       </c>
       <c r="B161" s="10" t="s">
@@ -6218,7 +6221,7 @@
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A162" s="19">
+      <c r="A162" s="18">
         <v>202603012000173</v>
       </c>
       <c r="B162" s="9" t="s">
@@ -6239,7 +6242,7 @@
       <c r="G162" s="7">
         <v>46134</v>
       </c>
-      <c r="H162" s="17">
+      <c r="H162" s="16">
         <v>46156</v>
       </c>
       <c r="I162" s="12" t="str">
@@ -6251,7 +6254,7 @@
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A163" s="19">
+      <c r="A163" s="18">
         <v>202603001000174</v>
       </c>
       <c r="B163" s="9" t="s">
@@ -6272,7 +6275,7 @@
       <c r="G163" s="7">
         <v>46116</v>
       </c>
-      <c r="H163" s="17">
+      <c r="H163" s="16">
         <v>46107</v>
       </c>
       <c r="I163" s="12" t="str">
@@ -6284,7 +6287,7 @@
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A164" s="18">
+      <c r="A164" s="17">
         <v>202603001000175</v>
       </c>
       <c r="B164" s="10" t="s">
@@ -6302,10 +6305,10 @@
       <c r="F164" s="13">
         <v>46108.686805555553</v>
       </c>
-      <c r="G164" s="27">
+      <c r="G164" s="26">
         <v>46138</v>
       </c>
-      <c r="H164" s="17">
+      <c r="H164" s="16">
         <v>46118</v>
       </c>
       <c r="I164" s="12" t="str">
@@ -6317,13 +6320,13 @@
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A165" s="19">
+      <c r="A165" s="18">
         <v>202603001000179</v>
       </c>
       <c r="B165" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C165" s="20" t="s">
+      <c r="C165" s="19" t="s">
         <v>43</v>
       </c>
       <c r="D165" s="9" t="s">
@@ -6338,7 +6341,7 @@
       <c r="G165" s="7">
         <v>46141</v>
       </c>
-      <c r="H165" s="17">
+      <c r="H165" s="16">
         <v>46113</v>
       </c>
       <c r="I165" s="12" t="str">
@@ -6350,7 +6353,7 @@
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A166" s="18">
+      <c r="A166" s="17">
         <v>202603012000180</v>
       </c>
       <c r="B166" s="10" t="s">
@@ -6371,7 +6374,7 @@
       <c r="G166" s="6">
         <v>46141</v>
       </c>
-      <c r="H166" s="17">
+      <c r="H166" s="16">
         <v>46119</v>
       </c>
       <c r="I166" s="12" t="str">
@@ -6383,7 +6386,7 @@
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A167" s="19">
+      <c r="A167" s="18">
         <v>202603007000181</v>
       </c>
       <c r="B167" s="9" t="s">
@@ -6404,7 +6407,7 @@
       <c r="G167" s="7">
         <v>46141</v>
       </c>
-      <c r="H167" s="17">
+      <c r="H167" s="16">
         <v>46160</v>
       </c>
       <c r="I167" s="12" t="str">
@@ -6416,7 +6419,7 @@
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A168" s="19">
+      <c r="A168" s="18">
         <v>202604012000182</v>
       </c>
       <c r="B168" s="9" t="s">
@@ -6437,7 +6440,7 @@
       <c r="G168" s="7">
         <v>46143</v>
       </c>
-      <c r="H168" s="17">
+      <c r="H168" s="16">
         <v>46125</v>
       </c>
       <c r="I168" s="12" t="str">
@@ -6449,7 +6452,7 @@
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A169" s="19">
+      <c r="A169" s="18">
         <v>202604013000183</v>
       </c>
       <c r="B169" s="9" t="s">
@@ -6470,7 +6473,7 @@
       <c r="G169" s="7">
         <v>46149</v>
       </c>
-      <c r="H169" s="17">
+      <c r="H169" s="16">
         <v>46121</v>
       </c>
       <c r="I169" s="12" t="str">
@@ -6482,7 +6485,7 @@
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A170" s="19">
+      <c r="A170" s="18">
         <v>202604004000184</v>
       </c>
       <c r="B170" s="9" t="s">
@@ -6503,7 +6506,7 @@
       <c r="G170" s="7">
         <v>46152</v>
       </c>
-      <c r="H170" s="17">
+      <c r="H170" s="16">
         <v>46127</v>
       </c>
       <c r="I170" s="12" t="str">
@@ -6515,7 +6518,7 @@
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A171" s="19">
+      <c r="A171" s="18">
         <v>202604007000185</v>
       </c>
       <c r="B171" s="9" t="s">
@@ -6536,7 +6539,7 @@
       <c r="G171" s="7">
         <v>46157</v>
       </c>
-      <c r="H171" s="17">
+      <c r="H171" s="16">
         <v>46157</v>
       </c>
       <c r="I171" s="12" t="str">
@@ -6548,7 +6551,7 @@
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A172" s="18">
+      <c r="A172" s="17">
         <v>202604011000186</v>
       </c>
       <c r="B172" s="10" t="s">
@@ -6569,7 +6572,7 @@
       <c r="G172" s="6">
         <v>46158</v>
       </c>
-      <c r="H172" s="17">
+      <c r="H172" s="16">
         <v>46176</v>
       </c>
       <c r="I172" s="12" t="str">
@@ -6581,7 +6584,7 @@
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A173" s="19">
+      <c r="A173" s="18">
         <v>202604013000187</v>
       </c>
       <c r="B173" s="9" t="s">
@@ -6602,7 +6605,7 @@
       <c r="G173" s="7">
         <v>46164</v>
       </c>
-      <c r="H173" s="17">
+      <c r="H173" s="16">
         <v>46161</v>
       </c>
       <c r="I173" s="12" t="str">
@@ -6614,7 +6617,7 @@
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A174" s="18">
+      <c r="A174" s="17">
         <v>202604013000188</v>
       </c>
       <c r="B174" s="10" t="s">
@@ -6635,7 +6638,7 @@
       <c r="G174" s="6">
         <v>46164</v>
       </c>
-      <c r="H174" s="17">
+      <c r="H174" s="16">
         <v>46156</v>
       </c>
       <c r="I174" s="12" t="str">
@@ -6647,7 +6650,7 @@
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A175" s="19">
+      <c r="A175" s="18">
         <v>202604011000189</v>
       </c>
       <c r="B175" s="9" t="s">
@@ -6668,7 +6671,7 @@
       <c r="G175" s="7">
         <v>46164</v>
       </c>
-      <c r="H175" s="17">
+      <c r="H175" s="16">
         <v>46176</v>
       </c>
       <c r="I175" s="12" t="str">
@@ -6680,7 +6683,7 @@
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A176" s="18">
+      <c r="A176" s="17">
         <v>202604003000190</v>
       </c>
       <c r="B176" s="10" t="s">
@@ -6701,7 +6704,7 @@
       <c r="G176" s="6">
         <v>46164</v>
       </c>
-      <c r="H176" s="17">
+      <c r="H176" s="16">
         <v>46135</v>
       </c>
       <c r="I176" s="12" t="str">
@@ -6713,7 +6716,7 @@
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A177" s="19">
+      <c r="A177" s="18">
         <v>202604012000191</v>
       </c>
       <c r="B177" s="9" t="s">
@@ -6734,7 +6737,7 @@
       <c r="G177" s="7">
         <v>46165</v>
       </c>
-      <c r="H177" s="17">
+      <c r="H177" s="16">
         <v>46135</v>
       </c>
       <c r="I177" s="12" t="str">
@@ -6746,7 +6749,7 @@
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A178" s="19">
+      <c r="A178" s="18">
         <v>202604007000192</v>
       </c>
       <c r="B178" s="9" t="s">
@@ -6767,7 +6770,7 @@
       <c r="G178" s="7">
         <v>46166</v>
       </c>
-      <c r="H178" s="29">
+      <c r="H178" s="28">
         <v>46167</v>
       </c>
       <c r="I178" s="12" t="str">
@@ -6779,7 +6782,7 @@
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A179" s="18">
+      <c r="A179" s="17">
         <v>202604012000193</v>
       </c>
       <c r="B179" s="10" t="s">
@@ -6800,7 +6803,7 @@
       <c r="G179" s="6">
         <v>46169</v>
       </c>
-      <c r="H179" s="29">
+      <c r="H179" s="28">
         <v>46141</v>
       </c>
       <c r="I179" s="12" t="str">
@@ -6812,7 +6815,7 @@
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A180" s="19">
+      <c r="A180" s="18">
         <v>202604007000194</v>
       </c>
       <c r="B180" s="9" t="s">
@@ -6833,7 +6836,7 @@
       <c r="G180" s="7">
         <v>46171</v>
       </c>
-      <c r="H180" s="17">
+      <c r="H180" s="16">
         <v>46150</v>
       </c>
       <c r="I180" s="12" t="str">
@@ -6845,7 +6848,7 @@
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A181" s="18">
+      <c r="A181" s="17">
         <v>202605015000195</v>
       </c>
       <c r="B181" s="10" t="s">
@@ -6866,7 +6869,7 @@
       <c r="G181" s="6">
         <v>46178</v>
       </c>
-      <c r="H181" s="17">
+      <c r="H181" s="16">
         <v>46148</v>
       </c>
       <c r="I181" s="12" t="str">
@@ -6878,7 +6881,7 @@
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A182" s="19">
+      <c r="A182" s="18">
         <v>202605007000196</v>
       </c>
       <c r="B182" s="9" t="s">
@@ -6899,7 +6902,7 @@
       <c r="G182" s="7">
         <v>46179</v>
       </c>
-      <c r="H182" s="17">
+      <c r="H182" s="16">
         <v>46150</v>
       </c>
       <c r="I182" s="12" t="str">
@@ -6911,7 +6914,7 @@
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A183" s="18">
+      <c r="A183" s="17">
         <v>202605007000197</v>
       </c>
       <c r="B183" s="10" t="s">
@@ -6932,7 +6935,7 @@
       <c r="G183" s="6">
         <v>46179</v>
       </c>
-      <c r="H183" s="17">
+      <c r="H183" s="16">
         <v>46176</v>
       </c>
       <c r="I183" s="12" t="str">
@@ -6944,7 +6947,7 @@
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A184" s="19">
+      <c r="A184" s="18">
         <v>202605001000198</v>
       </c>
       <c r="B184" s="9" t="s">
@@ -6965,7 +6968,7 @@
       <c r="G184" s="7">
         <v>46179</v>
       </c>
-      <c r="H184" s="29">
+      <c r="H184" s="28">
         <v>46167</v>
       </c>
       <c r="I184" s="12" t="str">
@@ -6977,7 +6980,7 @@
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A185" s="18">
+      <c r="A185" s="17">
         <v>202605007000199</v>
       </c>
       <c r="B185" s="10" t="s">
@@ -6998,7 +7001,7 @@
       <c r="G185" s="6">
         <v>46179</v>
       </c>
-      <c r="H185" s="17">
+      <c r="H185" s="16">
         <v>46150</v>
       </c>
       <c r="I185" s="12" t="str">
@@ -7010,7 +7013,7 @@
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A186" s="19">
+      <c r="A186" s="18">
         <v>202605013000200</v>
       </c>
       <c r="B186" s="9" t="s">
@@ -7031,7 +7034,7 @@
       <c r="G186" s="7">
         <v>46180</v>
       </c>
-      <c r="H186" s="17">
+      <c r="H186" s="16">
         <v>46153</v>
       </c>
       <c r="I186" s="12" t="str">
@@ -7043,7 +7046,7 @@
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A187" s="18">
+      <c r="A187" s="17">
         <v>202605011000201</v>
       </c>
       <c r="B187" s="10" t="s">
@@ -7064,7 +7067,7 @@
       <c r="G187" s="6">
         <v>46186</v>
       </c>
-      <c r="H187" s="17">
+      <c r="H187" s="16">
         <v>46176</v>
       </c>
       <c r="I187" s="12" t="str">
@@ -7076,7 +7079,7 @@
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A188" s="19">
+      <c r="A188" s="18">
         <v>202605007000202</v>
       </c>
       <c r="B188" s="9" t="s">
@@ -7097,14 +7100,19 @@
       <c r="G188" s="7">
         <v>46187</v>
       </c>
-      <c r="H188" s="14"/>
-      <c r="I188" s="14"/>
-      <c r="J188" s="21" t="s">
-        <v>94</v>
+      <c r="H188" s="16">
+        <v>46189</v>
+      </c>
+      <c r="I188" s="12" t="str">
+        <f>IF(H188&lt;=G188,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J188" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A189" s="18">
+      <c r="A189" s="17">
         <v>202605007000203</v>
       </c>
       <c r="B189" s="10" t="s">
@@ -7125,14 +7133,19 @@
       <c r="G189" s="6">
         <v>46190</v>
       </c>
-      <c r="H189" s="14"/>
-      <c r="I189" s="14"/>
+      <c r="H189" s="16">
+        <v>46195</v>
+      </c>
+      <c r="I189" s="12" t="str">
+        <f>IF(H189&lt;=G189,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Fora do Prazo</v>
+      </c>
       <c r="J189" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A190" s="19">
+      <c r="A190" s="18">
         <v>202605013000204</v>
       </c>
       <c r="B190" s="9" t="s">
@@ -7153,7 +7166,7 @@
       <c r="G190" s="7">
         <v>46190</v>
       </c>
-      <c r="H190" s="17">
+      <c r="H190" s="16">
         <v>46160</v>
       </c>
       <c r="I190" s="12" t="str">
@@ -7165,7 +7178,7 @@
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A191" s="18">
+      <c r="A191" s="17">
         <v>202605011000205</v>
       </c>
       <c r="B191" s="10" t="s">
@@ -7186,7 +7199,7 @@
       <c r="G191" s="6">
         <v>46191</v>
       </c>
-      <c r="H191" s="29">
+      <c r="H191" s="28">
         <v>46167</v>
       </c>
       <c r="I191" s="12" t="str">
@@ -7198,7 +7211,7 @@
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A192" s="19">
+      <c r="A192" s="18">
         <v>202605001000206</v>
       </c>
       <c r="B192" s="9" t="s">
@@ -7219,14 +7232,19 @@
       <c r="G192" s="7">
         <v>46192</v>
       </c>
-      <c r="H192" s="14"/>
-      <c r="I192" s="14"/>
+      <c r="H192" s="16">
+        <v>46195</v>
+      </c>
+      <c r="I192" s="12" t="str">
+        <f>IF(H192&lt;=G192,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Fora do Prazo</v>
+      </c>
       <c r="J192" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A193" s="18">
+      <c r="A193" s="17">
         <v>202605003000207</v>
       </c>
       <c r="B193" s="10" t="s">
@@ -7247,11 +7265,11 @@
       <c r="G193" s="6">
         <v>46192</v>
       </c>
-      <c r="H193" s="29">
+      <c r="H193" s="28">
         <v>46167</v>
       </c>
       <c r="I193" s="12" t="str">
-        <f>IF(H193&lt;=G193,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I193:I200" si="10">IF(H193&lt;=G193,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J193" s="2" t="s">
@@ -7259,7 +7277,7 @@
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A194" s="19">
+      <c r="A194" s="18">
         <v>202605011000208</v>
       </c>
       <c r="B194" s="9" t="s">
@@ -7280,14 +7298,19 @@
       <c r="G194" s="7">
         <v>46192</v>
       </c>
-      <c r="H194" s="14"/>
-      <c r="I194" s="14"/>
+      <c r="H194" s="28">
+        <v>46183</v>
+      </c>
+      <c r="I194" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J194" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A195" s="18">
+      <c r="A195" s="17">
         <v>202605007000209</v>
       </c>
       <c r="B195" s="10" t="s">
@@ -7308,14 +7331,19 @@
       <c r="G195" s="6">
         <v>46194</v>
       </c>
-      <c r="H195" s="28"/>
-      <c r="I195" s="14"/>
+      <c r="H195" s="28">
+        <v>46183</v>
+      </c>
+      <c r="I195" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J195" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A196" s="19">
+      <c r="A196" s="18">
         <v>202605007000210</v>
       </c>
       <c r="B196" s="9" t="s">
@@ -7336,39 +7364,44 @@
       <c r="G196" s="7">
         <v>46194</v>
       </c>
-      <c r="H196" s="16"/>
-      <c r="I196" s="14"/>
+      <c r="H196" s="28">
+        <v>46183</v>
+      </c>
+      <c r="I196" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J196" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A197" s="33">
+      <c r="A197" s="32">
         <v>202605001000211</v>
       </c>
-      <c r="B197" s="30" t="s">
+      <c r="B197" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C197" s="30" t="s">
+      <c r="C197" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="D197" s="30" t="s">
+      <c r="D197" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="E197" s="30" t="s">
+      <c r="E197" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="F197" s="31">
+      <c r="F197" s="30">
         <v>46168.666666666664</v>
       </c>
-      <c r="G197" s="32">
+      <c r="G197" s="31">
         <v>46198</v>
       </c>
-      <c r="H197" s="34">
+      <c r="H197" s="33">
         <v>46168</v>
       </c>
       <c r="I197" s="12" t="str">
-        <f>IF(H197&lt;=G197,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="10"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J197" s="2" t="s">
@@ -7376,7 +7409,7 @@
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A198" s="18">
+      <c r="A198" s="17">
         <v>202605007000212</v>
       </c>
       <c r="B198" s="10" t="s">
@@ -7397,11 +7430,11 @@
       <c r="G198" s="6">
         <v>46199</v>
       </c>
-      <c r="H198" s="29">
+      <c r="H198" s="28">
         <v>46181</v>
       </c>
       <c r="I198" s="12" t="str">
-        <f>IF(H198&lt;=G198,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="10"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J198" s="2" t="s">
@@ -7409,7 +7442,7 @@
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A199" s="19">
+      <c r="A199" s="18">
         <v>202605007000213</v>
       </c>
       <c r="B199" s="9" t="s">
@@ -7437,7 +7470,7 @@
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A200" s="18">
+      <c r="A200" s="17">
         <v>202606012000214</v>
       </c>
       <c r="B200" s="10" t="s">
@@ -7458,14 +7491,19 @@
       <c r="G200" s="6">
         <v>46206</v>
       </c>
-      <c r="H200" s="14"/>
-      <c r="I200" s="14"/>
+      <c r="H200" s="33">
+        <v>46195</v>
+      </c>
+      <c r="I200" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J200" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A201" s="19">
+      <c r="A201" s="18">
         <v>202606011000215</v>
       </c>
       <c r="B201" s="9" t="s">
@@ -7493,7 +7531,7 @@
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A202" s="19">
+      <c r="A202" s="18">
         <v>202606007000216</v>
       </c>
       <c r="B202" s="9" t="s">
@@ -7514,7 +7552,7 @@
       <c r="G202" s="7">
         <v>46211</v>
       </c>
-      <c r="H202" s="17">
+      <c r="H202" s="16">
         <v>46181</v>
       </c>
       <c r="I202" s="12" t="str">
@@ -7526,7 +7564,7 @@
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A203" s="18">
+      <c r="A203" s="17">
         <v>202606012000217</v>
       </c>
       <c r="B203" s="10" t="s">
@@ -7554,7 +7592,7 @@
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A204" s="19">
+      <c r="A204" s="18">
         <v>202606009000218</v>
       </c>
       <c r="B204" s="9" t="s">
@@ -7575,14 +7613,19 @@
       <c r="G204" s="7">
         <v>46213</v>
       </c>
-      <c r="H204" s="16"/>
-      <c r="I204" s="14"/>
+      <c r="H204" s="16">
+        <v>46189</v>
+      </c>
+      <c r="I204" s="12" t="str">
+        <f>IF(H204&lt;=G204,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J204" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A205" s="18">
+      <c r="A205" s="17">
         <v>202606016000219</v>
       </c>
       <c r="B205" s="10" t="s">
@@ -7603,14 +7646,14 @@
       <c r="G205" s="6">
         <v>46214</v>
       </c>
-      <c r="H205" s="28"/>
+      <c r="H205" s="27"/>
       <c r="I205" s="14"/>
       <c r="J205" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A206" s="19">
+      <c r="A206" s="18">
         <v>202606002000220</v>
       </c>
       <c r="B206" s="9" t="s">
@@ -7631,14 +7674,253 @@
       <c r="G206" s="7">
         <v>46215</v>
       </c>
-      <c r="H206" s="14"/>
-      <c r="I206" s="14"/>
+      <c r="H206" s="16">
+        <v>46189</v>
+      </c>
+      <c r="I206" s="12" t="str">
+        <f>IF(H207&lt;=G206,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J206" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A207" s="17">
+        <v>202606012000221</v>
+      </c>
+      <c r="B207" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C207" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D207" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E207" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F207" s="13">
+        <v>46189.368750000001</v>
+      </c>
+      <c r="G207" s="6">
+        <v>46219</v>
+      </c>
+      <c r="H207" s="16">
+        <v>46195</v>
+      </c>
+      <c r="I207" s="12" t="str">
+        <f>IF(H208&lt;=G207,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J207" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A208" s="18">
+        <v>202606015000222</v>
+      </c>
+      <c r="B208" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C208" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D208" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E208" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F208" s="15">
+        <v>46190.431250000001</v>
+      </c>
+      <c r="G208" s="7">
+        <v>46220</v>
+      </c>
+      <c r="H208" s="14"/>
+      <c r="I208" s="14"/>
+      <c r="J208" s="2" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A209" s="17">
+        <v>202606007000223</v>
+      </c>
+      <c r="B209" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C209" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D209" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E209" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F209" s="13">
+        <v>46190.479861111111</v>
+      </c>
+      <c r="G209" s="6">
+        <v>46220</v>
+      </c>
+      <c r="H209" s="27"/>
+      <c r="I209" s="14"/>
+      <c r="J209" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A210" s="18">
+        <v>202606003000224</v>
+      </c>
+      <c r="B210" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C210" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D210" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E210" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F210" s="15">
+        <v>46192.575694444444</v>
+      </c>
+      <c r="G210" s="7">
+        <v>46222</v>
+      </c>
+      <c r="H210" s="16">
+        <v>46195</v>
+      </c>
+      <c r="I210" s="12" t="str">
+        <f>IF(H211&lt;=G210,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J210" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A211" s="17">
+        <v>202606004000225</v>
+      </c>
+      <c r="B211" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C211" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D211" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E211" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F211" s="13">
+        <v>46192.585416666669</v>
+      </c>
+      <c r="G211" s="6">
+        <v>46222</v>
+      </c>
+      <c r="H211" s="14"/>
+      <c r="I211" s="14"/>
+      <c r="J211" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A212" s="18">
+        <v>202606012000226</v>
+      </c>
+      <c r="B212" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C212" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D212" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E212" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F212" s="15">
+        <v>46192.593055555553</v>
+      </c>
+      <c r="G212" s="7">
+        <v>46222</v>
+      </c>
+      <c r="H212" s="14"/>
+      <c r="I212" s="14"/>
+      <c r="J212" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A213" s="17">
+        <v>202606010000227</v>
+      </c>
+      <c r="B213" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C213" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D213" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E213" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="F213" s="13">
+        <v>46197.37222222222</v>
+      </c>
+      <c r="G213" s="6">
+        <v>46227</v>
+      </c>
+      <c r="H213" s="14"/>
+      <c r="I213" s="14"/>
+      <c r="J213" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A214" s="18">
+        <v>202606012000228</v>
+      </c>
+      <c r="B214" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C214" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D214" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E214" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F214" s="15">
+        <v>46197.375</v>
+      </c>
+      <c r="G214" s="7">
+        <v>46227</v>
+      </c>
+      <c r="H214" s="14"/>
+      <c r="I214" s="14"/>
+      <c r="J214" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J206" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
+  <autoFilter ref="A1:J214" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J159">
     <sortCondition ref="F1:F159"/>
   </sortState>

--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5674A29-C10A-4DBF-A541-4C8686B96E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3850A7D-D664-4B7A-933B-33C690EB7E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="116">
   <si>
     <t>Protocolo</t>
   </si>
@@ -909,7 +909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J214"/>
+  <dimension ref="A1:J216"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -5917,10 +5917,15 @@
       <c r="G152" s="12">
         <v>46109</v>
       </c>
-      <c r="H152" s="12"/>
-      <c r="I152" s="12"/>
-      <c r="J152" s="20" t="s">
-        <v>94</v>
+      <c r="H152" s="11">
+        <v>46203</v>
+      </c>
+      <c r="I152" s="12" t="str">
+        <f>IF(H152&lt;=G152,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J152" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -6972,7 +6977,7 @@
         <v>46167</v>
       </c>
       <c r="I184" s="12" t="str">
-        <f>IF(H184&lt;=G184,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I184:I192" si="10">IF(H184&lt;=G184,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J184" s="2" t="s">
@@ -7005,7 +7010,7 @@
         <v>46150</v>
       </c>
       <c r="I185" s="12" t="str">
-        <f>IF(H185&lt;=G185,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="10"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J185" s="2" t="s">
@@ -7038,7 +7043,7 @@
         <v>46153</v>
       </c>
       <c r="I186" s="12" t="str">
-        <f>IF(H186&lt;=G186,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="10"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J186" s="2" t="s">
@@ -7071,7 +7076,7 @@
         <v>46176</v>
       </c>
       <c r="I187" s="12" t="str">
-        <f>IF(H187&lt;=G187,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="10"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J187" s="2" t="s">
@@ -7104,7 +7109,7 @@
         <v>46189</v>
       </c>
       <c r="I188" s="12" t="str">
-        <f>IF(H188&lt;=G188,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="10"/>
         <v>Fora do Prazo</v>
       </c>
       <c r="J188" s="2" t="s">
@@ -7137,7 +7142,7 @@
         <v>46195</v>
       </c>
       <c r="I189" s="12" t="str">
-        <f>IF(H189&lt;=G189,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="10"/>
         <v>Fora do Prazo</v>
       </c>
       <c r="J189" s="2" t="s">
@@ -7170,7 +7175,7 @@
         <v>46160</v>
       </c>
       <c r="I190" s="12" t="str">
-        <f>IF(H190&lt;=G190,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="10"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J190" s="2" t="s">
@@ -7203,7 +7208,7 @@
         <v>46167</v>
       </c>
       <c r="I191" s="12" t="str">
-        <f>IF(H191&lt;=G191,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="10"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J191" s="2" t="s">
@@ -7236,7 +7241,7 @@
         <v>46195</v>
       </c>
       <c r="I192" s="12" t="str">
-        <f>IF(H192&lt;=G192,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="10"/>
         <v>Fora do Prazo</v>
       </c>
       <c r="J192" s="2" t="s">
@@ -7269,7 +7274,7 @@
         <v>46167</v>
       </c>
       <c r="I193" s="12" t="str">
-        <f t="shared" ref="I193:I200" si="10">IF(H193&lt;=G193,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I193:I200" si="11">IF(H193&lt;=G193,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J193" s="2" t="s">
@@ -7302,7 +7307,7 @@
         <v>46183</v>
       </c>
       <c r="I194" s="12" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J194" s="2" t="s">
@@ -7335,7 +7340,7 @@
         <v>46183</v>
       </c>
       <c r="I195" s="12" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J195" s="2" t="s">
@@ -7368,7 +7373,7 @@
         <v>46183</v>
       </c>
       <c r="I196" s="12" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J196" s="2" t="s">
@@ -7401,7 +7406,7 @@
         <v>46168</v>
       </c>
       <c r="I197" s="12" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J197" s="2" t="s">
@@ -7434,7 +7439,7 @@
         <v>46181</v>
       </c>
       <c r="I198" s="12" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J198" s="2" t="s">
@@ -7463,10 +7468,15 @@
       <c r="G199" s="7">
         <v>46201</v>
       </c>
-      <c r="H199" s="14"/>
-      <c r="I199" s="14"/>
+      <c r="H199" s="28">
+        <v>46203</v>
+      </c>
+      <c r="I199" s="12" t="str">
+        <f t="shared" si="11"/>
+        <v>Fora do Prazo</v>
+      </c>
       <c r="J199" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
@@ -7495,7 +7505,7 @@
         <v>46195</v>
       </c>
       <c r="I200" s="12" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J200" s="2" t="s">
@@ -7740,10 +7750,15 @@
       <c r="G208" s="7">
         <v>46220</v>
       </c>
-      <c r="H208" s="14"/>
-      <c r="I208" s="14"/>
+      <c r="H208" s="16">
+        <v>46203</v>
+      </c>
+      <c r="I208" s="12" t="str">
+        <f>IF(H209&lt;=G208,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J208" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
@@ -7885,10 +7900,15 @@
       <c r="G213" s="6">
         <v>46227</v>
       </c>
-      <c r="H213" s="14"/>
-      <c r="I213" s="14"/>
+      <c r="H213" s="16">
+        <v>46203</v>
+      </c>
+      <c r="I213" s="12" t="str">
+        <f>IF(H214&lt;=G213,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J213" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
@@ -7913,10 +7933,76 @@
       <c r="G214" s="7">
         <v>46227</v>
       </c>
-      <c r="H214" s="14"/>
-      <c r="I214" s="14"/>
+      <c r="H214" s="16">
+        <v>46203</v>
+      </c>
+      <c r="I214" s="12" t="str">
+        <f>IF(H215&lt;=G214,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J214" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A215" s="17">
+        <v>202606007000229</v>
+      </c>
+      <c r="B215" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C215" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D215" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E215" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F215" s="13">
+        <v>46202.495833333334</v>
+      </c>
+      <c r="G215" s="6">
+        <v>46232</v>
+      </c>
+      <c r="H215" s="14"/>
+      <c r="I215" s="14"/>
+      <c r="J215" s="2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A216" s="18">
+        <v>202606013000230</v>
+      </c>
+      <c r="B216" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C216" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D216" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E216" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F216" s="15">
+        <v>46203.409722222219</v>
+      </c>
+      <c r="G216" s="7">
+        <v>46233</v>
+      </c>
+      <c r="H216" s="16">
+        <v>46203</v>
+      </c>
+      <c r="I216" s="12" t="str">
+        <f>IF(H217&lt;=G216,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J216" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3850A7D-D664-4B7A-933B-33C690EB7E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DFDB8E-1341-4F03-A8E1-35B22FC61B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Dash" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$222</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="117">
   <si>
     <t>Protocolo</t>
   </si>
@@ -376,6 +376,9 @@
   </si>
   <si>
     <t>Mulher</t>
+  </si>
+  <si>
+    <t>SAMU- Serviço de Atendimento Móvel de Urgência</t>
   </si>
 </sst>
 </file>
@@ -502,7 +505,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -593,6 +596,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -909,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J216"/>
+  <dimension ref="A1:J222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -7274,7 +7280,7 @@
         <v>46167</v>
       </c>
       <c r="I193" s="12" t="str">
-        <f t="shared" ref="I193:I200" si="11">IF(H193&lt;=G193,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I193:I201" si="11">IF(H193&lt;=G193,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J193" s="2" t="s">
@@ -7534,10 +7540,15 @@
       <c r="G201" s="7">
         <v>46206</v>
       </c>
-      <c r="H201" s="14"/>
-      <c r="I201" s="14"/>
+      <c r="H201" s="7">
+        <v>46204</v>
+      </c>
+      <c r="I201" s="12" t="str">
+        <f t="shared" si="11"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J201" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
@@ -7595,10 +7606,15 @@
       <c r="G203" s="6">
         <v>46213</v>
       </c>
-      <c r="H203" s="14"/>
-      <c r="I203" s="14"/>
+      <c r="H203" s="16">
+        <v>46217</v>
+      </c>
+      <c r="I203" s="12" t="str">
+        <f>IF(H203&lt;=G203,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Fora do Prazo</v>
+      </c>
       <c r="J203" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
@@ -7872,10 +7888,15 @@
       <c r="G212" s="7">
         <v>46222</v>
       </c>
-      <c r="H212" s="14"/>
-      <c r="I212" s="14"/>
+      <c r="H212" s="16">
+        <v>46217</v>
+      </c>
+      <c r="I212" s="12" t="str">
+        <f>IF(H213&lt;=G212,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J212" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
@@ -7966,10 +7987,15 @@
       <c r="G215" s="6">
         <v>46232</v>
       </c>
-      <c r="H215" s="14"/>
-      <c r="I215" s="14"/>
+      <c r="H215" s="7">
+        <v>46204</v>
+      </c>
+      <c r="I215" s="12" t="str">
+        <f t="shared" ref="I215" si="12">IF(H215&lt;=G215,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J215" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
@@ -8005,8 +8031,176 @@
         <v>19</v>
       </c>
     </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A217" s="17">
+        <v>202606012000231</v>
+      </c>
+      <c r="B217" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C217" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D217" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E217" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F217" s="13">
+        <v>46203.688194444447</v>
+      </c>
+      <c r="G217" s="6">
+        <v>46233</v>
+      </c>
+      <c r="H217" s="27"/>
+      <c r="I217" s="14"/>
+      <c r="J217" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A218" s="18">
+        <v>202607007000232</v>
+      </c>
+      <c r="B218" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C218" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D218" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E218" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F218" s="15">
+        <v>46204.598611111112</v>
+      </c>
+      <c r="G218" s="7">
+        <v>46234</v>
+      </c>
+      <c r="H218" s="34"/>
+      <c r="I218" s="14"/>
+      <c r="J218" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A219" s="17">
+        <v>202607007000233</v>
+      </c>
+      <c r="B219" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C219" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D219" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E219" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F219" s="13">
+        <v>46204.636805555558</v>
+      </c>
+      <c r="G219" s="6">
+        <v>46234</v>
+      </c>
+      <c r="H219" s="14"/>
+      <c r="I219" s="14"/>
+      <c r="J219" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A220" s="18">
+        <v>202607007000234</v>
+      </c>
+      <c r="B220" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C220" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D220" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E220" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F220" s="15">
+        <v>46205.646527777775</v>
+      </c>
+      <c r="G220" s="7">
+        <v>46235</v>
+      </c>
+      <c r="H220" s="34"/>
+      <c r="I220" s="14"/>
+      <c r="J220" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A221" s="17">
+        <v>202607007000235</v>
+      </c>
+      <c r="B221" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C221" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D221" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E221" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F221" s="13">
+        <v>46206.888888888891</v>
+      </c>
+      <c r="G221" s="6">
+        <v>46236</v>
+      </c>
+      <c r="H221" s="14"/>
+      <c r="I221" s="14"/>
+      <c r="J221" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A222" s="18">
+        <v>202607013000236</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C222" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D222" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E222" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F222" s="15">
+        <v>46213.632638888892</v>
+      </c>
+      <c r="G222" s="7">
+        <v>46243</v>
+      </c>
+      <c r="H222" s="34"/>
+      <c r="I222" s="14"/>
+      <c r="J222" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J214" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
+  <autoFilter ref="A1:J222" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J159">
     <sortCondition ref="F1:F159"/>
   </sortState>

--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DFDB8E-1341-4F03-A8E1-35B22FC61B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2C2DCE-8AE2-4AD1-8F06-76F4EC1C06B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Dash" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$229</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="117">
   <si>
     <t>Protocolo</t>
   </si>
@@ -915,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J222"/>
+  <dimension ref="A1:J229"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -7672,10 +7672,15 @@
       <c r="G205" s="6">
         <v>46214</v>
       </c>
-      <c r="H205" s="27"/>
-      <c r="I205" s="14"/>
+      <c r="H205" s="16">
+        <v>46218</v>
+      </c>
+      <c r="I205" s="12" t="str">
+        <f>IF(H205&lt;=G205,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Fora do Prazo</v>
+      </c>
       <c r="J205" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
@@ -7801,8 +7806,8 @@
       </c>
       <c r="H209" s="27"/>
       <c r="I209" s="14"/>
-      <c r="J209" s="2" t="s">
-        <v>15</v>
+      <c r="J209" s="20" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
@@ -7860,10 +7865,15 @@
       <c r="G211" s="6">
         <v>46222</v>
       </c>
-      <c r="H211" s="14"/>
-      <c r="I211" s="14"/>
+      <c r="H211" s="16">
+        <v>46220</v>
+      </c>
+      <c r="I211" s="12" t="str">
+        <f>IF(H212&lt;=G211,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J211" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
@@ -8137,10 +8147,15 @@
       <c r="G220" s="7">
         <v>46235</v>
       </c>
-      <c r="H220" s="34"/>
-      <c r="I220" s="14"/>
+      <c r="H220" s="16">
+        <v>46229</v>
+      </c>
+      <c r="I220" s="12" t="str">
+        <f>IF(H221&lt;=G220,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J220" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
@@ -8165,10 +8180,15 @@
       <c r="G221" s="6">
         <v>46236</v>
       </c>
-      <c r="H221" s="14"/>
-      <c r="I221" s="14"/>
+      <c r="H221" s="16">
+        <v>46229</v>
+      </c>
+      <c r="I221" s="12" t="str">
+        <f>IF(H222&lt;=G221,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J221" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
@@ -8199,8 +8219,229 @@
         <v>15</v>
       </c>
     </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A223" s="18">
+        <v>202607001000237</v>
+      </c>
+      <c r="B223" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C223" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D223" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E223" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F223" s="15">
+        <v>46219.37222222222</v>
+      </c>
+      <c r="G223" s="7">
+        <v>46249</v>
+      </c>
+      <c r="H223" s="16">
+        <v>46230</v>
+      </c>
+      <c r="I223" s="12" t="str">
+        <f>IF(H224&lt;=G223,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J223" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A224" s="17">
+        <v>202607004000238</v>
+      </c>
+      <c r="B224" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C224" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D224" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E224" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F224" s="13">
+        <v>46219.384722222225</v>
+      </c>
+      <c r="G224" s="6">
+        <v>46249</v>
+      </c>
+      <c r="H224" s="27"/>
+      <c r="I224" s="14"/>
+      <c r="J224" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A225" s="18">
+        <v>202607007000239</v>
+      </c>
+      <c r="B225" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C225" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D225" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E225" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F225" s="15">
+        <v>46219.662499999999</v>
+      </c>
+      <c r="G225" s="7">
+        <v>46249</v>
+      </c>
+      <c r="H225" s="16">
+        <v>46230</v>
+      </c>
+      <c r="I225" s="12" t="str">
+        <f>IF(H226&lt;=G225,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J225" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A226" s="17">
+        <v>202607001000240</v>
+      </c>
+      <c r="B226" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C226" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D226" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E226" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F226" s="13">
+        <v>46220.405555555553</v>
+      </c>
+      <c r="G226" s="6">
+        <v>46250</v>
+      </c>
+      <c r="H226" s="14"/>
+      <c r="I226" s="14"/>
+      <c r="J226" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A227" s="18">
+        <v>202607012000241</v>
+      </c>
+      <c r="B227" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C227" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D227" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E227" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F227" s="15">
+        <v>46220.426388888889</v>
+      </c>
+      <c r="G227" s="7">
+        <v>46250</v>
+      </c>
+      <c r="H227" s="16">
+        <v>46230</v>
+      </c>
+      <c r="I227" s="12" t="str">
+        <f>IF(H228&lt;=G227,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J227" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A228" s="17">
+        <v>202607007000242</v>
+      </c>
+      <c r="B228" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C228" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D228" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E228" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F228" s="13">
+        <v>46222.859722222223</v>
+      </c>
+      <c r="G228" s="6">
+        <v>46252</v>
+      </c>
+      <c r="H228" s="16">
+        <v>46230</v>
+      </c>
+      <c r="I228" s="12" t="str">
+        <f>IF(H229&lt;=G228,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J228" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A229" s="18">
+        <v>202607009000243</v>
+      </c>
+      <c r="B229" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C229" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D229" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E229" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F229" s="15">
+        <v>46227.65</v>
+      </c>
+      <c r="G229" s="7">
+        <v>46257</v>
+      </c>
+      <c r="H229" s="16">
+        <v>46230</v>
+      </c>
+      <c r="I229" s="12" t="str">
+        <f>IF(H230&lt;=G229,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J229" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J222" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
+  <autoFilter ref="A1:J229" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J159">
     <sortCondition ref="F1:F159"/>
   </sortState>

--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2C2DCE-8AE2-4AD1-8F06-76F4EC1C06B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172FC04C-6F20-49A4-A12F-26D6DB410B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Dash" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$229</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$238</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="118">
   <si>
     <t>Protocolo</t>
   </si>
@@ -379,13 +379,16 @@
   </si>
   <si>
     <t>SAMU- Serviço de Atendimento Móvel de Urgência</t>
+  </si>
+  <si>
+    <t>Assuntos Diversos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -438,6 +441,12 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -505,7 +514,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -601,6 +610,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -915,7 +925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J229"/>
+  <dimension ref="A1:J238"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -7280,7 +7290,7 @@
         <v>46167</v>
       </c>
       <c r="I193" s="12" t="str">
-        <f t="shared" ref="I193:I201" si="11">IF(H193&lt;=G193,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I193:I216" si="11">IF(H193&lt;=G193,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J193" s="2" t="s">
@@ -7577,7 +7587,7 @@
         <v>46181</v>
       </c>
       <c r="I202" s="12" t="str">
-        <f>IF(H202&lt;=G202,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J202" s="2" t="s">
@@ -7610,7 +7620,7 @@
         <v>46217</v>
       </c>
       <c r="I203" s="12" t="str">
-        <f>IF(H203&lt;=G203,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="11"/>
         <v>Fora do Prazo</v>
       </c>
       <c r="J203" s="2" t="s">
@@ -7643,7 +7653,7 @@
         <v>46189</v>
       </c>
       <c r="I204" s="12" t="str">
-        <f>IF(H204&lt;=G204,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J204" s="2" t="s">
@@ -7676,7 +7686,7 @@
         <v>46218</v>
       </c>
       <c r="I205" s="12" t="str">
-        <f>IF(H205&lt;=G205,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="11"/>
         <v>Fora do Prazo</v>
       </c>
       <c r="J205" s="2" t="s">
@@ -7709,7 +7719,7 @@
         <v>46189</v>
       </c>
       <c r="I206" s="12" t="str">
-        <f>IF(H207&lt;=G206,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J206" s="2" t="s">
@@ -7742,7 +7752,7 @@
         <v>46195</v>
       </c>
       <c r="I207" s="12" t="str">
-        <f>IF(H208&lt;=G207,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J207" s="2" t="s">
@@ -7775,7 +7785,7 @@
         <v>46203</v>
       </c>
       <c r="I208" s="12" t="str">
-        <f>IF(H209&lt;=G208,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J208" s="2" t="s">
@@ -7804,10 +7814,15 @@
       <c r="G209" s="6">
         <v>46220</v>
       </c>
-      <c r="H209" s="27"/>
-      <c r="I209" s="14"/>
-      <c r="J209" s="20" t="s">
-        <v>94</v>
+      <c r="H209" s="7">
+        <v>46236</v>
+      </c>
+      <c r="I209" s="12" t="str">
+        <f t="shared" si="11"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J209" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
@@ -7836,7 +7851,7 @@
         <v>46195</v>
       </c>
       <c r="I210" s="12" t="str">
-        <f>IF(H211&lt;=G210,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J210" s="2" t="s">
@@ -7869,7 +7884,7 @@
         <v>46220</v>
       </c>
       <c r="I211" s="12" t="str">
-        <f>IF(H212&lt;=G211,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J211" s="2" t="s">
@@ -7902,7 +7917,7 @@
         <v>46217</v>
       </c>
       <c r="I212" s="12" t="str">
-        <f>IF(H213&lt;=G212,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J212" s="2" t="s">
@@ -7935,7 +7950,7 @@
         <v>46203</v>
       </c>
       <c r="I213" s="12" t="str">
-        <f>IF(H214&lt;=G213,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J213" s="2" t="s">
@@ -7968,7 +7983,7 @@
         <v>46203</v>
       </c>
       <c r="I214" s="12" t="str">
-        <f>IF(H215&lt;=G214,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J214" s="2" t="s">
@@ -8001,7 +8016,7 @@
         <v>46204</v>
       </c>
       <c r="I215" s="12" t="str">
-        <f t="shared" ref="I215" si="12">IF(H215&lt;=G215,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J215" s="2" t="s">
@@ -8034,7 +8049,7 @@
         <v>46203</v>
       </c>
       <c r="I216" s="12" t="str">
-        <f>IF(H217&lt;=G216,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="11"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J216" s="2" t="s">
@@ -8065,8 +8080,8 @@
       </c>
       <c r="H217" s="27"/>
       <c r="I217" s="14"/>
-      <c r="J217" s="2" t="s">
-        <v>15</v>
+      <c r="J217" s="20" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
@@ -8091,10 +8106,15 @@
       <c r="G218" s="7">
         <v>46234</v>
       </c>
-      <c r="H218" s="34"/>
-      <c r="I218" s="14"/>
+      <c r="H218" s="16">
+        <v>46240</v>
+      </c>
+      <c r="I218" s="12" t="str">
+        <f t="shared" ref="I218:I229" si="12">IF(H218&lt;=G218,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Fora do Prazo</v>
+      </c>
       <c r="J218" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
@@ -8119,10 +8139,15 @@
       <c r="G219" s="6">
         <v>46234</v>
       </c>
-      <c r="H219" s="14"/>
-      <c r="I219" s="14"/>
+      <c r="H219" s="16">
+        <v>46243</v>
+      </c>
+      <c r="I219" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Fora do Prazo</v>
+      </c>
       <c r="J219" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
@@ -8151,7 +8176,7 @@
         <v>46229</v>
       </c>
       <c r="I220" s="12" t="str">
-        <f>IF(H221&lt;=G220,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="12"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J220" s="2" t="s">
@@ -8184,7 +8209,7 @@
         <v>46229</v>
       </c>
       <c r="I221" s="12" t="str">
-        <f>IF(H222&lt;=G221,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="12"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J221" s="2" t="s">
@@ -8213,10 +8238,15 @@
       <c r="G222" s="7">
         <v>46243</v>
       </c>
-      <c r="H222" s="34"/>
-      <c r="I222" s="14"/>
+      <c r="H222" s="16">
+        <v>46252</v>
+      </c>
+      <c r="I222" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Fora do Prazo</v>
+      </c>
       <c r="J222" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
@@ -8245,7 +8275,7 @@
         <v>46230</v>
       </c>
       <c r="I223" s="12" t="str">
-        <f>IF(H224&lt;=G223,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="12"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J223" s="2" t="s">
@@ -8274,10 +8304,15 @@
       <c r="G224" s="6">
         <v>46249</v>
       </c>
-      <c r="H224" s="27"/>
-      <c r="I224" s="14"/>
+      <c r="H224" s="16">
+        <v>46252</v>
+      </c>
+      <c r="I224" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Fora do Prazo</v>
+      </c>
       <c r="J224" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
@@ -8306,7 +8341,7 @@
         <v>46230</v>
       </c>
       <c r="I225" s="12" t="str">
-        <f>IF(H226&lt;=G225,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="12"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J225" s="2" t="s">
@@ -8335,10 +8370,15 @@
       <c r="G226" s="6">
         <v>46250</v>
       </c>
-      <c r="H226" s="14"/>
-      <c r="I226" s="14"/>
+      <c r="H226" s="16">
+        <v>46252</v>
+      </c>
+      <c r="I226" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Fora do Prazo</v>
+      </c>
       <c r="J226" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
@@ -8367,7 +8407,7 @@
         <v>46230</v>
       </c>
       <c r="I227" s="12" t="str">
-        <f>IF(H228&lt;=G227,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="12"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J227" s="2" t="s">
@@ -8400,7 +8440,7 @@
         <v>46230</v>
       </c>
       <c r="I228" s="12" t="str">
-        <f>IF(H229&lt;=G228,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="12"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J228" s="2" t="s">
@@ -8433,15 +8473,267 @@
         <v>46230</v>
       </c>
       <c r="I229" s="12" t="str">
-        <f>IF(H230&lt;=G229,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" si="12"/>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J229" s="2" t="s">
         <v>19</v>
       </c>
     </row>
+    <row r="230" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A230" s="18">
+        <v>202608007000244</v>
+      </c>
+      <c r="B230" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C230" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D230" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E230" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F230" s="15">
+        <v>46245.377083333333</v>
+      </c>
+      <c r="G230" s="7">
+        <v>46275</v>
+      </c>
+      <c r="H230" s="34"/>
+      <c r="I230" s="14"/>
+      <c r="J230" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="17">
+        <v>202608016000245</v>
+      </c>
+      <c r="B231" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C231" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D231" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E231" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F231" s="13">
+        <v>46245.386805555558</v>
+      </c>
+      <c r="G231" s="6">
+        <v>46275</v>
+      </c>
+      <c r="H231" s="27"/>
+      <c r="I231" s="14"/>
+      <c r="J231" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="18">
+        <v>202608012000246</v>
+      </c>
+      <c r="B232" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C232" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D232" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E232" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F232" s="15">
+        <v>46245.39166666667</v>
+      </c>
+      <c r="G232" s="7">
+        <v>46275</v>
+      </c>
+      <c r="H232" s="34"/>
+      <c r="I232" s="14"/>
+      <c r="J232" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A233" s="17">
+        <v>202608003000247</v>
+      </c>
+      <c r="B233" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C233" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D233" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="E233" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F233" s="13">
+        <v>46245.397222222222</v>
+      </c>
+      <c r="G233" s="6">
+        <v>46275</v>
+      </c>
+      <c r="H233" s="14"/>
+      <c r="I233" s="14"/>
+      <c r="J233" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="18">
+        <v>202608013000248</v>
+      </c>
+      <c r="B234" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C234" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D234" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E234" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F234" s="15">
+        <v>46248.429166666669</v>
+      </c>
+      <c r="G234" s="7">
+        <v>46278</v>
+      </c>
+      <c r="H234" s="34"/>
+      <c r="I234" s="14"/>
+      <c r="J234" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="17">
+        <v>202608001000249</v>
+      </c>
+      <c r="B235" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C235" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D235" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E235" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F235" s="13">
+        <v>46251.328472222223</v>
+      </c>
+      <c r="G235" s="6">
+        <v>46281</v>
+      </c>
+      <c r="H235" s="14"/>
+      <c r="I235" s="14"/>
+      <c r="J235" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A236" s="18">
+        <v>202608004000250</v>
+      </c>
+      <c r="B236" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C236" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D236" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E236" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F236" s="15">
+        <v>46251.468055555553</v>
+      </c>
+      <c r="G236" s="7">
+        <v>46281</v>
+      </c>
+      <c r="H236" s="34"/>
+      <c r="I236" s="14"/>
+      <c r="J236" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="17">
+        <v>202608007000251</v>
+      </c>
+      <c r="B237" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C237" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D237" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E237" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F237" s="13">
+        <v>46253.349305555559</v>
+      </c>
+      <c r="G237" s="6">
+        <v>46283</v>
+      </c>
+      <c r="H237" s="14"/>
+      <c r="I237" s="14"/>
+      <c r="J237" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A238" s="18">
+        <v>202608007000252</v>
+      </c>
+      <c r="B238" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C238" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D238" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E238" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F238" s="15">
+        <v>46255.595833333333</v>
+      </c>
+      <c r="G238" s="7">
+        <v>46285</v>
+      </c>
+      <c r="H238" s="34"/>
+      <c r="I238" s="14"/>
+      <c r="J238" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J229" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
+  <autoFilter ref="A1:J238" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J159">
     <sortCondition ref="F1:F159"/>
   </sortState>
